--- a/identity/output/통합_신원보안위협_매트릭스_v2.xlsx
+++ b/identity/output/통합_신원보안위협_매트릭스_v2.xlsx
@@ -37,7 +37,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="17">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -100,12 +100,26 @@
       <color rgb="002E86C1"/>
     </font>
     <font>
-      <color rgb="008C8C8C"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="14"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="001F3864"/>
-      <sz val="14"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00595959"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00A04000"/>
     </font>
     <font>
       <b val="1"/>
@@ -197,7 +211,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -262,12 +276,14 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -860,7 +876,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>시트 양식만 수록 — 시나리오(data/scenarios.yaml)는 다음 단계에서 작성</t>
+          <t>실제 사고 기반 공격 흐름 8개 — 단계별 세부위협(IDT-ID)·행위·탐지 포인트·초크 포인트</t>
         </is>
       </c>
     </row>
@@ -1088,7 +1104,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>38/65개 작성(핵심 요약·요약설명·참조·탐지·대응) — 나머지 27개는 '문구 미작성'(요약설명 자리에 영문명 회색 표시, 대표 사례는 사고 DB 최신 실제 사고, 핵심 대응은 매핑된 대응 기준 ID) | scripts/validate.py 검증 결과: 오류 0건 · 경고 0건</t>
+          <t>65/65개 작성(핵심 요약·요약설명·참조·탐지·대응) — 전 항목 완료 | scripts/validate.py 검증 결과: 오류 0건 · 경고 0건</t>
         </is>
       </c>
     </row>
@@ -1257,7 +1273,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="27" t="inlineStr">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>CISA KEV 신원 판정 — 2026.10.02판 1733건 중 81건</t>
         </is>
@@ -1271,7 +1287,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="29" t="inlineStr">
+      <c r="A4" s="31" t="inlineStr">
         <is>
           <t>■ 원격 접속·경계 장비 인증 우회 (25)</t>
         </is>
@@ -2503,7 +2519,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="29" t="inlineStr">
+      <c r="A32" s="31" t="inlineStr">
         <is>
           <t>■ 세션·토큰 노출·탈취 (6)</t>
         </is>
@@ -2841,7 +2857,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="29" t="inlineStr">
+      <c r="A41" s="31" t="inlineStr">
         <is>
           <t>■ 하드코딩·기본 자격증명·고정 키 (14)</t>
         </is>
@@ -3558,7 +3574,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="29" t="inlineStr">
+      <c r="A58" s="31" t="inlineStr">
         <is>
           <t>■ 디렉터리·Kerberos·NTLM (12)</t>
         </is>
@@ -4179,7 +4195,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="29" t="inlineStr">
+      <c r="A73" s="31" t="inlineStr">
         <is>
           <t>■ 서명·인증서·신원 검증 결함 (5)</t>
         </is>
@@ -4471,7 +4487,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="29" t="inlineStr">
+      <c r="A81" s="31" t="inlineStr">
         <is>
           <t>■ IdP·SSO·신원 관리 제품·계정 복구 (13)</t>
         </is>
@@ -5136,7 +5152,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="29" t="inlineStr">
+      <c r="A97" s="31" t="inlineStr">
         <is>
           <t>■ 자격증명·인증 정보 노출 (6)</t>
         </is>
@@ -5499,14 +5515,14 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="27" t="inlineStr">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>교차 매핑 항목별 연계 세부위협 — 커버리지 점검(미연계 항목은 사유 표기)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="29" t="inlineStr">
+      <c r="A3" s="31" t="inlineStr">
         <is>
           <t>■ Browser &amp; Identity Attacks Matrix (Push Security)</t>
         </is>
@@ -7302,7 +7318,7 @@
       <c r="H55" s="9" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="29" t="inlineStr">
+      <c r="A57" s="31" t="inlineStr">
         <is>
           <t>■ OWASP Non-Human Identities Top 10 (2025)</t>
         </is>
@@ -7715,7 +7731,7 @@
       <c r="H68" s="9" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="29" t="inlineStr">
+      <c r="A70" s="31" t="inlineStr">
         <is>
           <t>■ NIST SP 800-63-4 (주제 코드)</t>
         </is>
@@ -8289,7 +8305,7 @@
       <c r="H85" s="9" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="29" t="inlineStr">
+      <c r="A87" s="31" t="inlineStr">
         <is>
           <t>■ OWASP ASVS 5.0</t>
         </is>
@@ -9262,7 +9278,7 @@
       <c r="H115" s="9" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" s="29" t="inlineStr">
+      <c r="A117" s="31" t="inlineStr">
         <is>
           <t>■ OWASP Automated Threats</t>
         </is>
@@ -9537,7 +9553,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="27" t="inlineStr">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>대응 기준별 연계 세부위협 — 연계 위협의 위험도 분포로 통제 우선순위를 가늠</t>
         </is>
@@ -9551,7 +9567,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="29" t="inlineStr">
+      <c r="A4" s="31" t="inlineStr">
         <is>
           <t>■ CSA CCM v4.1</t>
         </is>
@@ -10382,7 +10398,7 @@
       <c r="G29" s="9" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="29" t="inlineStr">
+      <c r="A31" s="31" t="inlineStr">
         <is>
           <t>■ CIS Controls v8.1</t>
         </is>
@@ -10908,7 +10924,7 @@
       <c r="G46" s="9" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="29" t="inlineStr">
+      <c r="A48" s="31" t="inlineStr">
         <is>
           <t>■ NIST SP 800-53 Rev.5</t>
         </is>
@@ -12518,7 +12534,7 @@
       <c r="G106" s="9" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" s="29" t="inlineStr">
+      <c r="A108" s="31" t="inlineStr">
         <is>
           <t>■ ISMS-P 인증기준</t>
         </is>
@@ -12989,7 +13005,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="27" t="inlineStr">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>다른 매트릭스 항목 ↔ 신원 세부위협 — 같은 위협을 영역별 매트릭스와 오가며 보기</t>
         </is>
@@ -15751,7 +15767,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -15812,17 +15828,17 @@
       </c>
       <c r="D2" s="9" t="inlineStr">
         <is>
-          <t>신원 관점 문구</t>
+          <t>신원 관점 문구 27개 추가(PE·NH·LC·CI·IM)</t>
         </is>
       </c>
       <c r="E2" s="9" t="inlineStr">
         <is>
-          <t>세부위협 65개 중 38개(AU 9·SE 7·CR 5·TS 9·DI 8) 작성 — 핵심 요약·요약설명 2줄·참조(■ 신원 관점 / ■ 실제 사례)·탐지·대응. 실제 사례는 그 행에 매핑된 사고만 [실제 사고]·[실증]·[위협인텔]·[공개 취약점]·[시연] 라벨로 인용하고 수치는 사고 DB 요약에 있는 것만 사용. DI 영역부터는 공격 수법 설명을 줄이고 침해 지점·사례·탐지·대응 위주로 작성</t>
+          <t>PE 6·NH 7·LC 5·CI 4·IM 5개를 작성해 65/65 완료 — DI와 같은 수준(침해 지점·실제 사례·탐지·대응 위주)으로 쓰고, IM(영향·확산)은 '■ 신원 관점'에 그 결과로 이어지는 앞 단계 세부위협을 적음. 사고가 많이 매핑된 행은 최근·국내·대형 사고 중심 대표 사례만 인용(IM-03 47건 중 8건). 인용 사례 131건 → 252건([실제 사고] 209 · [공개 취약점] 16 · [시연] 14 · [실증] 9 · [위협인텔] 4). 사례가 없는 PE-03은 '공개 사고 미확인'과 ATT&amp;CK 절차 근거로 작성</t>
         </is>
       </c>
       <c r="F2" s="9" t="inlineStr">
         <is>
-          <t>보고서 본문에 바로 쓸 수 있는 설명을 사고 근거와 함께 제공</t>
+          <t>전 행에 보고서용 문구를 제공해 v2 마무리</t>
         </is>
       </c>
     </row>
@@ -15839,22 +15855,22 @@
       </c>
       <c r="C3" s="9" t="inlineStr">
         <is>
-          <t>문구</t>
+          <t>시나리오</t>
         </is>
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성 27개</t>
+          <t>공격 체인 시나리오(data/scenarios.yaml)</t>
         </is>
       </c>
       <c r="E3" s="9" t="inlineStr">
         <is>
-          <t>PE·NH·LC·CI·IM 도메인 27개는 '문구 미작성'으로 표시 — 요약설명 자리에 영문명(회색), 보고서용 간략 매트릭스의 대표 사례는 매핑된 실제 사고 중 최신 1건(사고 DB 제목·시점), 핵심 대응은 매핑된 CIS·NIST·ISMS-P ID</t>
+          <t>실제 사고 29건(국내 6건)을 8개 흐름·42개 단계로 재구성 — SCN-01 헬프데스크 사칭→IdP→하이퍼바이저 암호화, SCN-02 토큰 서명 키 탈취·위조, SCN-03 인포스틸러→MFA 없는 SaaS·VPN, SCN-04 SaaS 연동 토큰·연결 앱, SCN-05 AD 장악→랜섬웨어·하이브리드 클라우드 파괴, SCN-06 IdP 공급업체 침해→교체 누락 재침투, SCN-07 국내 크리덴셜 스터핑, SCN-08 국내 통신 가입자 인증 체계. 단계마다 세부위협·ATT&amp;CK 전술 국문명·사고 DB 요약에 있는 행위·탐지 포인트, 흐름마다 초크 포인트(25개)</t>
         </is>
       </c>
       <c r="F3" s="9" t="inlineStr">
         <is>
-          <t>작성 중간 산출물에서도 위험평가·근거·대응 기준 열은 완결된 상태로 활용</t>
+          <t>개별 세부위협을 공격 흐름 안에서 보고 가장 싸게 끊는 통제를 드러냄</t>
         </is>
       </c>
     </row>
@@ -15881,12 +15897,12 @@
       </c>
       <c r="E4" s="9" t="inlineStr">
         <is>
-          <t>문구 검사 추가 — 문구 형식(한 줄 50자·요약 2줄·단락 구성), 사례 라벨·사고 ID·시점·수치·ATT&amp;CK ID를 사고 DB와 대조, KEV 판정 건수·SAT 시연·참조 ID(SAT·NHI·CCM·CIS·NIST·ISMS-P·다른 매트릭스)의 행 매핑 일치, 금지 용어. --allow-missing-text(검증기·빌드)로 미작성 행만 목록으로 두고 작성된 문구는 그대로 검사</t>
+          <t>--allow-missing-text 없이 검증 통과(문구 65개·시나리오 8개, 오류·경고 0건, --strict 통과). 복사본에 오류를 넣어 시나리오·사례 검사가 동작하는지 확인. 빌드·검증 기본 명령에서 --allow-missing-text 제거(중간 산출물용 옵션으로 유지)</t>
         </is>
       </c>
       <c r="F4" s="9" t="inlineStr">
         <is>
-          <t>문구가 근거 DB와 어긋나는 것을 빌드 단계에서 차단</t>
+          <t>v2 완료 기준 충족</t>
         </is>
       </c>
     </row>
@@ -15908,24 +15924,24 @@
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>README · docs/methodology.md · reference/README.md</t>
+          <t>README · docs/methodology.md · docs/작업방향.md · 루트 README</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>매트릭스 README, 방법론(설계 원칙·입력 데이터·분류·사고 DB·교차 매핑·근거 집계·평가 로직·문구 규칙·검증·한계·로드맵), 참조 자료 출처·라이선스 문서 신설, 저장소 루트 README에 신원 매트릭스 절 추가</t>
+          <t>v2 완료 기준으로 숫자·현황·시나리오 절(방법론 §11)·사례 선택 규칙·한계·로드맵 갱신, README에 시나리오 요약 표 추가</t>
         </is>
       </c>
       <c r="F5" s="9" t="inlineStr">
         <is>
-          <t>다른 매트릭스와 같은 문서 구성으로 재현·검토 가능하게 함</t>
+          <t>산출물과 문서의 현황을 일치시킴</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>v1</t>
+          <t>v2</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
@@ -15935,29 +15951,29 @@
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>평가</t>
+          <t>문구</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>위험 평가·근거 집계</t>
+          <t>신원 관점 문구(1차 38개)</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>발생가능성은 AI v3.2·클라우드 v5·OT·공급망 수식 그대로(상 = 실제 사고 2건 이상), 심각도는 신원 결과 기준(신원 체계 장악·다수 계정 동시 장악·정상 권한 대량 피해 = 상, 단일 계정 발판·사용자 선택 의존·조건형 = 중). ATT&amp;CK 사례는 신원 기법 전체 + 범용 기법의 신원 맥락 절차만, KEV는 신원 판정 81건만, Browser &amp; Identity Attacks Matrix는 시연 예시가 있는 기법만 실증 근거로 집계</t>
+          <t>세부위협 65개 중 38개(AU 9·SE 7·CR 5·TS 9·DI 8) 먼저 작성 — 핵심 요약·요약설명 2줄·참조(■ 신원 관점 / ■ 실제 사례)·탐지·대응. 실제 사례는 그 행에 매핑된 사고만 [실제 사고]·[실증]·[위협인텔]·[공개 취약점]·[시연] 라벨로 인용하고 수치는 사고 DB 요약에 있는 것만 사용. DI 영역부터는 공격 수법 설명을 줄이고 침해 지점·사례·탐지·대응 위주로 작성</t>
         </is>
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>다른 매트릭스와 비교 가능성을 유지하면서 '상' 판정을 장악 범위로 제한해 위험도 포화를 줄임(매우 높음 65개 중 26개)</t>
+          <t>보고서 본문에 바로 쓸 수 있는 설명을 사고 근거와 함께 제공</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>v1</t>
+          <t>v2</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
@@ -15967,29 +15983,29 @@
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>구조</t>
+          <t>문구</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>워크북</t>
+          <t>문구 미작성 표시(중간 빌드)</t>
         </is>
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>개요·보고서용 간략 매트릭스·매트릭스 뷰·통합 매트릭스·LITE·도메인 요약·신원 유형·ID 환경 요약·공격 체인 시나리오·역매핑_사고사례·KEV 근거·프레임워크 연계·대응 기준 연계·다른 매트릭스 연계·평가 기준·변경이력 15개 시트</t>
+          <t>1차 중간 빌드에서는 PE·NH·LC·CI·IM 도메인 27개를 '문구 미작성'으로 표시(이후 27개 추가로 해소, 기능은 --allow-missing-text 중간 산출물용으로 유지) — 요약설명 자리에 영문명(회색), 보고서용 간략 매트릭스의 대표 사례는 매핑된 실제 사고 중 최신 1건(사고 DB 제목·시점), 핵심 대응은 매핑된 CIS·NIST·ISMS-P ID</t>
         </is>
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>공급망 v2 양식을 따르되 신원 특성(신원 유형·ID 환경별 현황, 다른 매트릭스 연계 역참조)을 추가</t>
+          <t>작성 중간 산출물에서도 위험평가·근거·대응 기준 열은 완결된 상태로 활용</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>v1</t>
+          <t>v2</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
@@ -16004,93 +16020,93 @@
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>scripts/validate.py</t>
+          <t>scripts/validate.py · 빌드</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>검증기 신설 — 사고 DB 필드·어휘·ID, 분류 체계의 ATT&amp;CK·SAT·NHI·SP 800-63-4·ASVS·OAT·CCM·CIS·NIST·ISMS-P·다른 매트릭스 ID 존재, KEV 판정 CVE·매핑, 미연계 사유 정합(--data-only), 문구·시나리오 대조(v2)</t>
+          <t>문구 검사 추가 — 문구 형식(한 줄 50자·요약 2줄·단락 구성), 사례 라벨·사고 ID·시점·수치·ATT&amp;CK ID를 사고 DB와 대조, KEV 판정 건수·SAT 시연·참조 ID(SAT·NHI·CCM·CIS·NIST·ISMS-P·다른 매트릭스)의 행 매핑 일치, 금지 용어. --allow-missing-text(검증기·빌드)로 미작성 행만 목록으로 두고 작성된 문구는 그대로 검사</t>
         </is>
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>원천 데이터 오류가 위험평가로 번지는 것을 막음</t>
+          <t>문구가 근거 DB와 어긋나는 것을 빌드 단계에서 차단</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>v0</t>
+          <t>v2</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>근거</t>
+          <t>문서</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>신원 보안사고 DB</t>
+          <t>README · docs/methodology.md · reference/README.md</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>공개 출처 126건(2011~2025) 신규 구축 — 실제 사고 116건·실증·연구 7건·위협인텔 3건, 국내 10건(SK텔레콤·KT·쿠팡·LG유플러스·GS리테일 등), 공급망 사고 DB 재인용 14건(origin 표기). 출처 URL은 1차 출처 제목 확인 또는 웹 검색 결과로 확인</t>
+          <t>매트릭스 README, 방법론(설계 원칙·입력 데이터·분류·사고 DB·교차 매핑·근거 집계·평가 로직·문구 규칙·검증·한계·로드맵), 참조 자료 출처·라이선스 문서 신설, 저장소 루트 README에 신원 매트릭스 절 추가</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>클라우드 사고 DB(680건)·OT(85건)·공급망(167건)에 대응하는 신원 영역 실제 근거</t>
+          <t>다른 매트릭스와 같은 문서 구성으로 재현·검토 가능하게 함</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>v0</t>
+          <t>v1</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>근거</t>
+          <t>평가</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>CISA KEV</t>
+          <t>위험 평가·근거 집계</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>2026.10.02판 1,733건 중 인증 계열 CWE·신원 인프라 제품 후보 375건을 수동 판정해 81건 채택(원격 접속 인증 우회 25·하드코딩 자격증명 14·IdP 제품 13·디렉터리/Kerberos/NTLM 12·세션 노출 6·자격증명 노출 6·서명 검증 5)</t>
+          <t>발생가능성은 AI v3.2·클라우드 v5·OT·공급망 수식 그대로(상 = 실제 사고 2건 이상), 심각도는 신원 결과 기준(신원 체계 장악·다수 계정 동시 장악·정상 권한 대량 피해 = 상, 단일 계정 발판·사용자 선택 의존·조건형 = 중). ATT&amp;CK 사례는 신원 기법 전체 + 범용 기법의 신원 맥락 절차만, KEV는 신원 판정 81건만, Browser &amp; Identity Attacks Matrix는 시연 예시가 있는 기법만 실증 근거로 집계</t>
         </is>
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>CWE만으로는 Zerologon·Citrix Bleed·noPac 같은 핵심 신원 취약점이 빠지고, 키워드만으로는 일반 권한 상승이 섞임</t>
+          <t>다른 매트릭스와 비교 가능성을 유지하면서 '상' 판정을 장악 범위로 제한해 위험도 포화를 줄임(매우 높음 65개 중 26개)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>v0</t>
+          <t>v1</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
@@ -16100,47 +16116,175 @@
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>분류 체계</t>
+          <t>워크북</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>신원 공격면 10개 도메인(인증 공격·사회공학·자격증명 탈취·토큰·세션·티켓·디렉터리·IdP·특권·지속성·비인간 신원·수명주기·내부자·고객 계정·영향) → 위협분류 36개 → 세부위협 65개(data/taxonomy.yaml), ATT&amp;CK 전술을 '공격 단계'로 병기</t>
+          <t>개요·보고서용 간략 매트릭스·매트릭스 뷰·통합 매트릭스·LITE·도메인 요약·신원 유형·ID 환경 요약·공격 체인 시나리오·역매핑_사고사례·KEV 근거·프레임워크 연계·대응 기준 연계·다른 매트릭스 연계·평가 기준·변경이력 15개 시트</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>같은 기법이 인력·특권·비인간 신원·고객마다 다른 통제로 막히므로 공격면 축으로 통제 지점을 드러냄</t>
+          <t>공급망 v2 양식을 따르되 신원 특성(신원 유형·ID 환경별 현황, 다른 매트릭스 연계 역참조)을 추가</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>검증</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>scripts/validate.py</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>검증기 신설 — 사고 DB 필드·어휘·ID, 분류 체계의 ATT&amp;CK·SAT·NHI·SP 800-63-4·ASVS·OAT·CCM·CIS·NIST·ISMS-P·다른 매트릭스 ID 존재, KEV 판정 CVE·매핑, 미연계 사유 정합(--data-only), 문구·시나리오 대조(v2)</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>원천 데이터 오류가 위험평가로 번지는 것을 막음</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
           <t>v0</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>근거</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>신원 보안사고 DB</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>공개 출처 126건(2011~2025) 신규 구축 — 실제 사고 116건·실증·연구 7건·위협인텔 3건, 국내 10건(SK텔레콤·KT·쿠팡·LG유플러스·GS리테일 등), 공급망 사고 DB 재인용 14건(origin 표기). 출처 URL은 1차 출처 제목 확인 또는 웹 검색 결과로 확인</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>클라우드 사고 DB(680건)·OT(85건)·공급망(167건)에 대응하는 신원 영역 실제 근거</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>v0</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>근거</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>CISA KEV</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>2026.10.02판 1,733건 중 인증 계열 CWE·신원 인프라 제품 후보 375건을 수동 판정해 81건 채택(원격 접속 인증 우회 25·하드코딩 자격증명 14·IdP 제품 13·디렉터리/Kerberos/NTLM 12·세션 노출 6·자격증명 노출 6·서명 검증 5)</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>CWE만으로는 Zerologon·Citrix Bleed·noPac 같은 핵심 신원 취약점이 빠지고, 키워드만으로는 일반 권한 상승이 섞임</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>v0</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>구조</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>분류 체계</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>신원 공격면 10개 도메인(인증 공격·사회공학·자격증명 탈취·토큰·세션·티켓·디렉터리·IdP·특권·지속성·비인간 신원·수명주기·내부자·고객 계정·영향) → 위협분류 36개 → 세부위협 65개(data/taxonomy.yaml), ATT&amp;CK 전술을 '공격 단계'로 병기</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>같은 기법이 인력·특권·비인간 신원·고객마다 다른 통제로 막히므로 공격면 축으로 통제 지점을 드러냄</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>v0</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
         <is>
           <t>교차 매핑</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="D16" s="9" t="inlineStr">
         <is>
           <t>프레임워크</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E16" s="9" t="inlineStr">
         <is>
           <t>ATT&amp;CK v19.2 · Browser &amp; Identity Attacks Matrix 51개 기법(전부 매핑) · OWASP NHI Top 10 · NIST SP 800-63-4 주제 · OWASP ASVS 5.0 · OWASP 자동화 위협 · CSA CCM v4.1 · CIS Controls v8.1 · NIST SP 800-53 · ISMS-P, 통합 AI·클라우드·OT 매트릭스 v2와 공급망 v2 연계 ID</t>
         </is>
       </c>
-      <c r="F12" s="9" t="inlineStr">
+      <c r="F16" s="9" t="inlineStr">
         <is>
           <t>원문을 싣지 않고 ID·명칭만 연계(라이선스 조건 준수)</t>
         </is>
@@ -16272,7 +16416,7 @@
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>(문구 미작성) Mass data theft and extortion via identities</t>
+          <t>정상 계정·토큰으로 SaaS·DB를 대량 조회해 데이터 탈취·갈취</t>
         </is>
       </c>
       <c r="F5" s="11" t="inlineStr">
@@ -16298,12 +16442,12 @@
       </c>
       <c r="K5" s="9" t="inlineStr">
         <is>
-          <t>[실제 사고] 쿠팡 고객 계정 정보 3,367만 건 유출(퇴사 개발자의 토큰 서명키 악용)(2025-11) (IDI-042)</t>
+          <t>[실제 사고] Snowflake 고객 인스턴스 대량 데이터 탈취(2024-05) (IDI-016)</t>
         </is>
       </c>
       <c r="L5" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: CIS 6.8, NIST AC-6·SI-4·AU-6, ISMS-P 2.9.5</t>
+          <t>데이터 접근 권한을 역할별 최소 권한으로 줄이고 대량 조회·내보내기는 승인·속도 제한 적용(CIS 6.8, NIST AC-6, CCM IAM-05)</t>
         </is>
       </c>
     </row>
@@ -16328,7 +16472,7 @@
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>(문구 미작성) Account-takeover fraud (BEC, payment and impersonation)</t>
+          <t>장악한 메일·SNS·금융 계정으로 송금 사기·사칭 게시·부정 결제</t>
         </is>
       </c>
       <c r="F6" s="11" t="inlineStr">
@@ -16354,12 +16498,12 @@
       </c>
       <c r="K6" s="9" t="inlineStr">
         <is>
-          <t>[실제 사고] KT 불법 펨토셀 경유 결제 인증 탈취·무단 소액결제(2025-09) (IDI-041)</t>
+          <t>[실제 사고] Arup 딥페이크 화상회의 송금 사기(2024-01) (IDI-013)</t>
         </is>
       </c>
       <c r="L6" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: CIS 6.3, NIST AT-2(3)·SI-4·IA-2(1), ISMS-P 2.5.3</t>
+          <t>메일·공식 소셜 미디어·금융 계정에 피싱 저항 MFA를 적용하고 문자 단독 인증을 줄임(CIS 6.3, NIST IA-2(1), ISMS-P 2.5.3, CCM IAM-13)</t>
         </is>
       </c>
     </row>
@@ -16384,7 +16528,7 @@
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>(문구 미작성) Ransomware and destruction after identity takeover</t>
+          <t>도메인·IdP 관리 권한 장악 뒤 전사 랜섬웨어·백업 삭제</t>
         </is>
       </c>
       <c r="F7" s="11" t="inlineStr">
@@ -16410,12 +16554,12 @@
       </c>
       <c r="K7" s="9" t="inlineStr">
         <is>
-          <t>[실제 사고] CitrixBleed 2 세션 토큰 탈취 악용(2025-07) (IDI-090)</t>
+          <t>[실제 사고] MGM Resorts 랜섬웨어(2023-09) (IDI-005)</t>
         </is>
       </c>
       <c r="L7" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: CIS 5.4·6.5, NIST CP-9·AC-6(5)·SI-4, ISMS-P 2.5.5</t>
+          <t>도메인·IdP·백업 관리 권한을 전용 관리자 계정과 피싱 저항 MFA로 분리하고 관리 계층 간 자격증명 재사용 금지(CIS 5.4·6.5, NIST AC-6(5), ISMS-P 2.5.5, CCM IAM-10)</t>
         </is>
       </c>
     </row>
@@ -16440,7 +16584,7 @@
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>(문구 미작성) Chained account compromise across vendors and customers</t>
+          <t>공급업체·플랫폼 신원 침해가 그 서비스를 쓰는 고객 계정으로 연쇄 확산</t>
         </is>
       </c>
       <c r="F8" s="11" t="inlineStr">
@@ -16466,12 +16610,12 @@
       </c>
       <c r="K8" s="9" t="inlineStr">
         <is>
-          <t>[실제 사고] npm chalk·debug 메인테이너 계정 탈취(가짜 2FA 재설정 피싱)(2025-09) (IDI-077)</t>
+          <t>[실제 사고] Okta 지원 시스템 침해(2023-10) (IDI-019)</t>
         </is>
       </c>
       <c r="L8" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: CIS 6.6, NIST SA-9·SR-6·IR-4, ISMS-P 2.3.3</t>
+          <t>신원·원격 지원·CI/CD·연동 공급업체를 핵심 공급망으로 분류해 보안 요구 사항 계약과 정기 평가(NIST SA-9·SR-6, ISMS-P 2.3.3, CCM STA-09)</t>
         </is>
       </c>
     </row>
@@ -16552,7 +16696,7 @@
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>(문구 미작성) Abuse of long-lived access keys, API keys and tokens</t>
+          <t>MFA 없는 장기 액세스 키·API 키 하나로 고객 데이터·인프라 접근</t>
         </is>
       </c>
       <c r="F10" s="11" t="inlineStr">
@@ -16578,12 +16722,12 @@
       </c>
       <c r="K10" s="9" t="inlineStr">
         <is>
-          <t>[실제 사고] Storm-2139 — 노출된 고객 API 키로 생성형 AI 서비스 탈취·재판매(2025-02) (IDI-115)</t>
+          <t>[실제 사고] BeyondTrust 원격 지원 SaaS API 키 탈취로 미 재무부 등 고객 17곳 침해(2024-12) (IDI-084)</t>
         </is>
       </c>
       <c r="L10" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: CIS 5.5, NIST IA-5(13)·IA-9·AC-6·SC-12, ISMS-P 2.5.5·2.7.2</t>
+          <t>장기 키를 단기 토큰·워크로드 신원으로 대체하고 남는 키는 권한 최소화·만료 설정·정기 교체(CIS 5.5, NIST IA-5(13)·AC-6·SC-12, ISMS-P 2.5.5·2.7.2, CCM IAM-14·IAM-05·CEK-12)</t>
         </is>
       </c>
     </row>
@@ -16720,7 +16864,7 @@
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>(문구 미작성) Large-scale credential stuffing against customer accounts</t>
+          <t>유출 아이디·비밀번호 자동 대입으로 고객 계정 대량 탈취</t>
         </is>
       </c>
       <c r="F13" s="11" t="inlineStr">
@@ -16751,7 +16895,7 @@
       </c>
       <c r="L13" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: CIS 6.3, NIST AC-7·IA-5(1)·IA-2(2)·SI-4, ISMS-P 2.5.3·2.5.4</t>
+          <t>고객 계정에 MFA·패스키를 제공하고 위험 기반 추가 인증 적용, 결제·개인정보 변경은 재인증(CIS 6.3, NIST IA-2(2), ISMS-P 2.5.3, CCM IAM-13)</t>
         </is>
       </c>
     </row>
@@ -16832,7 +16976,7 @@
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>(문구 미작성) Insider misuse of legitimate access</t>
+          <t>내부자가 정상 권한으로 고객·내부 데이터를 대량 조회·반출</t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
@@ -16858,12 +17002,12 @@
       </c>
       <c r="K15" s="9" t="inlineStr">
         <is>
-          <t>[실제 사고] 쿠팡 고객 계정 정보 3,367만 건 유출(퇴사 개발자의 토큰 서명키 악용)(2025-11) (IDI-042)</t>
+          <t>[실제 사고] 쿠팡 고객 계정 정보 3,367만 건 유출(2025-11) (IDI-042)</t>
         </is>
       </c>
       <c r="L15" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: CIS 6.8, NIST PM-12·AC-6·AU-6·PS-4, ISMS-P 2.5.6·2.9.5·2.2.5</t>
+          <t>직무 기반 최소 권한과 직무 분리, 고객정보 대량 조회는 승인·사유 기록 뒤 허용(CIS 6.8, NIST AC-6, ISMS-P 2.5.6, CCM IAM-04·IAM-05)</t>
         </is>
       </c>
     </row>
@@ -16888,7 +17032,7 @@
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>(문구 미작성) Malicious or overprivileged OAuth app registration and grants</t>
+          <t>악성·과다 권한 OAuth 앱으로 사용자 MFA와 무관한 조직 데이터 지속 접근</t>
         </is>
       </c>
       <c r="F16" s="11" t="inlineStr">
@@ -16914,12 +17058,12 @@
       </c>
       <c r="K16" s="9" t="inlineStr">
         <is>
-          <t>[실제 사고] Salesforce 대상 음성 피싱(악성 Data Loader 연결 앱 승인 유도)(2025-06) (IDI-036)</t>
+          <t>[실제 사고] Microsoft 기업 메일 침해(2024-01) (IDI-017)</t>
         </is>
       </c>
       <c r="L16" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: CIS 6.7·6.8, NIST AC-6·AC-2·AU-6, ISMS-P 2.5.5·2.5.6</t>
+          <t>앱 등록·동의를 관리자 승인으로 제한하고 검증된 게시자 앱만 허용(CIS 6.7, CCM IAM-15)</t>
         </is>
       </c>
     </row>
@@ -17056,7 +17200,7 @@
       </c>
       <c r="E19" s="9" t="inlineStr">
         <is>
-          <t>(문구 미작성) Service account abuse and human use of NHIs</t>
+          <t>MFA 예외인 고권한 서비스 계정 탈취로 고객 DB·지원 시스템 장악</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
@@ -17082,12 +17226,12 @@
       </c>
       <c r="K19" s="9" t="inlineStr">
         <is>
-          <t>[실제 사고] Storm-0501 하이브리드 환경 랜섬웨어(Entra Connect 동기화 계정 장악)(2024-09) (IDI-022)</t>
+          <t>[실제 사고] Dropbox Sign 고객 DB 침해(2024-04) (IDI-038)</t>
         </is>
       </c>
       <c r="L19" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: CIS 5.5·5.4, NIST IA-9·AC-2·AC-6, ISMS-P 2.5.1·2.5.5</t>
+          <t>서비스 계정 인벤토리로 소유자·용도·권한을 관리하고 대화형 로그인 금지·출발지 제한(CIS 5.5, NIST IA-9·AC-2, ISMS-P 2.5.1, CCM IAM-03)</t>
         </is>
       </c>
     </row>
@@ -17336,7 +17480,7 @@
       </c>
       <c r="E24" s="9" t="inlineStr">
         <is>
-          <t>(문구 미작성) Compromise of telecom subscriber authentication (SIM keys, rogue base stations)</t>
+          <t>유심 인증키 유출·불법 기지국으로 휴대폰 기반 인증 체계 무력화</t>
         </is>
       </c>
       <c r="F24" s="11" t="inlineStr">
@@ -17362,12 +17506,12 @@
       </c>
       <c r="K24" s="9" t="inlineStr">
         <is>
-          <t>[실제 사고] KT 불법 펨토셀 경유 결제 인증 탈취·무단 소액결제(2025-09) (IDI-041)</t>
+          <t>[실제 사고] SK텔레콤 유심 정보 2,696만 건 유출(2025-04) (IDI-040)</t>
         </is>
       </c>
       <c r="L24" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST SC-12·SC-8·SI-4, ISMS-P 2.7.2·2.5.3</t>
+          <t>가입자 인증키를 하드웨어 보안 모듈 등으로 보호하고 침해 시 키 교체·유심 교체 절차 준비(NIST SC-12, ISMS-P 2.7.2, CCM CEK-19)</t>
         </is>
       </c>
     </row>
@@ -17392,7 +17536,7 @@
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
-          <t>(문구 미작성) Bribed or recruited insiders</t>
+          <t>고객지원·협력사 인력 매수로 정상 조회 권한을 통한 고객 정보 유출</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
@@ -17418,12 +17562,12 @@
       </c>
       <c r="K25" s="9" t="inlineStr">
         <is>
-          <t>[실제 사고] Coinbase 고객 데이터 유출(매수된 해외 고객지원 인력)(2025-05) (IDI-012)</t>
+          <t>[실제 사고] Coinbase 고객 데이터 유출(2025-05) (IDI-012)</t>
         </is>
       </c>
       <c r="L25" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: CIS 6.8, NIST PM-12·PS-3·AU-6, ISMS-P 2.5.6·2.9.5</t>
+          <t>고객정보 조회는 티켓·사유와 묶어 필요한 항목만 보이게 하고 민감 정보는 마스킹(CIS 6.8, ISMS-P 2.5.6, CCM IAM-04)</t>
         </is>
       </c>
     </row>
@@ -17448,7 +17592,7 @@
       </c>
       <c r="E26" s="9" t="inlineStr">
         <is>
-          <t>(문구 미작성) Theft of SaaS integration tokens and chained access</t>
+          <t>SaaS 연동 공급자의 OAuth 토큰 탈취로 여러 고객 조직 데이터 연쇄 접근</t>
         </is>
       </c>
       <c r="F26" s="11" t="inlineStr">
@@ -17479,7 +17623,7 @@
       </c>
       <c r="L26" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: CIS 6.6, NIST IA-9·SA-9·AC-6, ISMS-P 2.3.3·2.5.5</t>
+          <t>연동 앱 승인은 관리자 검토로 제한하고 권한 범위·토큰 수명 최소화, 미사용 연동 정기 정리(CIS 6.6, NIST AC-6, ISMS-P 2.5.5, CCM IAM-14)</t>
         </is>
       </c>
     </row>
@@ -17672,7 +17816,7 @@
       </c>
       <c r="E30" s="9" t="inlineStr">
         <is>
-          <t>(문구 미작성) Compromise of privileged access management and admin tooling</t>
+          <t>PAM·계정 관리 도구 장악으로 연결된 시스템 관리 권한 일괄 확보</t>
         </is>
       </c>
       <c r="F30" s="11" t="inlineStr">
@@ -17698,12 +17842,12 @@
       </c>
       <c r="K30" s="9" t="inlineStr">
         <is>
-          <t>[실제 사고] Uber 내부망 침해(협력사 자격증명·MFA 승인 반복·PAM 관리자 자격증명)(2022-09) (IDI-002)</t>
+          <t>[실제 사고] Uber 내부망 침해(2022-09) (IDI-002)</t>
         </is>
       </c>
       <c r="L30" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: CIS 5.4·6.5, NIST AC-2(7)·AC-6(5)·IA-2(1), ISMS-P 2.5.5</t>
+          <t>PAM·관리 도구 관리자는 전용 관리자 계정·전용 단말로 분리하고 피싱 저항 MFA 필수(CIS 5.4·6.5, NIST AC-6(5)·IA-2(1), ISMS-P 2.5.5, CCM IAM-09·IAM-10)</t>
         </is>
       </c>
     </row>
@@ -17840,7 +17984,7 @@
       </c>
       <c r="E33" s="9" t="inlineStr">
         <is>
-          <t>(문구 미작성) Abuse of vendor, contractor and guest accounts</t>
+          <t>협력사·외주 인력 계정과 외주 지원 창구를 거쳐 원청 시스템 침투</t>
         </is>
       </c>
       <c r="F33" s="12" t="inlineStr">
@@ -17866,12 +18010,12 @@
       </c>
       <c r="K33" s="9" t="inlineStr">
         <is>
-          <t>[실제 사고] Marks &amp; Spencer 랜섬웨어(협력사 대상 직원 사칭으로 비밀번호 재설정)(2025-04) (IDI-010)</t>
+          <t>[실제 사고] Medibank 고객 970만 명 정보 유출(2022-10) (IDI-018)</t>
         </is>
       </c>
       <c r="L33" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: CIS 6.1·6.2, NIST PS-7·AC-2·AC-20·SA-9, ISMS-P 2.3.3·2.3.4</t>
+          <t>외부 인력 계정은 승인 절차로 발급하고 접근 범위·기간을 계약에 맞춰 제한, 만료 시 즉시 회수(CIS 6.1·6.2, NIST PS-7·AC-2, ISMS-P 2.3.3·2.3.4, CCM IAM-06·IAM-08)</t>
         </is>
       </c>
     </row>
@@ -17896,7 +18040,7 @@
       </c>
       <c r="E34" s="9" t="inlineStr">
         <is>
-          <t>(문구 미작성) Failure to rotate or revoke secrets and credentials</t>
+          <t>샌 비밀·퇴사자 키를 교체·폐기하지 않아 침해 뒤에도 재침투 허용</t>
         </is>
       </c>
       <c r="F34" s="12" t="inlineStr">
@@ -17922,12 +18066,12 @@
       </c>
       <c r="K34" s="9" t="inlineStr">
         <is>
-          <t>[실제 사고] 쿠팡 고객 계정 정보 3,367만 건 유출(퇴사 개발자의 토큰 서명키 악용)(2025-11) (IDI-042)</t>
+          <t>[실제 사고] 쿠팡 고객 계정 정보 3,367만 건 유출(2025-11) (IDI-042)</t>
         </is>
       </c>
       <c r="L34" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: CIS 5.5·6.2, NIST IA-5·IA-5(13)·AC-2(3), ISMS-P 2.5.1·2.7.2</t>
+          <t>비밀 인벤토리에 소유자·용도·만료일을 기록하고 정기 교체·자동 만료 적용(CIS 5.5, NIST IA-5·IA-5(13), ISMS-P 2.7.2, CCM CEK-12)</t>
         </is>
       </c>
     </row>
@@ -18008,7 +18152,7 @@
       </c>
       <c r="E36" s="9" t="inlineStr">
         <is>
-          <t>(문구 미작성) Registering attacker MFA devices and authentication methods</t>
+          <t>탈취 계정에 공격자 MFA 장치·인증 수단을 등록해 접근 유지</t>
         </is>
       </c>
       <c r="F36" s="12" t="inlineStr">
@@ -18034,12 +18178,12 @@
       </c>
       <c r="K36" s="9" t="inlineStr">
         <is>
-          <t>[실제 사고] Storm-2372 디바이스 코드 피싱 캠페인(2025-02) (IDI-031)</t>
+          <t>[실제 사고] Scattered Spider 합동 권고(2023-11) (IDI-008)</t>
         </is>
       </c>
       <c r="L36" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: CIS 6.3·6.5, NIST IA-5·IA-2(1)·AU-6, ISMS-P 2.5.3</t>
+          <t>MFA 등록·재등록에 기존 강한 인증 수단 확인이나 관리자 승인을 요구하고 등록 가능 위치·장치를 조건부로 제한(NIST IA-5, ISMS-P 2.5.3, CCM IAM-13·IAM-07)</t>
         </is>
       </c>
     </row>
@@ -18232,7 +18376,7 @@
       </c>
       <c r="E40" s="9" t="inlineStr">
         <is>
-          <t>(문구 미작성) Orphaned, dormant and unrevoked accounts</t>
+          <t>퇴사자·휴면·미사용 계정과 회수되지 않은 권한으로 침투·무단 조회</t>
         </is>
       </c>
       <c r="F40" s="12" t="inlineStr">
@@ -18258,12 +18402,12 @@
       </c>
       <c r="K40" s="9" t="inlineStr">
         <is>
-          <t>[실제 사고] 쿠팡 고객 계정 정보 3,367만 건 유출(퇴사 개발자의 토큰 서명키 악용)(2025-11) (IDI-042)</t>
+          <t>[실제 사고] Colonial Pipeline 랜섬웨어(2021-05) (IDI-014)</t>
         </is>
       </c>
       <c r="L40" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: CIS 5.3·5.6·6.2, NIST AC-2(3)·PS-4·PS-5·AC-2, ISMS-P 2.2.5·2.5.1·2.5.6</t>
+          <t>인사 변동과 연동한 계정·권한 자동 회수, 퇴사 당일 비활성화와 관련 키·토큰 폐기(CIS 6.2, NIST AC-2(3)·PS-4·PS-5, ISMS-P 2.2.5, CCM IAM-07·HRS-06)</t>
         </is>
       </c>
     </row>
@@ -18512,7 +18656,7 @@
       </c>
       <c r="E45" s="9" t="inlineStr">
         <is>
-          <t>(문구 미작성) Bypassing eKYC and face verification (deepfake, injection)</t>
+          <t>딥페이크 얼굴·영상으로 eKYC·생체 본인확인을 통과해 계좌 접근</t>
         </is>
       </c>
       <c r="F45" s="12" t="inlineStr">
@@ -18538,12 +18682,12 @@
       </c>
       <c r="K45" s="9" t="inlineStr">
         <is>
-          <t>[실제 사고] FinCEN 경보 — 딥페이크 신분증·영상으로 계좌 개설·본인확인 우회(2024-11) (IDI-062)</t>
+          <t>[실제 사고] GoldPickaxe 얼굴 인식 정보 탈취 트로이목마(2024-02) (IDI-060)</t>
         </is>
       </c>
       <c r="L45" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST IA-12·IA-12(5), ISMS-P 2.5.3</t>
+          <t>실제 사람 여부를 판별하는 생체 검사와 주입 공격 탐지를 적용하고 얼굴 인증 단독으로 고위험 거래를 허용하지 않음(NIST IA-12, ISMS-P 2.5.3, CCM IAM-13)</t>
         </is>
       </c>
     </row>
@@ -18568,7 +18712,7 @@
       </c>
       <c r="E46" s="9" t="inlineStr">
         <is>
-          <t>(문구 미작성) Account access removal and admin lockout</t>
+          <t>관리자 계정 삭제·자격증명 변경으로 대응 차단과 연동 계정 파괴</t>
         </is>
       </c>
       <c r="F46" s="12" t="inlineStr">
@@ -18594,12 +18738,12 @@
       </c>
       <c r="K46" s="9" t="inlineStr">
         <is>
-          <t>[실제 사고] MERCURY·DEV-1084 하이브리드 환경 파괴 공격(Azure AD Connect 악용)(2023-04) (IDI-023)</t>
+          <t>[실제 사고] LAPSUS$ 연쇄 침해(2022-03) (IDI-001)</t>
         </is>
       </c>
       <c r="L46" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: CIS 5.4, NIST CP-9·AC-2(7)·IR-4, ISMS-P 2.5.5</t>
+          <t>일상 관리와 분리된 긴급(break-glass) 계정을 오프라인 보관 자격증명·하드웨어 키로 유지하고 특권 계정 사용을 감사(CIS 5.4, NIST AC-2(7), ISMS-P 2.5.5, CCM IAM-10)</t>
         </is>
       </c>
     </row>
@@ -18624,7 +18768,7 @@
       </c>
       <c r="E47" s="9" t="inlineStr">
         <is>
-          <t>(문구 미작성) Fraudulent hiring with stolen or fake identities</t>
+          <t>도용·위조 신원으로 원격 IT 인력 위장 취업해 정규 계정 획득</t>
         </is>
       </c>
       <c r="F47" s="12" t="inlineStr">
@@ -18650,12 +18794,12 @@
       </c>
       <c r="K47" s="9" t="inlineStr">
         <is>
-          <t>[실제 사고] 북한 원격 IT 인력 위장 취업 일제 단속(도용·위조 신원, 노트북 농장)(2025-06) (IDI-105)</t>
+          <t>[실제 사고] 북한 원격 IT 인력 위장 취업 일제 단속(2025-06) (IDI-105)</t>
         </is>
       </c>
       <c r="L47" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: CIS 6.1, NIST PS-3·IA-12·PM-12, ISMS-P 2.5.1</t>
+          <t>원격 채용에 대면 또는 강한 신원 확인 절차를 두고 신분증·주소 진위를 검증(NIST IA-12·PS-3, CCM HRS-09)</t>
         </is>
       </c>
     </row>
@@ -18736,7 +18880,7 @@
       </c>
       <c r="E49" s="9" t="inlineStr">
         <is>
-          <t>(문구 미작성) Account opening with stolen or synthetic identities</t>
+          <t>도용 신분증·합성 신원으로 금융 계좌·서비스 계정 부정 개설</t>
         </is>
       </c>
       <c r="F49" s="12" t="inlineStr">
@@ -18762,12 +18906,12 @@
       </c>
       <c r="K49" s="9" t="inlineStr">
         <is>
-          <t>[실제 사고] FinCEN 경보 — 딥페이크 신분증·영상으로 계좌 개설·본인확인 우회(2024-11) (IDI-062)</t>
+          <t>[실제 사고] 홍콩 딥페이크 얼굴 바꾸기로 대출·계좌 개설 사기 조직 검거(2023-08) (IDI-061)</t>
         </is>
       </c>
       <c r="L49" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST IA-12·IA-8, ISMS-P 2.5.2</t>
+          <t>비대면 개설의 신원 확인을 신분증 진위·명의자 확인·기기 정보 등 여러 근거로 교차 검증(NIST IA-12, ISMS-P 2.5.2)</t>
         </is>
       </c>
     </row>
@@ -18792,7 +18936,7 @@
       </c>
       <c r="E50" s="9" t="inlineStr">
         <is>
-          <t>(문구 미작성) Mailbox rules, delegation and forwarding abuse</t>
+          <t>메일함 규칙·자동 전달·위임 설정으로 대화 은닉과 메일 지속 수집</t>
         </is>
       </c>
       <c r="F50" s="12" t="inlineStr">
@@ -18818,12 +18962,12 @@
       </c>
       <c r="K50" s="9" t="inlineStr">
         <is>
-          <t>[실제 사고] Storm-1167 다단계 AiTM 피싱·BEC(신뢰 거래처 계정 경유 확산)(2023-06) (IDI-030)</t>
+          <t>[실제 사고] AiTM 피싱으로 세션 쿠키 탈취 후 BEC(2022-07) (IDI-029)</t>
         </is>
       </c>
       <c r="L50" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST AU-6·SI-4, ISMS-P 2.9.5</t>
+          <t>조직 외부 자동 전달을 기본 차단하고 예외는 승인제로 운영, 규칙·위임 변경 감사 로그 정기 점검(ISMS-P 2.9.5, CCM LOG-05)</t>
         </is>
       </c>
     </row>
@@ -19240,7 +19384,7 @@
       </c>
       <c r="E58" s="9" t="inlineStr">
         <is>
-          <t>(문구 미작성) Abuse of AI agent identity and delegated authority</t>
+          <t>AI 에이전트가 위임받은 사용자 토큰·연동 권한으로 데이터 노출</t>
         </is>
       </c>
       <c r="F58" s="13" t="inlineStr">
@@ -19266,12 +19410,12 @@
       </c>
       <c r="K58" s="9" t="inlineStr">
         <is>
-          <t>[실제 사고] Asana MCP 서버 조직 간 데이터 노출(AI 연동 권한 격리 결함)(2025-06) (IDI-117)</t>
+          <t>[실제 사고] Asana MCP 서버 조직 간 데이터 노출(2025-06) (IDI-117)</t>
         </is>
       </c>
       <c r="L58" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: CIS 6.8, NIST AC-6·IA-9·AC-3, ISMS-P 2.5.5</t>
+          <t>에이전트 전용 신원을 두고 작업별 최소 범위·짧은 수명의 토큰만 위임(CIS 6.8, NIST AC-6·IA-9, ISMS-P 2.5.5, CCM IAM-05)</t>
         </is>
       </c>
     </row>
@@ -19520,7 +19664,7 @@
       </c>
       <c r="E63" s="9" t="inlineStr">
         <is>
-          <t>(문구 미작성) Overprivileged workload identities and trust misconfiguration</t>
+          <t>과다 권한 워크로드 역할·느슨한 신뢰 설정으로 클라우드 데이터 대량 접근</t>
         </is>
       </c>
       <c r="F63" s="13" t="inlineStr">
@@ -19546,12 +19690,12 @@
       </c>
       <c r="K63" s="9" t="inlineStr">
         <is>
-          <t>[실제 사고] Capital One 1억 600만 명 정보 유출(과다 권한 워크로드 역할 자격증명)(2019-07) (IDI-112)</t>
+          <t>[실제 사고] Capital One 1억 600만 명 정보 유출(2019-07) (IDI-112)</t>
         </is>
       </c>
       <c r="L63" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: CIS 6.8, NIST AC-6·IA-9·CM-6, ISMS-P 2.5.5</t>
+          <t>워크로드 역할을 작업별 최소 권한으로 나누고 데이터 접근은 별도 역할로 분리(CIS 6.8, NIST AC-6, ISMS-P 2.5.5, CCM IAM-05·IAM-15)</t>
         </is>
       </c>
     </row>
@@ -19576,7 +19720,7 @@
       </c>
       <c r="E64" s="9" t="inlineStr">
         <is>
-          <t>(문구 미작성) Excessive permissions and privilege escalation paths</t>
+          <t>과다 권한·누적 역할을 타고 탈취 계정에서 관리자 권한으로 확대</t>
         </is>
       </c>
       <c r="F64" s="13" t="inlineStr">
@@ -19602,12 +19746,12 @@
       </c>
       <c r="K64" s="9" t="inlineStr">
         <is>
-          <t>[실제 사고] Twitter 내부 관리 도구 장악(IT 헬프데스크 사칭 전화와 가짜 VPN 로그인)(2020-07) (IDI-063)</t>
+          <t>[실제 사고] Twitter 내부 관리 도구 장악(2020-07) (IDI-063)</t>
         </is>
       </c>
       <c r="L64" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: CIS 6.8, NIST AC-6·AC-6(7)·AC-2, ISMS-P 2.5.5·2.5.6</t>
+          <t>역할 기반 접근 통제로 직무별 최소 권한을 정의하고 정기 권한 검토로 누적 권한 회수(CIS 6.8, NIST AC-6·AC-6(7), ISMS-P 2.5.5·2.5.6, CCM IAM-05·IAM-08)</t>
         </is>
       </c>
     </row>
@@ -19632,7 +19776,7 @@
       </c>
       <c r="E65" s="9" t="inlineStr">
         <is>
-          <t>(문구 미작성) Backdoor accounts and additional credentials</t>
+          <t>백도어 계정 생성·앱 자격증명 추가로 비밀번호 재설정 뒤에도 접근 유지</t>
         </is>
       </c>
       <c r="F65" s="13" t="inlineStr">
@@ -19658,12 +19802,12 @@
       </c>
       <c r="K65" s="9" t="inlineStr">
         <is>
-          <t>[실제 사고] SolarWinds 침해 이후 클라우드 장악(Golden SAML·페더레이션 신뢰·앱 자격증명 추가)(2020-12) (IDI-027)</t>
+          <t>[실제 사고] SolarWinds 침해 이후 클라우드 장악(2020-12) (IDI-027)</t>
         </is>
       </c>
       <c r="L65" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: CIS 5.1·5.5, NIST AC-2·AC-2(12)·AU-6, ISMS-P 2.5.1·2.5.6</t>
+          <t>계정·서비스 계정 인벤토리를 유지하고 소유자 없는 계정 비활성화(CIS 5.1·5.5, NIST AC-2, ISMS-P 2.5.1, CCM IAM-03)</t>
         </is>
       </c>
     </row>
@@ -19800,7 +19944,7 @@
       </c>
       <c r="E68" s="9" t="inlineStr">
         <is>
-          <t>(문구 미작성) Disabling audit logs, conditional access and MFA policies</t>
+          <t>감사 로그·조건부 액세스·MFA 정책 변경으로 신원 통제 무력화</t>
         </is>
       </c>
       <c r="F68" s="13" t="inlineStr">
@@ -19831,7 +19975,7 @@
       </c>
       <c r="L68" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: CIS 6.7, NIST AU-9·AU-12·CM-6·SI-4, ISMS-P 2.9.4</t>
+          <t>감사 로그를 관리자도 지울 수 없는 별도 저장소로 보내고 로그 설정 변경 권한 분리(NIST AU-9, ISMS-P 2.9.4)</t>
         </is>
       </c>
     </row>
@@ -28901,13 +29045,28 @@
           <t>과다 권한·권한 상승 경로 악용</t>
         </is>
       </c>
-      <c r="E43" s="9" t="inlineStr"/>
-      <c r="F43" s="26" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Excessive permissions and privilege escalation paths</t>
-        </is>
-      </c>
-      <c r="G43" s="9" t="inlineStr"/>
+      <c r="E43" s="9" t="inlineStr">
+        <is>
+          <t>과다 권한·누적 역할을 타고 탈취 계정에서 관리자 권한으로 확대</t>
+        </is>
+      </c>
+      <c r="F43" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 탈취한 계정에 필요 이상으로 붙은 역할·그룹·내부 도구 권한을 쓰거나 클라우드 역할을 직접 추가해 관리자 수준 권한까지 넓힐 수 있음
+- 수년간 누적된 권한은 실제 업무 범위와 차이가 커도 잘 보이지 않고, 지원·운영 인력 계정 하나가 수많은 고객·사용자 계정 관리로 이어짐</t>
+        </is>
+      </c>
+      <c r="G43" s="9" t="inlineStr">
+        <is>
+          <t>■ 신원 관점
+- 침해 지점: 클라우드 역할·그룹 구성원(T1098.003·T1069.003), 일시 권한 상승 기능(T1548.005), 고객 계정을 다루는 내부 관리·지원 도구
+- 조건: 직무 변경 뒤에도 남는 권한, 지원 인력에게 넓게 열린 관리 도구, 정기 권한 검토 부재 — ATT&amp;CK에 LAPSUS$(G1004)·Scattered Spider(G1015)·Storm-0501(G1053)의 클라우드 관리 역할 추가 절차 수록
+- 연계: 클라우드 CL-PV-01(역할 추가·일시 권한 상승)·CL-DS-01(권한 탐색), AI AI-06-01(에이전트 과도한 권한) — 이미 연결된 OAuth 연동(SAT1001)도 권한 확대 경로가 됨
+■ 실제 사례
+- [실제 사고] Twitter 내부 관리 도구 장악(2020-07): 헬프데스크 사칭으로 얻은 직원 자격증명으로 고객 계정을 관리하는 내부 도구에 접근해 유명인 계정 130개를 장악하고 비트코인 사기 게시물 게시 (IDI-063)
+- [시연] SAT1001 기존 OAuth 연동 악용·SAT1021 링크 백도어: Zapier·Nuclino에서 이미 연결된 연동과 내부 문서 링크로 권한을 넓히는 공개 시연</t>
+        </is>
+      </c>
       <c r="H43" s="9" t="inlineStr">
         <is>
           <t>Excessive permissions and privilege escalation paths</t>
@@ -28920,7 +29079,7 @@
       </c>
       <c r="J43" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="K43" s="8" t="inlineStr">
@@ -29074,7 +29233,16 @@
 2.5.6 접근권한 검토</t>
         </is>
       </c>
-      <c r="AV43" s="9" t="inlineStr"/>
+      <c r="AV43" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 관리 역할·그룹 부여, 일시 권한 상승 요청, 권한 탐색 API 대량 호출을 평소 패턴과 비교해 경보(NIST AC-2)
+- 내부 관리·지원 도구에서 한 직원이 짧은 시간에 여러 고객 계정을 조회·변경하는 패턴 점검
+■ 대응
+- 역할 기반 접근 통제로 직무별 최소 권한을 정의하고 정기 권한 검토로 누적 권한 회수(CIS 6.8, NIST AC-6·AC-6(7), ISMS-P 2.5.5·2.5.6, CCM IAM-05·IAM-08)
+- 고객 계정을 바꿀 수 있는 내부 도구는 승인된 소수에게만 열고, 일시 권한 상승은 기간 제한·승인 기록을 남김</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="9" t="inlineStr">
@@ -29097,13 +29265,28 @@
           <t>특권 접근 관리(PAM)·관리 도구 체계 침해</t>
         </is>
       </c>
-      <c r="E44" s="9" t="inlineStr"/>
-      <c r="F44" s="26" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Compromise of privileged access management and admin tooling</t>
-        </is>
-      </c>
-      <c r="G44" s="9" t="inlineStr"/>
+      <c r="E44" s="9" t="inlineStr">
+        <is>
+          <t>PAM·계정 관리 도구 장악으로 연결된 시스템 관리 권한 일괄 확보</t>
+        </is>
+      </c>
+      <c r="F44" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 특권 접근 관리(PAM) 도구의 관리자 자격증명이나 내부 계정 관리 도구를 손에 넣어 그 도구가 다루는 모든 시스템·계정의 권한을 한 번에 얻을 수 있음
+- 특권 자격증명을 한곳에 모은 도구라 장악 즉시 피해가 조직 전체로 넓어지고, 도구 관리자 계정이 스크립트·공유 폴더에 남아 있는 경우가 많음</t>
+        </is>
+      </c>
+      <c r="G44" s="9" t="inlineStr">
+        <is>
+          <t>■ 신원 관점
+- 침해 지점: PAM 금고·세션 중계 도구의 관리자 계정, 고객 계정을 직접 다루는 내부 계정 관리 도구, 파일 속 관리자 자격증명(T1552.001)·비밀번호 저장소(T1555)
+- 조건: PAM 관리자 자격증명을 자동화 스크립트에 하드코딩, 관리 도구 접근에 전용 단말·별도 MFA 없음, 사람이 관리용 비인간 계정을 직접 사용(NHI10)
+- 연계: 스크립트 속 비밀 노출(IDT-CR-02.1)·인증 쿠키 위조(IDT-TS-03.3)와 이어짐 — ATT&amp;CK에 Scattered Spider(G1015)가 장악 호스트에서 자격증명 보관 문서를 찾는 절차 수록
+■ 실제 사례
+- [실제 사고] Uber 내부망 침해(2022-09): 내부 네트워크 공유의 PowerShell 스크립트에 하드코딩된 PAM 도구 관리자 자격증명으로 AWS·Google Cloud·Slack·보안 도구 등 여러 내부 시스템에 접근 (IDI-002, ATT&amp;CK G1004)
+- [실제 사고] Yahoo 계정 관리 도구 악용과 위조 쿠키로 계정 무단 접근(2017-03): 내부 계정 관리 도구로 관심 대상 계정을 찾고 인증 쿠키를 직접 만들어 최소 6,500개 계정에 무단 접근 (IDI-126)</t>
+        </is>
+      </c>
       <c r="H44" s="9" t="inlineStr">
         <is>
           <t>Compromise of privileged access management and admin tooling</t>
@@ -29116,7 +29299,7 @@
       </c>
       <c r="J44" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="K44" s="8" t="inlineStr"/>
@@ -29250,7 +29433,16 @@
           <t>2.5.5 특수 계정 및 권한 관리</t>
         </is>
       </c>
-      <c r="AV44" s="9" t="inlineStr"/>
+      <c r="AV44" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- PAM 관리자 로그인·정책 변경·금고 대량 조회, 평소와 다른 단말·위치의 관리 도구 접근을 실시간 경보
+- 공유 폴더·스크립트 저장소의 특권 자격증명 스캔, 계정 관리 도구 감사 로그의 비업무 계정 조회 패턴 점검
+■ 대응
+- PAM·관리 도구 관리자는 전용 관리자 계정·전용 단말로 분리하고 피싱 저항 MFA 필수(CIS 5.4·6.5, NIST AC-6(5)·IA-2(1), ISMS-P 2.5.5, CCM IAM-09·IAM-10)
+- 특권 계정 사용 내역 감사와 스크립트 하드코딩 금지, 관리 도구 접근 권한 정기 검토(NIST AC-2(7))</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="9" t="inlineStr">
@@ -29273,13 +29465,28 @@
           <t>백도어 계정 생성·자격증명 추가</t>
         </is>
       </c>
-      <c r="E45" s="9" t="inlineStr"/>
-      <c r="F45" s="26" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Backdoor accounts and additional credentials</t>
-        </is>
-      </c>
-      <c r="G45" s="9" t="inlineStr"/>
+      <c r="E45" s="9" t="inlineStr">
+        <is>
+          <t>백도어 계정 생성·앱 자격증명 추가로 비밀번호 재설정 뒤에도 접근 유지</t>
+        </is>
+      </c>
+      <c r="F45" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 장악한 관리 권한으로 새 관리자 계정을 만들거나 기존 앱·서비스 주체에 자격증명·API 키를 추가해 원래 침투 경로가 막혀도 다시 들어올 수 있음
+- 사용자 비밀번호를 모두 바꿔도 새 계정·앱 자격증명은 그대로 남고, 정상 관리 작업처럼 보여 계정·자격증명 인벤토리 없이는 찾기 어려움</t>
+        </is>
+      </c>
+      <c r="G45" s="9" t="inlineStr">
+        <is>
+          <t>■ 신원 관점
+- 침해 지점: 로컬·도메인·클라우드 계정 생성(T1136.001·T1136.002·T1136.003), 앱·서비스 주체 자격증명 추가(T1098.001), SaaS API 키 발급(SAT1004)
+- 조건: 계정·서비스 계정 인벤토리 부재, 앱 자격증명 추가를 감사하지 않음, 여러 용도로 재사용되는 비인간 신원(NHI9)
+- 연계: ATT&amp;CK에 APT29(G0016)·LAPSUS$(G1004)의 클라우드 계정 생성 절차 수록 — 클라우드 CL-PE-01, AI AI-07-05(에이전트 위장 등록)
+■ 실제 사례
+- [실제 사고] SolarWinds 침해 이후 클라우드 장악(2020-12): 기존 애플리케이션·서비스 주체에 자격증명을 추가해 Microsoft 365 메일 등 클라우드 자원에 지속 접근 (IDI-027, ATT&amp;CK G0016)
+- [시연] SAT1004 API 키: Shortcut에서 탈취 계정에 API 키를 만들어 프로그램 방식 접근을 유지하는 공개 시연</t>
+        </is>
+      </c>
       <c r="H45" s="9" t="inlineStr">
         <is>
           <t>Backdoor accounts and additional credentials</t>
@@ -29292,7 +29499,7 @@
       </c>
       <c r="J45" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="K45" s="8" t="inlineStr"/>
@@ -29448,7 +29655,16 @@
 2.5.6 접근권한 검토</t>
         </is>
       </c>
-      <c r="AV45" s="9" t="inlineStr"/>
+      <c r="AV45" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 새 관리자 계정 생성, 앱·서비스 주체 자격증명·API 키 추가, 업무 시간 외 계정 생성을 고위험 이벤트로 경보(NIST AU-6·AC-2(12))
+- 계정·서비스 계정 인벤토리와 실제 디렉터리·테넌트 계정을 정기 대조해 등록되지 않은 계정 식별
+■ 대응
+- 계정·서비스 계정 인벤토리를 유지하고 소유자 없는 계정 비활성화(CIS 5.1·5.5, NIST AC-2, ISMS-P 2.5.1, CCM IAM-03)
+- 앱 자격증명 추가·관리자 계정 생성 권한을 최소화하고 정기 접근 권한 검토(ISMS-P 2.5.6, CCM IAM-08)</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="9" t="inlineStr">
@@ -29471,13 +29687,34 @@
           <t>MFA 장치·인증 수단 추가 등록</t>
         </is>
       </c>
-      <c r="E46" s="9" t="inlineStr"/>
-      <c r="F46" s="26" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Registering attacker MFA devices and authentication methods</t>
-        </is>
-      </c>
-      <c r="G46" s="9" t="inlineStr"/>
+      <c r="E46" s="9" t="inlineStr">
+        <is>
+          <t>탈취 계정에 공격자 MFA 장치·인증 수단을 등록해 접근 유지</t>
+        </is>
+      </c>
+      <c r="F46" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 피싱·헬프데스크 사칭·MFA 피로로 한 번 얻은 계정에 자기 MFA 장치나 새 인증 수단, 기기를 등록해 이후에는 정상 사용자처럼 인증할 수 있음
+- 등록 뒤에는 MFA가 오히려 공격자 접근을 보증하고, 비밀번호를 바꿔도 등록된 장치·수단을 지우지 않으면 접근이 이어짐</t>
+        </is>
+      </c>
+      <c r="G46" s="9" t="inlineStr">
+        <is>
+          <t>■ 신원 관점
+- 침해 지점: IdP의 MFA 등록·인증 수단 관리(T1556.006), 테넌트 장치 등록(T1098.005), 열린 MFA 자가 등록 절차, 여러 로그인 방식 동시 허용(SAT1017·SAT1002)
+- 조건: 첫 MFA 등록·재등록에 추가 확인 없음, 휴면 계정의 MFA 미등록 방치, 장치 등록 정책 부재 — ATT&amp;CK에 Scattered Spider(G1015)·APT29(G0016) 절차 수록
+- 연계: 헬프데스크 사칭(IDT-SE-02.1)·MFA 피로(IDT-AU-03.1) 다음 단계로 자주 쓰임 — 클라우드 CL-PE-02
+■ 실제 사례
+- [실제 사고] Scattered Spider 합동 권고(2023-11): 헬프데스크에 전화해 MFA를 공격자 장치로 옮기게 하거나 계정을 얻은 뒤 자체 MFA 장치를 등록해 접근 유지 (IDI-008, ATT&amp;CK G1015)
+- [실제 사고] 이란 연계 행위자 무차별 대입·MFA 푸시 폭탄·MFA 장치 등록(2024-10): 탈취 계정에 자기 장치를 MFA로 등록하고 일부는 열린 MFA 등록 절차를 악용 (IDI-093)
+- [실제 사고] 러시아 SVR의 클라우드 초기 접근 수법 변화(2024-02): MFA 피로 공격으로 우회한 뒤 자기 장치를 테넌트에 새 장치로 등록 (IDI-094, ATT&amp;CK G0016)
+- [실제 사고] Retool 고객 계정 27곳 장악(2023-08): 딥페이크 음성 전화로 추가 MFA 코드를 받아 공격자 장치를 Okta에 등록 (IDI-072)
+- [실제 사고] Storm-1167 다단계 AiTM 피싱·BEC(2023-06): AiTM으로 가로챈 계정에 새 MFA 방법을 추가한 뒤 2차 피싱으로 확산 (IDI-030)
+- [실제 사고] Cisco 사내망 침해(2022-08): 음성 피싱과 반복된 MFA 푸시로 VPN에 접속한 뒤 새 MFA 장치를 등록해 접근 유지 (IDI-003)
+- [실제 사고] Storm-2372 디바이스 코드 피싱 캠페인(2025-02): 디바이스 코드로 기기를 등록해 주 리프레시 토큰을 얻는 방식으로 바뀜 (IDI-031)
+- [시연] SAT1017 고스트 로그인: Snowflake·Shortcut·Expensify에서 SSO와 별도로 남는 로그인 방식으로 접근을 유지하는 공개 시연</t>
+        </is>
+      </c>
       <c r="H46" s="9" t="inlineStr">
         <is>
           <t>Registering attacker MFA devices and authentication methods</t>
@@ -29490,7 +29727,7 @@
       </c>
       <c r="J46" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="K46" s="8" t="inlineStr">
@@ -29642,7 +29879,17 @@
           <t>2.5.3 사용자 인증</t>
         </is>
       </c>
-      <c r="AV46" s="9" t="inlineStr"/>
+      <c r="AV46" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 새 MFA 장치·인증 수단·기기 등록을 사용자 알림과 보안팀 경보로 함께 처리하고, 등록 직전의 새 위치 로그인·MFA 피로·재설정과 상관 분석(NIST AU-6)
+- 한 장치·전화번호가 여러 계정에 등록되거나 휴면 계정에 처음 MFA가 등록되는 패턴 점검
+■ 대응
+- MFA 등록·재등록에 기존 강한 인증 수단 확인이나 관리자 승인을 요구하고 등록 가능 위치·장치를 조건부로 제한(NIST IA-5, ISMS-P 2.5.3, CCM IAM-13·IAM-07)
+- 피싱 저항 MFA로 등록 이전 단계의 계정 탈취를 막고 관리자 계정은 하드웨어 키만 허용(CIS 6.3·6.5, NIST IA-2(1))
+- 침해 대응 때 비밀번호와 함께 등록된 MFA 장치·기기·세션을 전수 점검·삭제</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="9" t="inlineStr">
@@ -29665,13 +29912,29 @@
           <t>메일함 규칙·위임·전달 설정 악용</t>
         </is>
       </c>
-      <c r="E47" s="9" t="inlineStr"/>
-      <c r="F47" s="26" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Mailbox rules, delegation and forwarding abuse</t>
-        </is>
-      </c>
-      <c r="G47" s="9" t="inlineStr"/>
+      <c r="E47" s="9" t="inlineStr">
+        <is>
+          <t>메일함 규칙·자동 전달·위임 설정으로 대화 은닉과 메일 지속 수집</t>
+        </is>
+      </c>
+      <c r="F47" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 탈취한 메일함에 받은편지함 규칙·자동 전달·위임 권한을 추가해 보안 경고와 답장을 숨기고 메일을 계속 가로챌 수 있음
+- 사용자가 직접 만들 수 있는 정상 기능이라 보안 도구가 잘 보지 않고, 비밀번호를 바꿔도 규칙·전달·위임 설정은 남음</t>
+        </is>
+      </c>
+      <c r="G47" s="9" t="inlineStr">
+        <is>
+          <t>■ 신원 관점
+- 침해 지점: 받은편지함 규칙·자동 전달(T1114.003), 메일 숨김 규칙(T1564.008), 메일함 위임·사칭 권한(T1098.002), 외부 공유 링크(SAT1022)
+- 조건: 외부 자동 전달 허용, 규칙·위임 변경 감사 부재 — ATT&amp;CK에 Scattered Spider(G1015)가 보안 담당자 메일함에 보안 제품 알림 삭제 규칙을 만든 절차, APT29(G0016)의 사칭 권한 추가 절차 수록
+- 연계: BEC 송금 사기(IDT-IM-01)를 돕는 은닉 단계 — 클라우드 CL-PE-04·CL-ST-01·CL-CO-05
+■ 실제 사례
+- [실제 사고] AiTM 피싱으로 세션 쿠키 탈취 후 BEC(2022-07): 탈취 세션으로 메일함에 들어가 받은편지함 규칙을 만들고 거래처 메일 스레드에 끼어들어 송금 유도 (IDI-029)
+- [실제 사고] Storm-1167 다단계 AiTM 피싱·BEC(2023-06): 탈취 계정에 받은편지함 규칙을 만들어 수백 명에게 2차 피싱을 보내는 BEC로 확산 (IDI-030)
+- [시연] SAT1023 악성 메일 규칙: Office 365 메일 규칙으로 지속성과 은닉을 확보하는 공개 시연</t>
+        </is>
+      </c>
       <c r="H47" s="9" t="inlineStr">
         <is>
           <t>Mailbox rules, delegation and forwarding abuse</t>
@@ -29684,7 +29947,7 @@
       </c>
       <c r="J47" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="K47" s="8" t="inlineStr">
@@ -29818,7 +30081,16 @@
           <t>2.9.5 로그 및 접속기록 점검</t>
         </is>
       </c>
-      <c r="AV47" s="9" t="inlineStr"/>
+      <c r="AV47" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 새 받은편지함 규칙(삭제·이동·외부 전달), 외부 도메인 자동 전달, 메일함 위임·사칭 권한 추가를 실시간 경보(NIST SI-4, CCM LOG-05)
+- 송금·청구서·보안 경고 같은 키워드를 지우거나 옮기는 규칙과 같은 시점의 비정상 로그인 상관 분석(NIST AU-6, ISMS-P 2.9.5)
+■ 대응
+- 조직 외부 자동 전달을 기본 차단하고 예외는 승인제로 운영, 규칙·위임 변경 감사 로그 정기 점검(ISMS-P 2.9.5, CCM LOG-05)
+- 침해 대응 때 비밀번호 재설정과 함께 메일 규칙·전달·위임·연결 앱을 전수 점검·삭제</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="9" t="inlineStr">
@@ -29841,13 +30113,27 @@
           <t>감사 로그·조건부 액세스·MFA 정책 무력화</t>
         </is>
       </c>
-      <c r="E48" s="9" t="inlineStr"/>
-      <c r="F48" s="26" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Disabling audit logs, conditional access and MFA policies</t>
-        </is>
-      </c>
-      <c r="G48" s="9" t="inlineStr"/>
+      <c r="E48" s="9" t="inlineStr">
+        <is>
+          <t>감사 로그·조건부 액세스·MFA 정책 변경으로 신원 통제 무력화</t>
+        </is>
+      </c>
+      <c r="F48" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 관리 권한을 얻은 뒤 클라우드 감사 로그를 끄거나 조건부 액세스에 신뢰 위치를 추가하고 MFA 설정을 해제해 이후 활동이 탐지·차단되지 않게 할 수 있음
+- 직접 피해를 내지 않아 사고 경위에서 잘 드러나지 않고, 로그가 꺼진 기간의 활동은 사후 조사로도 복원하기 어려움</t>
+        </is>
+      </c>
+      <c r="G48" s="9" t="inlineStr">
+        <is>
+          <t>■ 신원 관점
+- 침해 지점: 조건부 액세스 정책(T1556.009), 클라우드 감사 로그 설정(T1685.002), 사용자·원격 접속 장비의 MFA 설정(T1556.006)
+- 근거: ATT&amp;CK에 Scattered Spider(G1015)의 조건부 액세스 신뢰 위치 추가, APT29(G0016)의 메일 탈취 전 감사 로그 비활성화, Storm-0501(G1053)의 조건부 액세스 우회, 2025 폴란드 와이퍼 공격(C0063)의 2단계 인증 설정 해제 절차 수록
+- 연계: 테넌트 신뢰 설정 변조(IDT-DI-03.2)·MFA 장치 추가 등록(IDT-PE-02.2)과 함께 쓰임 — 클라우드 CL-PE-02·CL-DI-01, OT OT-EV-03
+■ 실제 사례
+- 공개 사고 미확인 — 이 DB의 사고 경위에는 정책·로그 무력화가 별도 단계로 명시된 사례가 없어 ATT&amp;CK 절차로만 근거를 둠(발생가능성 '중')</t>
+        </is>
+      </c>
       <c r="H48" s="9" t="inlineStr">
         <is>
           <t>Disabling audit logs, conditional access and MFA policies</t>
@@ -29860,7 +30146,7 @@
       </c>
       <c r="J48" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="K48" s="8" t="inlineStr"/>
@@ -29995,7 +30281,16 @@
           <t>2.9.4 로그 및 접속기록 관리</t>
         </is>
       </c>
-      <c r="AV48" s="9" t="inlineStr"/>
+      <c r="AV48" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 감사 로그 비활성화·보존 기간 단축, 조건부 액세스 정책·신뢰 위치 변경, MFA 해제를 별도 채널로 즉시 경보(NIST SI-4·AU-12, CCM LOG-03)
+- 로그 수집이 끊긴 구간을 수집 파이프라인에서 감지하고 정책 변경 직후의 관리자 활동과 상관 분석
+■ 대응
+- 감사 로그를 관리자도 지울 수 없는 별도 저장소로 보내고 로그 설정 변경 권한 분리(NIST AU-9, ISMS-P 2.9.4)
+- 조건부 액세스·MFA 정책을 기준선으로 관리해 변경 시 이중 승인과 정기 대조(CIS 6.7, NIST CM-6, CCM IAM-13)</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="9" t="inlineStr">
@@ -30018,13 +30313,35 @@
           <t>장기 액세스 키·API 키·토큰 악용</t>
         </is>
       </c>
-      <c r="E49" s="9" t="inlineStr"/>
-      <c r="F49" s="26" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Abuse of long-lived access keys, API keys and tokens</t>
-        </is>
-      </c>
-      <c r="G49" s="9" t="inlineStr"/>
+      <c r="E49" s="9" t="inlineStr">
+        <is>
+          <t>MFA 없는 장기 액세스 키·API 키 하나로 고객 데이터·인프라 접근</t>
+        </is>
+      </c>
+      <c r="F49" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 코드·설정·연동 시스템에서 새거나 탈취한 장기 액세스 키·API 키·토큰으로 MFA 없이 클라우드·SaaS·원격 지원 인프라에 바로 접근할 수 있음
+- 키에 붙은 권한이 넓고 만료가 없어 한 번 새면 오래 쓰이며, 사람 로그인이 아니라 이상 로그인 탐지·MFA가 적용되지 않음</t>
+        </is>
+      </c>
+      <c r="G49" s="9" t="inlineStr">
+        <is>
+          <t>■ 신원 관점
+- 침해 지점: 클라우드 액세스 키·SaaS API 키·개인 접근 토큰(T1550.001·T1078.004), 파일·저장소 속 키(T1552.001), 원격 지원 SaaS 인프라 키, 블록체인 검증자 서명 키
+- 조건: 만료 없는 장기 비밀(NHI7), 조직 전체 권한을 가진 과다 권한 키(NHI5), 코드·이미지·공개 저장소로 새어 나간 비밀(NHI2)
+- 연계: 노출(IDT-CR-02.1)에서 시작해 교체 실패(IDT-NH-01.2)로 길어짐 — 클라우드 CL-IA-07·CL-CA-05, AI AI-07-01·AI-07-02, 공급망 SCT-SC-02.3
+■ 실제 사례
+- [실제 사고] BeyondTrust 원격 지원 SaaS API 키 탈취로 미 재무부 등 고객 17곳 침해(2024-12): 인프라 API 키로 고객 인스턴스의 로컬 애플리케이션 비밀번호를 재설정해 미 재무부 단말에 원격 접근 (IDI-084)
+- [실제 사고] OneLogin 미국 데이터센터 고객 데이터 침해(2017-05): 탈취한 AWS 키로 IdP 서비스 클라우드에 인스턴스를 만들어 약 7시간 정찰하고 사용자·앱·키 정보 DB에 접근 (IDI-081)
+- [실제 사고] Ronin 브리지 6억 달러대 탈취(2022-03): 검증자 키 9개 중 5개를 확보해 약 6억 달러 상당 암호화폐를 인출 (IDI-113, ATT&amp;CK G0032)
+- [실제 사고] New York Times 소스 코드 270GB 유출(2024-01): 노출된 GitHub 토큰으로 조직 전체 저장소에 접근해 약 270GB를 빼내 공개 (IDI-108)
+- [실제 사고] Storm-2139 — 노출된 고객 API 키로 생성형 AI 서비스 탈취·재판매(2025-02): 공개된 곳에서 수집한 API 키로 생성형 AI 서비스에 접근하고 접근권을 재판매 (IDI-115)
+- [실제 사고] Sisense 침해(2024-04): 고객 데이터 원천 접속용 자격증명·토큰·인증서가 노출되어 CISA가 고객에게 관련 자격증명 전부 교체를 권고 (IDI-039)
+- [실증] Microsoft AI 연구조직 과다 권한 SAS 토큰 노출(2023-06): 저장소 계정 전체에 권한을 주는 토큰 링크로 직원 단말 백업·비밀·키 등 38TB가 노출 (IDI-123)
+- [공개 취약점] 원격 지원 제품 명령 주입(CVE-2024-12356) — KEV 판정 1건, 원격 지원 SaaS API 키 탈취 사건 조사 중 발견
+- [시연] SAT1005 API 비밀 탈취: Postman에서 연동용으로 저장한 API 키를 다시 읽어 내는 공개 시연</t>
+        </is>
+      </c>
       <c r="H49" s="9" t="inlineStr">
         <is>
           <t>Abuse of long-lived access keys, API keys and tokens</t>
@@ -30037,7 +30354,7 @@
       </c>
       <c r="J49" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="K49" s="8" t="inlineStr"/>
@@ -30199,7 +30516,16 @@
 2.7.2 암호키 관리</t>
         </is>
       </c>
-      <c r="AV49" s="9" t="inlineStr"/>
+      <c r="AV49" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 키·토큰별 사용 출발지·호출 API·시간대 기준선을 두고 처음 보는 IP·국가·대량 조회를 경보, 노출이 확인되면 노출 시점 이후 사용 이력 조회
+- 저장소·이미지·공개 코드 사이트의 키 패턴 스캔, 공급업체 침해 공지 때 해당 연동 키 사용 내역 즉시 점검
+■ 대응
+- 장기 키를 단기 토큰·워크로드 신원으로 대체하고 남는 키는 권한 최소화·만료 설정·정기 교체(CIS 5.5, NIST IA-5(13)·AC-6·SC-12, ISMS-P 2.5.5·2.7.2, CCM IAM-14·IAM-05·CEK-12)
+- 서비스 간 인증에 출발지 제한·상호 인증을 더하고 비인간 신원 인벤토리로 소유자·용도 관리(NIST IA-9)</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="9" t="inlineStr">
@@ -30222,13 +30548,33 @@
           <t>비밀·자격증명 교체·폐기 실패</t>
         </is>
       </c>
-      <c r="E50" s="9" t="inlineStr"/>
-      <c r="F50" s="26" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Failure to rotate or revoke secrets and credentials</t>
-        </is>
-      </c>
-      <c r="G50" s="9" t="inlineStr"/>
+      <c r="E50" s="9" t="inlineStr">
+        <is>
+          <t>샌 비밀·퇴사자 키를 교체·폐기하지 않아 침해 뒤에도 재침투 허용</t>
+        </is>
+      </c>
+      <c r="F50" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 이미 유출됐거나 침해 대응에서 빠진 토큰·서비스 계정 비밀번호·서명 키가 계속 유효한 점을 이용해 대응이 끝난 뒤에도 다시 접근할 수 있음
+- 어떤 비밀이 어디에 쓰이는지 모르면 교체 대상을 빠뜨리기 쉽고, 퇴사자·협력사가 쓰던 키나 수년 전 유출된 비밀번호가 사고의 시작점이 됨</t>
+        </is>
+      </c>
+      <c r="G50" s="9" t="inlineStr">
+        <is>
+          <t>■ 신원 관점
+- 침해 지점: 침해 대응 뒤 남은 서비스 토큰·API 토큰(T1550.001), 오랫동안 바뀌지 않은 서버·클라우드 계정 비밀번호(T1078.004), 퇴사자가 알던 토큰 서명 키·위임 서명 권한
+- 조건: 비밀 인벤토리·소유자 부재로 교체 범위 산정 실패, 만료 없는 장기 비밀(NHI7), 퇴사·계약 종료 때 비인간 신원 회수 누락(NHI1)
+- 연계: 장기 키 악용(IDT-NH-01.1)·퇴사자 권한 미회수(IDT-LC-01.1)와 겹침 — 공급망 SCT-SC-02.3
+■ 실제 사례
+- [실제 사고] 쿠팡 고객 계정 정보 3,367만 건 유출(2025-11): 퇴사자가 쓰던 토큰 서명키를 갱신하지 않고 키 발급 이력도 관리하지 않아 퇴사 개발자가 약 8개월간 고객 정보를 조회 (IDI-042)
+- [실제 사고] SK텔레콤 유심 정보 2,696만 건 유출(2025-04): 시스템 관리망 서버 계정 비밀번호를 바꾸지 않고 만료일도 두지 않는 등 계정 관리 부실이 지적됨 (IDI-040)
+- [실제 사고] Cloudflare 내부 Atlassian 침해(2023-11): Okta 침해 때 유출된 것 가운데 쓰지 않는다고 잘못 판단해 교체하지 않은 서비스 토큰 1개와 서비스 계정 자격증명 3개로 침투 (IDI-020)
+- [실제 사고] Internet Archive 연쇄 침해(2024-10): 침해 뒤에도 교체하지 않은 Zendesk API 토큰으로 다시 들어가 지원 요청 첨부 신분증 등에 접근 (IDI-109)
+- [실제 사고] Snowflake 고객 인스턴스 대량 데이터 탈취(2024-05): 쓰인 고객 자격증명 일부가 2020년 유출 이후 교체되지 않은 상태 (IDI-016)
+- [실제 사고] HELLCAT 인포스틸러 유출 Jira 자격증명으로 연쇄 침해(2025-03): 협력사 직원 단말에서 2021년에 유출된 자격증명이 여전히 유효 (IDI-069)
+- [실제 사고] Ronin 브리지 6억 달러대 탈취(2022-03): 일시적 부하 대응을 위해 위임한 서명 권한을 회수하지 않아 다섯 번째 검증자 키로 쓰임 (IDI-113, ATT&amp;CK G0032)</t>
+        </is>
+      </c>
       <c r="H50" s="9" t="inlineStr">
         <is>
           <t>Failure to rotate or revoke secrets and credentials</t>
@@ -30241,7 +30587,7 @@
       </c>
       <c r="J50" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="K50" s="8" t="inlineStr"/>
@@ -30389,7 +30735,16 @@
 2.7.2 암호키 관리</t>
         </is>
       </c>
-      <c r="AV50" s="9" t="inlineStr"/>
+      <c r="AV50" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 침해 공지·유출 확인 이후에도 쓰이는 토큰·키를 식별하고 교체 완료 여부를 실제 사용 로그로 검증
+- 퇴사·계약 종료 인력과 연결된 키·토큰의 사용, 오랫동안 바뀌지 않은 서비스 계정 비밀번호를 정기 점검
+■ 대응
+- 비밀 인벤토리에 소유자·용도·만료일을 기록하고 정기 교체·자동 만료 적용(CIS 5.5, NIST IA-5·IA-5(13), ISMS-P 2.7.2, CCM CEK-12)
+- 침해 대응·퇴사 때 관련 비밀·서명 키를 전수 폐기·재발급하고 계정 비활성화(CIS 6.2, NIST AC-2(3), ISMS-P 2.5.1, CCM CEK-13·IAM-07)</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="9" t="inlineStr">
@@ -30412,13 +30767,30 @@
           <t>서비스 계정 악용·사람의 비인간 신원 사용</t>
         </is>
       </c>
-      <c r="E51" s="9" t="inlineStr"/>
-      <c r="F51" s="26" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Service account abuse and human use of NHIs</t>
-        </is>
-      </c>
-      <c r="G51" s="9" t="inlineStr"/>
+      <c r="E51" s="9" t="inlineStr">
+        <is>
+          <t>MFA 예외인 고권한 서비스 계정 탈취로 고객 DB·지원 시스템 장악</t>
+        </is>
+      </c>
+      <c r="F51" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 MFA가 없고 권한이 넓은 서비스 계정이나 사람이 대화형으로 쓰는 시스템 계정을 탈취해 고객 DB·지원 시스템·클라우드 관리 기능에 접근할 수 있음
+- 서비스 계정은 자동화 때문에 MFA·로그인 제한에서 빠지는 경우가 많고, 사람이 개인 브라우저에 그 자격증명을 저장하면 회사 통제 밖에서 털림</t>
+        </is>
+      </c>
+      <c r="G51" s="9" t="inlineStr">
+        <is>
+          <t>■ 신원 관점
+- 침해 지점: 도메인·클라우드 서비스 계정(T1078.002·T1078.004), 자동 구성 도구·동기화 서버의 고권한 계정, 지원 시스템 서비스 계정
+- 조건: 사람이 서비스 계정에 직접 로그인해 사용(NHI10), 한 계정을 여러 시스템에 재사용(NHI9), 전역 관리자급 과다 권한(NHI5)
+- 연계: 동기화 서버 장악(IDT-DI-02)·IdP 공급업체 침해(IDT-DI-03.1)의 핵심 고리 — ATT&amp;CK에 APT29(G0016)·Storm-0501(G1053) 절차 수록
+■ 실제 사례
+- [실제 사고] Dropbox Sign 고객 DB 침해(2024-04): 자동 시스템 구성 도구에 접근해 백엔드의 높은 권한을 가진 서비스 계정으로 고객 DB에 들어가 전 사용자의 이메일·사용자 이름 등이 노출 (IDI-038)
+- [실제 사고] Okta 지원 시스템 침해(2023-10): 직원이 개인 Google 계정에 저장한 지원 시스템 서비스 계정 자격증명이 탈취되어 고객 134곳에 영향 (IDI-019)
+- [실제 사고] Storm-0501 하이브리드 환경 랜섬웨어(2024-09): 전역 관리자 역할이 붙은 동기화 비인간 계정을 장악해 데이터 반출·삭제와 백업 파괴 뒤 갈취 (IDI-022, ATT&amp;CK G1053)
+- [실제 사고] 러시아 SVR의 클라우드 초기 접근 수법 변화(2024-02): 비밀번호 스프레이·대입으로 시스템 계정과 휴면 계정을 탈취 (IDI-094, ATT&amp;CK G0016)</t>
+        </is>
+      </c>
       <c r="H51" s="9" t="inlineStr">
         <is>
           <t>Service account abuse and human use of NHIs</t>
@@ -30431,7 +30803,7 @@
       </c>
       <c r="J51" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="K51" s="8" t="inlineStr"/>
@@ -30571,7 +30943,16 @@
 2.5.5 특수 계정 및 권한 관리</t>
         </is>
       </c>
-      <c r="AV51" s="9" t="inlineStr"/>
+      <c r="AV51" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 서비스 계정의 대화형 로그인, 평소와 다른 출발지·시간대, 정해진 작업 밖의 API 호출을 경보
+- 서비스 계정 인벤토리에 없는 계정 사용, 한 서비스 계정이 여러 시스템에서 동시에 쓰이는 패턴 점검
+■ 대응
+- 서비스 계정 인벤토리로 소유자·용도·권한을 관리하고 대화형 로그인 금지·출발지 제한(CIS 5.5, NIST IA-9·AC-2, ISMS-P 2.5.1, CCM IAM-03)
+- 서비스 계정 권한을 작업 범위로 줄이고 관리자급 서비스 계정은 특권 계정으로 분리 관리(CIS 5.4, NIST AC-6, ISMS-P 2.5.5, CCM IAM-05)</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="9" t="inlineStr">
@@ -30594,13 +30975,27 @@
           <t>워크로드 ID 과다 권한·신뢰 설정 오류</t>
         </is>
       </c>
-      <c r="E52" s="9" t="inlineStr"/>
-      <c r="F52" s="26" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Overprivileged workload identities and trust misconfiguration</t>
-        </is>
-      </c>
-      <c r="G52" s="9" t="inlineStr"/>
+      <c r="E52" s="9" t="inlineStr">
+        <is>
+          <t>과다 권한 워크로드 역할·느슨한 신뢰 설정으로 클라우드 데이터 대량 접근</t>
+        </is>
+      </c>
+      <c r="F52" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 웹 서비스·CI 작업 같은 워크로드에서 메타데이터 서비스나 OIDC 신뢰로 역할 자격증명을 얻어, 그 역할에 붙은 넓은 권한으로 저장소·데이터에 접근할 수 있음
+- 워크로드 역할은 사람이 보지 않는 곳에서 자동으로 발급되고, 권한이 과다하면 애플리케이션 결함 하나가 대량 유출로 직결됨</t>
+        </is>
+      </c>
+      <c r="G52" s="9" t="inlineStr">
+        <is>
+          <t>■ 신원 관점
+- 침해 지점: 인스턴스 메타데이터 서비스의 역할 자격증명(T1552.005), 워크로드 역할·클라우드 계정(T1078.004), CI/CD의 OIDC 신뢰 조건
+- 조건: 실제 필요보다 넓은 역할 권한(NHI5), 메타데이터 서비스 보호 미적용 같은 배포 구성 결함(NHI6), 개발·운영 환경의 신원 혼용(NHI8)
+- 연계: 클라우드 CL-CA-06(메타데이터 경유 자격증명 탈취)·CL-PV-01, 공급망 SCT-SC-02.2(OIDC 신뢰 게시 자격 탈취)
+■ 실제 사례
+- [실제 사고] Capital One 1억 600만 명 정보 유출(2019-07): 웹 방화벽 SSRF로 메타데이터 서비스에서 얻은 역할 자격증명에 고객 데이터 버킷 조회 권한까지 붙어 있어 약 1억 600만 명 정보 유출 (IDI-112)</t>
+        </is>
+      </c>
       <c r="H52" s="9" t="inlineStr">
         <is>
           <t>Overprivileged workload identities and trust misconfiguration</t>
@@ -30613,7 +31008,7 @@
       </c>
       <c r="J52" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="K52" s="8" t="inlineStr"/>
@@ -30757,7 +31152,16 @@
           <t>2.5.5 특수 계정 및 권한 관리</t>
         </is>
       </c>
-      <c r="AV52" s="9" t="inlineStr"/>
+      <c r="AV52" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 워크로드 역할 자격증명이 해당 인스턴스·작업 밖에서 쓰이는 경우, 평소와 다른 저장소 나열·대량 조회를 경보
+- OIDC 신뢰 정책의 조건(저장소·브랜치·환경) 누락과 와일드카드를 정기 점검
+■ 대응
+- 워크로드 역할을 작업별 최소 권한으로 나누고 데이터 접근은 별도 역할로 분리(CIS 6.8, NIST AC-6, ISMS-P 2.5.5, CCM IAM-05·IAM-15)
+- 메타데이터 서비스 보호 기능 적용과 신뢰 정책 기준선 관리(NIST CM-6·IA-9)</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="9" t="inlineStr">
@@ -30780,13 +31184,29 @@
           <t>SaaS 연동 앱 토큰 탈취와 연쇄 접근</t>
         </is>
       </c>
-      <c r="E53" s="9" t="inlineStr"/>
-      <c r="F53" s="26" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Theft of SaaS integration tokens and chained access</t>
-        </is>
-      </c>
-      <c r="G53" s="9" t="inlineStr"/>
+      <c r="E53" s="9" t="inlineStr">
+        <is>
+          <t>SaaS 연동 공급자의 OAuth 토큰 탈취로 여러 고객 조직 데이터 연쇄 접근</t>
+        </is>
+      </c>
+      <c r="F53" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 SaaS 연동 앱 공급자가 보관한 OAuth·리프레시 토큰을 탈취해 그 앱을 연결한 여러 조직의 SaaS·코드 저장소에 사용자 로그인 없이 접근할 수 있음
+- 토큰은 피해 조직의 MFA·로그인 정책을 거치지 않고, 연동 앱의 정상 API 호출처럼 보여 공급자 공지 전까지 알기 어려움</t>
+        </is>
+      </c>
+      <c r="G53" s="9" t="inlineStr">
+        <is>
+          <t>■ 신원 관점
+- 침해 지점: 연동 공급자가 보관한 OAuth 액세스·리프레시 토큰(T1528·T1550.001), 테넌트 단위 시스템 연동(SAT1036), 연동 공급자와의 신뢰 관계(T1199)
+- 조건: 취약한 서드파티 비인간 신원(NHI3), 수명이 긴 리프레시 토큰(NHI7), 연동 앱에 필요 이상 범위의 권한 승인
+- 연계: 공급업체 경유 연쇄 탈취(IDT-IM-05)로 번짐 — 클라우드 CL-PE-03·CL-IA-06, AI AI-07-02, 공급망 SCT-CS-03.1
+■ 실제 사례
+- [실제 사고] Salesloft Drift 연동 OAuth 토큰 탈취로 Salesforce 인스턴스 대량 데이터 반출(2025-08): 연동용 OAuth·리프레시 토큰으로 여러 조직의 Salesforce 데이터를 반출하고 그 안의 AWS 키·Snowflake 토큰 등 자격증명을 찾아냄 (IDI-037)
+- [실제 사고] Heroku·Travis CI 발급 GitHub OAuth 토큰 탈취로 비공개 저장소 반출(2022-04): 연동 서비스에 발급된 GitHub OAuth 사용자 토큰으로 npm 등 수십 개 조직의 비공개 저장소를 복제 (IDI-106)
+- [시연] SAT1027 OAuth 토큰·SAT1036 시스템 연동: Microsoft Graph Explorer·Slack에서 임의 권한 토큰과 테넌트 단위 연동으로 장기 접근을 유지하는 공개 시연</t>
+        </is>
+      </c>
       <c r="H53" s="9" t="inlineStr">
         <is>
           <t>Theft of SaaS integration tokens and chained access</t>
@@ -30799,7 +31219,7 @@
       </c>
       <c r="J53" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="K53" s="8" t="inlineStr"/>
@@ -30962,7 +31382,16 @@
 2.5.5 특수 계정 및 권한 관리</t>
         </is>
       </c>
-      <c r="AV53" s="9" t="inlineStr"/>
+      <c r="AV53" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 연동 앱 토큰의 평소와 다른 출발지 IP·대량 조회·내보내기 API 호출을 경보, 연동 공급자 침해 공지 즉시 해당 앱 토큰 사용 이력 점검
+- 승인된 연동 앱 목록과 실제 토큰 발급 현황을 정기 대조
+■ 대응
+- 연동 앱 승인은 관리자 검토로 제한하고 권한 범위·토큰 수명 최소화, 미사용 연동 정기 정리(CIS 6.6, NIST AC-6, ISMS-P 2.5.5, CCM IAM-14)
+- 연동 공급자를 공급망으로 관리해 보안 요구 사항·침해 통지 의무를 계약에 넣고, 침해 시 토큰 전수 폐기 절차 준비(NIST SA-9·IA-9, ISMS-P 2.3.3, CCM STA-09)</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="9" t="inlineStr">
@@ -30985,13 +31414,31 @@
           <t>악성·과다 권한 OAuth 앱 등록·권한 부여</t>
         </is>
       </c>
-      <c r="E54" s="9" t="inlineStr"/>
-      <c r="F54" s="26" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Malicious or overprivileged OAuth app registration and grants</t>
-        </is>
-      </c>
-      <c r="G54" s="9" t="inlineStr"/>
+      <c r="E54" s="9" t="inlineStr">
+        <is>
+          <t>악성·과다 권한 OAuth 앱으로 사용자 MFA와 무관한 조직 데이터 지속 접근</t>
+        </is>
+      </c>
+      <c r="F54" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 탈취한 계정·관리 권한으로 OAuth 앱을 새로 만들거나 기존 앱에 높은 권한과 자격증명을 붙여 조직 전체 메일함·SaaS 데이터에 앱 명의로 접근할 수 있음
+- 앱 권한은 사용자 비밀번호·MFA 변경과 무관하게 유지되고, 정상 연동 앱처럼 보여 승인된 앱 목록을 따로 검토하지 않으면 드러나지 않음</t>
+        </is>
+      </c>
+      <c r="G54" s="9" t="inlineStr">
+        <is>
+          <t>■ 신원 관점
+- 침해 지점: 클라우드 앱 통합(T1671), 앱·서비스 주체에 추가된 역할(T1098.003)·자격증명(T1098.001), 변조된 연결 앱, 정상 앱을 흉내 낸 연동(SAT1016)
+- 조건: 사용자 동의만으로 앱 등록·승인 가능, 레거시·테스트 앱의 과다 권한 방치(NHI5), 앱 권한 정기 검토 부재
+- 연계: 동의 피싱(IDT-SE-01.2)·IT 지원 사칭(IDT-SE-02.2) 다음 단계 — 클라우드 CL-PE-03, ATT&amp;CK에 LAPSUS$(G1004)·Scattered Spider(G1015)의 클라우드 역할 추가 절차 수록
+■ 실제 사례
+- [실제 사고] Microsoft 기업 메일 침해(2024-01): 레거시 테스트 OAuth 앱의 높은 권한으로 악성 앱을 추가로 만들고 전체 메일함 접근 역할을 받아 고위 경영진·보안팀 메일 열람 (IDI-017, ATT&amp;CK G0016)
+- [실제 사고] Salesforce 대상 음성 피싱(2025-06): IT 지원 사칭 전화로 직원이 변조된 Data Loader 연결 앱을 승인하게 해 조직 데이터를 API로 대량 반출·갈취 (IDI-036, ATT&amp;CK G1057)
+- [실제 사고] OAuth 앱 악용 금전 공격(2023-12): MFA 없는 탈취 계정으로 OAuth 앱을 만들거나 권한을 높여 암호화폐 채굴·BEC·스팸 발송에 사용 (IDI-034)
+- [실제 사고] SolarWinds 침해 이후 클라우드 장악(2020-12): 기존 애플리케이션·서비스 주체에 자격증명을 추가해 클라우드 자원에 지속 접근 (IDI-027, ATT&amp;CK C0024)
+- [시연] SAT1016 이블 트윈 연동·SAT1033 섀도 워크플로: HubSpot·Zapier에서 정상 앱처럼 보이는 연동과 자동화 워크플로로 접근을 유지하고 데이터를 빼내는 공개 시연</t>
+        </is>
+      </c>
       <c r="H54" s="9" t="inlineStr">
         <is>
           <t>Malicious or overprivileged OAuth app registration and grants</t>
@@ -31004,7 +31451,7 @@
       </c>
       <c r="J54" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="K54" s="8" t="inlineStr"/>
@@ -31157,7 +31604,16 @@
 2.5.6 접근권한 검토</t>
         </is>
       </c>
-      <c r="AV54" s="9" t="inlineStr"/>
+      <c r="AV54" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 새 OAuth 앱 등록·고위험 권한 승인, 앱·서비스 주체에 역할·자격증명 추가를 실시간 경보(NIST AU-6)
+- 전체 메일함 접근 같은 테넌트 단위 권한을 가진 앱 목록을 정기 추출해 게시자·소유자 확인
+■ 대응
+- 앱 등록·동의를 관리자 승인으로 제한하고 검증된 게시자 앱만 허용(CIS 6.7, CCM IAM-15)
+- 앱 권한을 최소화하고 레거시·테스트 앱까지 포함해 정기 권한 검토·미사용 앱 삭제(CIS 6.8, NIST AC-6·AC-2, ISMS-P 2.5.5·2.5.6, CCM IAM-08)</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="9" t="inlineStr">
@@ -31180,13 +31636,28 @@
           <t>AI 에이전트 신원·위임 권한 악용</t>
         </is>
       </c>
-      <c r="E55" s="9" t="inlineStr"/>
-      <c r="F55" s="26" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Abuse of AI agent identity and delegated authority</t>
-        </is>
-      </c>
-      <c r="G55" s="9" t="inlineStr"/>
+      <c r="E55" s="9" t="inlineStr">
+        <is>
+          <t>AI 에이전트가 위임받은 사용자 토큰·연동 권한으로 데이터 노출</t>
+        </is>
+      </c>
+      <c r="F55" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 AI 에이전트가 사용자에게서 위임받은 토큰·연동 권한을 프롬프트 인젝션으로 조종하거나 연동 서버의 권한 격리 결함을 이용해 다른 저장소·조직의 데이터를 가져갈 수 있음
+- 에이전트는 사용자 권한 전체를 위임받는 경우가 많아 피해 범위가 그 권한에 좌우되고, 정상 도구 호출처럼 보여 기존 로그로 구분하기 어려움</t>
+        </is>
+      </c>
+      <c r="G55" s="9" t="inlineStr">
+        <is>
+          <t>■ 신원 관점
+- 침해 지점: 에이전트에 위임된 사용자 토큰(T1550.001)과 연동 토큰 발급(T1528), MCP 서버 등 에이전트 연동 계층의 조직 간 권한 격리
+- 조건: 작업에 필요한 범위보다 넓은 위임(NHI5), 에이전트 연동의 인증·환경 격리 미흡(NHI4·NHI8), 외부 콘텐츠를 읽는 에이전트에 쓰기 권한까지 위임
+- 연계: AI AI-07-01·AI-07-03(혼동된 대리인)·AI-07-05·AI-06-01, 공급망 SCT-DE-03.2(MCP 서버 오염·사칭) — 프롬프트·도구 호출 경로는 AI 매트릭스에서 다룸
+■ 실제 사례
+- [실제 사고] Asana MCP 서버 조직 간 데이터 노출(2025-06): AI 에이전트 연동용 MCP 서버의 논리 결함으로 다른 조직의 작업·프로젝트·파일 정보가 보이는 상태가 되어 약 1천 고객이 노출 대상 (IDI-117)
+- [실증] GitHub MCP 서버 프롬프트 인젝션으로 에이전트가 비공개 저장소 유출(2025-05): 공개 저장소 이슈에 숨긴 지시로 에이전트가 사용자 토큰 권한으로 비공개 저장소 내용을 공개 PR로 올리도록 조종 (IDI-122)</t>
+        </is>
+      </c>
       <c r="H55" s="9" t="inlineStr">
         <is>
           <t>Abuse of AI agent identity and delegated authority</t>
@@ -31199,7 +31670,7 @@
       </c>
       <c r="J55" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="K55" s="8" t="inlineStr"/>
@@ -31350,7 +31821,16 @@
           <t>2.5.5 특수 계정 및 권한 관리</t>
         </is>
       </c>
-      <c r="AV55" s="9" t="inlineStr"/>
+      <c r="AV55" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 에이전트용 토큰·연동 계정의 호출 범위·대상 저장소·조직을 기준선과 비교해 평소와 다른 접근 경보
+- 에이전트 도구 호출 기록을 사용자 세션 로그와 구분해 남기고, 외부 콘텐츠 처리 직후의 쓰기·공개 작업 점검
+■ 대응
+- 에이전트 전용 신원을 두고 작업별 최소 범위·짧은 수명의 토큰만 위임(CIS 6.8, NIST AC-6·IA-9, ISMS-P 2.5.5, CCM IAM-05)
+- 연동 서버의 조직·테넌트 간 접근 통제를 검증하고 고위험 작업은 사람 승인 뒤 실행(NIST AC-3, CCM IAM-15)</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="9" t="inlineStr">
@@ -31373,13 +31853,31 @@
           <t>퇴사자·휴면·미사용 계정과 권한 미회수</t>
         </is>
       </c>
-      <c r="E56" s="9" t="inlineStr"/>
-      <c r="F56" s="26" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Orphaned, dormant and unrevoked accounts</t>
-        </is>
-      </c>
-      <c r="G56" s="9" t="inlineStr"/>
+      <c r="E56" s="9" t="inlineStr">
+        <is>
+          <t>퇴사자·휴면·미사용 계정과 회수되지 않은 권한으로 침투·무단 조회</t>
+        </is>
+      </c>
+      <c r="F56" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자나 퇴사자는 쓰지 않지만 활성 상태로 남은 VPN·메인테이너·클라우드 계정이나 퇴사 뒤에도 회수되지 않은 권한·키로 정상 사용자처럼 들어올 수 있음
+- 주인이 없는 계정은 이상 행위를 알아챌 사람이 없어 탐지가 늦고, MFA 없이 남은 오래된 비밀번호는 유출 비밀번호 하나로 열림</t>
+        </is>
+      </c>
+      <c r="G56" s="9" t="inlineStr">
+        <is>
+          <t>■ 신원 관점
+- 대상: 쓰지 않는 VPN·원격 접속 계정, 휴면 패키지 메인테이너 계정, 퇴사자·전보자의 SaaS·보고서 접근 권한과 비인간 신원(T1078·T1078.002)
+- 조건: 인사 시스템과 계정 관리가 연동되지 않아 퇴사·전보 때 회수 누락, 휴면 계정 자동 비활성화 부재, 퇴사자가 알던 키·토큰 미폐기(NHI1)
+- 연계: ATT&amp;CK에 APT29(G0016)가 퇴사자 등의 휴면 계정을 노린 절차 수록 — 비밀 교체 실패(IDT-NH-01.2)·내부자 오남용(IDT-LC-02.1)과 이어짐
+■ 실제 사례
+- [실제 사고] Colonial Pipeline 랜섬웨어(2021-05): 쓰지 않지만 활성 상태로 남은 레거시 VPN 계정이 비밀번호 하나로만 보호되어 침투 경로가 되고 송유관 운영 중단으로 이어짐 (IDI-014)
+- [실제 사고] 쿠팡 고객 계정 정보 3,367만 건 유출(2025-11): 퇴사한 백엔드 개발자가 재직 중 확보한 토큰 서명키로 정상 로그인 없이 약 8개월간 고객 정보를 조회 (IDI-042)
+- [실제 사고] Cash App 퇴사자의 고객 보고서 무단 다운로드(2022-04): 퇴사 뒤에도 고객 보고서를 내려받을 수 있었던 전 직원이 고객 820만 명의 정보를 내려받음 (IDI-103)
+- [실제 사고] 러시아 SVR의 클라우드 초기 접근 수법 변화(2024-02): 비밀번호 스프레이·대입으로 퇴사자 등의 휴면 계정을 탈취 (IDI-094, ATT&amp;CK G0016)
+- [실제 사고] Packagist 방치 메인테이너 계정 탈취(2023-05): 오래 쓰지 않던 메인테이너 계정 4개가 예전에 유출된 비밀번호로 장악되어 패키지 14개의 정보가 바뀜 (IDI-078)</t>
+        </is>
+      </c>
       <c r="H56" s="9" t="inlineStr">
         <is>
           <t>Orphaned, dormant and unrevoked accounts</t>
@@ -31392,7 +31890,7 @@
       </c>
       <c r="J56" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="K56" s="8" t="inlineStr">
@@ -31542,7 +32040,16 @@
 2.5.6 접근권한 검토</t>
         </is>
       </c>
-      <c r="AV56" s="9" t="inlineStr"/>
+      <c r="AV56" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 오랫동안 로그인이 없던 계정의 갑작스러운 로그인, 퇴사·전보 처리된 사용자 명의 접근, 퇴사자와 연결된 키·토큰 사용을 경보
+- 인사 시스템의 재직 현황과 계정·권한 목록을 정기 대조해 회수 누락 식별
+■ 대응
+- 인사 변동과 연동한 계정·권한 자동 회수, 퇴사 당일 비활성화와 관련 키·토큰 폐기(CIS 6.2, NIST AC-2(3)·PS-4·PS-5, ISMS-P 2.2.5, CCM IAM-07·HRS-06)
+- 휴면 계정 자동 비활성화와 계정 관리 중앙화, 정기 접근 권한 검토(CIS 5.3·5.6, NIST AC-2, ISMS-P 2.5.1·2.5.6, CCM IAM-08)</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="9" t="inlineStr">
@@ -31565,13 +32072,34 @@
           <t>협력사·외주·게스트 계정 악용</t>
         </is>
       </c>
-      <c r="E57" s="9" t="inlineStr"/>
-      <c r="F57" s="26" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Abuse of vendor, contractor and guest accounts</t>
-        </is>
-      </c>
-      <c r="G57" s="9" t="inlineStr"/>
+      <c r="E57" s="9" t="inlineStr">
+        <is>
+          <t>협력사·외주 인력 계정과 외주 지원 창구를 거쳐 원청 시스템 침투</t>
+        </is>
+      </c>
+      <c r="F57" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 원청 시스템에 접근하는 협력사·외주 인력의 계정을 탈취하거나 외주 헬프데스크·IT 지원업체를 속여 원청 내부로 들어올 수 있음
+- 협력사 단말·절차는 원청이 직접 통제하지 못하고, 외부 인력 계정은 권한·만료 관리가 느슨해 대량 유출의 입구가 됨</t>
+        </is>
+      </c>
+      <c r="G57" s="9" t="inlineStr">
+        <is>
+          <t>■ 신원 관점
+- 대상: 협력사 포털·VPN 계정, 외주 IT 지원·헬프데스크 인력, 용역 인력의 원청 사무실 PC·시스템 접근 권한(T1199·T1078), SaaS 게스트 사용자(SAT1046)
+- 조건: 협력사 직원 개인 단말의 브라우저 동기화, MFA 없는 협력사 VPN, 외주 업체의 신원 확인 절차 미준수, 계약 만료 뒤 남는 계정과 원청의 이행 점검 부재
+- 연계: 클라우드 CL-IA-06(신뢰 관계 악용), OT OT-IA-02(외부 원격 접속), 공급망 SCT-CS-02.3(공급업체 계정 경유 침입)
+■ 실제 사례
+- [실제 사고] Medibank 고객 970만 명 정보 유출(2022-10): IT 협력사 직원 브라우저 프로필에 저장된 자격증명이 개인 컴퓨터의 악성코드로 탈취되어 MFA 없는 VPN으로 침투 (IDI-018)
+- [실제 사고] Marks &amp; Spencer 랜섬웨어(2025-04): 협력사를 상대로 한 정교한 사칭으로 직원 비밀번호를 재설정받아 침투, 온라인 주문이 수주간 중단 (IDI-010, ATT&amp;CK G1015)
+- [실제 사고] Target 결제정보 4천만 건 유출(2013-12): 냉난방 협력사 직원에게 보낸 피싱 메일의 악성코드로 협력사 포털 자격증명을 훔쳐 내부망에 들어감 (IDI-079)
+- [실제 사고] 카드 3사 고객정보 1억여 건 유출(2014-01): 부정사용방지시스템 개발 용역 직원이 카드사 사무실 PC에서 고객정보 약 1억 건을 USB로 빼내 판매 (IDI-048)
+- [실제 사고] Latitude Financial 고객 1,400만 건 유출(2023-03): 대형 협력사의 내부 기반 시설을 침해해 Latitude 직원의 로그인 자격증명을 얻고 고객 신분증·여권 번호 등을 빼냄 (IDI-085)
+- [실제 사고] Caesars Entertainment 회원 DB 탈취(2023-09): 외주 IT 지원업체에 대한 사회공학으로 시작된 침해로 로열티 프로그램 DB 사본이 탈취 (IDI-006, ATT&amp;CK G1015)
+- [실제 사고] Uber 내부망 침해(2022-09): 협력사 직원 개인 단말에서 유출된 업무 비밀번호로 로그인을 반복하다 협력사 직원이 2단계 인증 요청을 승인 (IDI-002, ATT&amp;CK G1004)
+- [시연] SAT1046 게스트 접근 악용: Salesforce·ServiceNow의 게스트 사용자 권한 오설정으로 데이터에 접근하는 공개 시연</t>
+        </is>
+      </c>
       <c r="H57" s="9" t="inlineStr">
         <is>
           <t>Abuse of vendor, contractor and guest accounts</t>
@@ -31584,7 +32112,7 @@
       </c>
       <c r="J57" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="K57" s="8" t="inlineStr">
@@ -31736,7 +32264,16 @@
 2.3.4 외부자 계약 변경 및 만료 시 보안</t>
         </is>
       </c>
-      <c r="AV57" s="9" t="inlineStr"/>
+      <c r="AV57" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 협력사·외주 계정의 접속 시간·출발지·접근 시스템을 계약 범위와 비교해 이상 접근 경보, 외주 헬프데스크의 재설정 이력 감사
+- 계약 만료·인력 교체 뒤에도 쓰이는 외부 인력 계정과 게스트 사용자 권한 정기 점검
+■ 대응
+- 외부 인력 계정은 승인 절차로 발급하고 접근 범위·기간을 계약에 맞춰 제한, 만료 시 즉시 회수(CIS 6.1·6.2, NIST PS-7·AC-2, ISMS-P 2.3.3·2.3.4, CCM IAM-06·IAM-08)
+- 협력사·외주 업체에 MFA·관리 단말 사용과 신원 확인 절차 준수를 계약으로 요구하고 이행 점검(NIST SA-9·AC-20, CCM STA-09)</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="9" t="inlineStr">
@@ -31759,13 +32296,32 @@
           <t>내부자의 정상 권한 오남용·반출</t>
         </is>
       </c>
-      <c r="E58" s="9" t="inlineStr"/>
-      <c r="F58" s="26" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Insider misuse of legitimate access</t>
-        </is>
-      </c>
-      <c r="G58" s="9" t="inlineStr"/>
+      <c r="E58" s="9" t="inlineStr">
+        <is>
+          <t>내부자가 정상 권한으로 고객·내부 데이터를 대량 조회·반출</t>
+        </is>
+      </c>
+      <c r="F58" s="9" t="inlineStr">
+        <is>
+          <t>- 내부자는 업무상 가진 DB·클라우드·보고서 접근 권한이나 재직 중 확보한 키로 고객·임직원 정보를 대량으로 내려받아 팔거나 공개·갈취에 쓸 수 있음
+- 정상 권한 안의 행위라 접근 통제가 막지 못하고, 조회량·시간대 이상을 따로 분석하지 않으면 수개월 동안 드러나지 않음</t>
+        </is>
+      </c>
+      <c r="G58" s="9" t="inlineStr">
+        <is>
+          <t>■ 신원 관점
+- 대상: 고객 DB·보고서 조회 권한, 클라우드 저장소·코드 저장소 관리 권한(T1530·T1213), 개발 과정에서 얻은 토큰 서명 키, 데이터 내보내기 기능(SAT1037)
+- 조건: 직무에 비해 넓은 조회 권한, 대량 조회·내려받기 모니터링 부재, 개발·운영 권한 미분리, 퇴사 예정자 접근 관리 미흡
+- 연계: 퇴사자 권한 미회수(IDT-LC-01.1)와 겹치며 대량 데이터 탈취(IDT-IM-03)로 이어짐 — 클라우드 CL-CO-04
+■ 실제 사례
+- [실제 사고] 쿠팡 고객 계정 정보 3,367만 건 유출(2025-11): 개발자가 재직 중 확보한 토큰 서명키로 퇴사 뒤 약 8개월간 고객 정보를 조회해 이름·이메일 3,367만 건이 유출 (IDI-042)
+- [실제 사고] 카드 3사 고객정보 1억여 건 유출(2014-01): 용역 직원이 카드사 사무실 PC에서 고객정보 약 1억 건을 USB에 저장해 대출 중개업자에게 판매 (IDI-048)
+- [실제 사고] Ubiquiti 내부자 데이터 탈취·갈취(2020-12): 클라우드 엔지니어가 업무상 가진 AWS·GitHub 관리 권한으로 기밀 데이터를 내려받고 익명 해커로 위장해 50비트코인을 요구 (IDI-101)
+- [실제 사고] Tesla 전 직원 2명의 직원 7만 5천여 명 정보 유출(2023-05): 전 직원 2명이 정책을 어기고 직원 약 7만 5천 명의 개인정보 등 내부 데이터를 언론에 넘김 (IDI-102)
+- [실제 사고] Cash App 퇴사자의 고객 보고서 무단 다운로드(2022-04): 재직 중 업무로 접근하던 고객 보고서를 퇴사 뒤 내려받아 고객 820만 명 정보가 유출 (IDI-103)
+- [시연] SAT1037 데이터 내보내기 서비스: Google의 계정 데이터 일괄 내보내기 기능으로 데이터를 빼내는 공개 시연</t>
+        </is>
+      </c>
       <c r="H58" s="9" t="inlineStr">
         <is>
           <t>Insider misuse of legitimate access</t>
@@ -31778,7 +32334,7 @@
       </c>
       <c r="J58" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="K58" s="8" t="inlineStr">
@@ -31923,7 +32479,16 @@
 2.2.5 퇴직 및 직무변경 관리</t>
         </is>
       </c>
-      <c r="AV58" s="9" t="inlineStr"/>
+      <c r="AV58" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 개인별 조회·내려받기 양과 시간대 기준선을 두고 대량 조회·내보내기·외부 저장 장치 사용을 경보(NIST AU-6, ISMS-P 2.9.5, CCM LOG-05)
+- 퇴사 예정·징계 대상자처럼 위험 신호가 있는 사용자의 접근을 내부자 위협 프로그램에서 집중 점검(NIST PM-12)
+■ 대응
+- 직무 기반 최소 권한과 직무 분리, 고객정보 대량 조회는 승인·사유 기록 뒤 허용(CIS 6.8, NIST AC-6, ISMS-P 2.5.6, CCM IAM-04·IAM-05)
+- 퇴사 때 접근 권한·키를 즉시 회수하고 정기 접근 권한 검토(NIST PS-4, ISMS-P 2.2.5)</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="9" t="inlineStr">
@@ -31946,13 +32511,28 @@
           <t>외부의 내부자 매수·포섭</t>
         </is>
       </c>
-      <c r="E59" s="9" t="inlineStr"/>
-      <c r="F59" s="26" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Bribed or recruited insiders</t>
-        </is>
-      </c>
-      <c r="G59" s="9" t="inlineStr"/>
+      <c r="E59" s="9" t="inlineStr">
+        <is>
+          <t>고객지원·협력사 인력 매수로 정상 조회 권한을 통한 고객 정보 유출</t>
+        </is>
+      </c>
+      <c r="F59" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 고객 데이터 조회 권한을 가진 고객지원·협력사 인력을 돈으로 매수하거나 내부자로 모집해 정상 업무 화면으로 고객 정보를 빼내거나 사내 접근을 얻을 수 있음
+- 정상 계정의 정상 업무 조회라 기술 통제를 우회하고, 빼낸 정보는 회사를 사칭한 2차 사기로 이어져 고객 피해가 커짐</t>
+        </is>
+      </c>
+      <c r="G59" s="9" t="inlineStr">
+        <is>
+          <t>■ 신원 관점
+- 대상: 고객 계정·신분증 이미지를 조회하는 해외·외주 고객지원 인력, 협력사 직원의 업무 계정(T1078)
+- 조건: 지원 인력에게 넓게 열린 고객정보 조회 권한, 조회 사유·양 모니터링 부재, 외주 인력 채용 검증·보안 교육 미흡
+- 연계: 빼낸 정보로 회사를 사칭하는 사회공학(T1684.001)·금전 사기(IDT-IM-01)로 이어짐 — ATT&amp;CK에 LAPSUS$(G1004) 절차 수록
+■ 실제 사례
+- [실제 사고] Coinbase 고객 데이터 유출(2025-05): 범죄자들이 해외 고객지원 인력과 협력사 직원을 매수해 고객 이름·주소·신분증 이미지·잔액 등을 빼내고 Coinbase를 사칭한 사회공학으로 고객 자산을 노림 (IDI-012)
+- [실제 사고] LAPSUS$ 연쇄 침해(2022-03): 직원·협력사 내부자 모집을 다른 수법과 함께 써서 Microsoft·Nvidia·Samsung·Okta 등을 침해 (IDI-001, ATT&amp;CK G1004)</t>
+        </is>
+      </c>
       <c r="H59" s="9" t="inlineStr">
         <is>
           <t>Bribed or recruited insiders</t>
@@ -31965,7 +32545,7 @@
       </c>
       <c r="J59" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="K59" s="8" t="inlineStr">
@@ -32095,7 +32675,16 @@
 2.9.5 로그 및 접속기록 점검</t>
         </is>
       </c>
-      <c r="AV59" s="9" t="inlineStr"/>
+      <c r="AV59" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 고객지원 인력의 조회 건수·대상·시간대 기준선을 두고 담당 티켓과 무관한 고객 조회, 신분증 이미지 대량 열람을 경보(NIST AU-6, ISMS-P 2.9.5, CCM LOG-05)
+- 내부자 모집 게시물·매수 제안 신고 창구를 운영하고 신고된 인력의 접근 이력 점검(NIST PM-12)
+■ 대응
+- 고객정보 조회는 티켓·사유와 묶어 필요한 항목만 보이게 하고 민감 정보는 마스킹(CIS 6.8, ISMS-P 2.5.6, CCM IAM-04)
+- 외주·해외 지원 인력 채용 검증과 역할·책임 명시, 매수 제안 신고 의무 교육(NIST PS-3, CCM HRS-09)</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="9" t="inlineStr">
@@ -32118,13 +32707,28 @@
           <t>위장 취업(도용·위조 신원으로 정규 계정 획득)</t>
         </is>
       </c>
-      <c r="E60" s="9" t="inlineStr"/>
-      <c r="F60" s="26" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Fraudulent hiring with stolen or fake identities</t>
-        </is>
-      </c>
-      <c r="G60" s="9" t="inlineStr"/>
+      <c r="E60" s="9" t="inlineStr">
+        <is>
+          <t>도용·위조 신원으로 원격 IT 인력 위장 취업해 정규 계정 획득</t>
+        </is>
+      </c>
+      <c r="F60" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 도용·위조 신원과 AI로 보정한 사진으로 화상 면접·신원 조회를 통과해 원격 IT 인력으로 채용되고 회사가 지급한 노트북과 정규 계정을 받을 수 있음
+- 채용 절차로 정상 발급된 계정이라 접근 통제가 막지 않고, 대리 접속용 노트북 농장으로 근무 위치를 속여 데이터 탈취·갈취로 이어지기도 함</t>
+        </is>
+      </c>
+      <c r="G60" s="9" t="inlineStr">
+        <is>
+          <t>■ 신원 관점
+- 대상: 원격 근무 채용·온보딩의 신원 확인 절차, 지급 노트북과 정규 업무 계정(T1078), 위장 신원으로 만든 계정(T1585)
+- 조건: 화상 면접·서류만으로 신원 확인, 지급 장비 배송지와 신원 주소 불일치 미점검, 입사 직후 넓은 권한 부여
+- 연계: 채용 단계의 신원 확인 보증 수준·사기 관리 문제 — AI AI-01-07(딥페이크 생체인증 우회), 공급망 SCT-DE-01.2(가짜 채용 사회공학)
+■ 실제 사례
+- [실제 사고] 북한 원격 IT 인력 위장 취업 일제 단속(2025-06): 도용·위조 신원으로 미국 기업 100곳 이상에 원격 IT 인력으로 취업하고 조력자의 노트북 농장으로 원격 접속, 일부는 데이터 탈취·갈취로 이어짐 (IDI-105)
+- [실제 사고] KnowBe4 북한 위장 IT 인력 채용(2024-07): 도용한 미국인 신원과 AI로 보정한 사진으로 화상 면접·신원 조회를 통과했고 지급 노트북에서 악성코드를 내려받다 25분 만에 격리 (IDI-104)</t>
+        </is>
+      </c>
       <c r="H60" s="9" t="inlineStr">
         <is>
           <t>Fraudulent hiring with stolen or fake identities</t>
@@ -32137,7 +32741,7 @@
       </c>
       <c r="J60" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="K60" s="8" t="inlineStr">
@@ -32278,7 +32882,17 @@
           <t>2.5.1 사용자 계정 관리</t>
         </is>
       </c>
-      <c r="AV60" s="9" t="inlineStr"/>
+      <c r="AV60" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 지급 노트북의 원격 접속 도구 설치·해외 IP 접속·배송지와 다른 접속 위치, 입사 직후 대량 접근을 경보
+- 면접자와 근무자의 동일인 여부 재확인, 같은 연락처·계좌·주소를 쓰는 지원자 점검
+■ 대응
+- 원격 채용에 대면 또는 강한 신원 확인 절차를 두고 신분증·주소 진위를 검증(NIST IA-12·PS-3, CCM HRS-09)
+- 입사 초기 권한은 최소로 시작해 단계적으로 부여하고 접근 권한 부여 절차 준수(CIS 6.1, ISMS-P 2.5.1, CCM IAM-06)
+- 위장 취업 정황을 내부자 위협 프로그램 점검 대상에 포함(NIST PM-12)</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="9" t="inlineStr">
@@ -32301,13 +32915,32 @@
           <t>고객 계정 대량 크리덴셜 스터핑</t>
         </is>
       </c>
-      <c r="E61" s="9" t="inlineStr"/>
-      <c r="F61" s="26" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Large-scale credential stuffing against customer accounts</t>
-        </is>
-      </c>
-      <c r="G61" s="9" t="inlineStr"/>
+      <c r="E61" s="9" t="inlineStr">
+        <is>
+          <t>유출 아이디·비밀번호 자동 대입으로 고객 계정 대량 탈취</t>
+        </is>
+      </c>
+      <c r="F61" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 다른 곳에서 유출된 아이디·비밀번호 목록을 여러 IP로 나눠 고객 로그인에 자동 대입해 비밀번호를 재사용한 수만~수십만 계정에 한꺼번에 로그인할 수 있음
+- 서비스 자체가 뚫리지 않아도 개인정보 노출·부정 결제가 생기고, 정상 로그인과 섞여 단시간 대량 시도를 따로 탐지하지 않으면 수개월간 이어짐</t>
+        </is>
+      </c>
+      <c r="G61" s="9" t="inlineStr">
+        <is>
+          <t>■ 신원 관점
+- 대상: 쇼핑·예매·금융·게임 서비스의 고객 로그인과 로그인 뒤 개인정보 수정·배송지·결제 화면(T1110.004·T1078)
+- 조건: 고객 계정 MFA 미제공·선택 사항, 같은 IP·단시간 대량 로그인 탐지·차단 부재, 로그인 뒤 개인정보 마스킹 미흡 — OWASP 자동화 위협 OAT-008(크리덴셜 스터핑)·OAT-009(CAPTCHA 우회) 유형
+- 연계: 기업 계정 대상 재사용(IDT-AU-01.2)과 같은 기법이며 금전 사기(IDT-IM-01)·대량 데이터 탈취(IDT-IM-03)로 이어짐 — 클라우드 CL-CA-01
+■ 실제 사례
+- [실제 사고] GS리테일(GS SHOP·GS25) 크리덴셜 스터핑으로 회원 166만 명 정보 노출(2025-01): 같은 IP의 단시간 대량 로그인을 탐지·차단하지 못해 회원정보 수정 페이지에서 이름·연락처·주소 등이 빠져나가 과징금 128억 원 부과 (IDI-044)
+- [실제 사고] SK스토아 크리덴셜 스터핑으로 회원 12만 5천여 명 정보 유출(2023-11): 14개 IP로 초당 최대 372회, 총 4,400만 회 이상 로그인을 시도해 12만 5천여 계정에 로그인 (IDI-045)
+- [실제 사고] 23andMe 크리덴셜 스터핑(2023-10): 비밀번호를 재사용한 약 1만 4천 계정이 탈취되고 친척 찾기 기능으로 연결된 약 690만 명의 프로필 정보가 노출 (IDI-050)
+- [실제 사고] 케이티알파 기프티쇼 크리덴셜 스터핑(2023-01): 열흘간 4,305개 IP로 540만 회 이상 로그인을 시도해 약 9만 8천 개 계정에 로그인, 마스킹 덕분에 실제 유출은 51명 (IDI-046)
+- [실제 사고] Roku 크리덴셜 스터핑(57만 6천 계정)과 전 계정 2단계 인증 도입(2024-04): 약 57만 6천 계정이 탈취되어 일부에서 무단 구매가 일어난 뒤 전체 계정에 2단계 인증 적용 (IDI-051)
+- [실제 사고] DraftKings 크리덴셜 스터핑(2022-11): 약 6만 8천 명의 계정이 탈취되어 30만 달러 미만의 고객 자금이 빠져나감 (IDI-054)</t>
+        </is>
+      </c>
       <c r="H61" s="9" t="inlineStr">
         <is>
           <t>Large-scale credential stuffing against customer accounts</t>
@@ -32320,7 +32953,7 @@
       </c>
       <c r="J61" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="K61" s="8" t="inlineStr"/>
@@ -32475,7 +33108,16 @@
 2.5.4 비밀번호 관리</t>
         </is>
       </c>
-      <c r="AV61" s="9" t="inlineStr"/>
+      <c r="AV61" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 같은 IP·ASN·기기 지문의 단시간 대량 로그인, 로그인 성공률 급변, 처음 보는 기기의 개인정보 조회·배송지 변경을 실시간 탐지(NIST SI-4·AC-7)
+- 유출 자격증명 목록과 고객 계정 대조, 자동화 도구 지문으로 봇 트래픽 식별
+■ 대응
+- 고객 계정에 MFA·패스키를 제공하고 위험 기반 추가 인증 적용, 결제·개인정보 변경은 재인증(CIS 6.3, NIST IA-2(2), ISMS-P 2.5.3, CCM IAM-13)
+- 로그인 시도 제한·봇 차단과 유출 비밀번호 사용 금지, 로그인 뒤 개인정보 화면 마스킹(NIST AC-7·IA-5(1), ISMS-P 2.5.4)</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="9" t="inlineStr">
@@ -32498,13 +33140,28 @@
           <t>통신 가입자 인증 체계 침해(유심 인증키·불법 기지국)</t>
         </is>
       </c>
-      <c r="E62" s="9" t="inlineStr"/>
-      <c r="F62" s="26" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Compromise of telecom subscriber authentication (SIM keys, rogue base stations)</t>
-        </is>
-      </c>
-      <c r="G62" s="9" t="inlineStr"/>
+      <c r="E62" s="9" t="inlineStr">
+        <is>
+          <t>유심 인증키 유출·불법 기지국으로 휴대폰 기반 인증 체계 무력화</t>
+        </is>
+      </c>
+      <c r="F62" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 통신사 가입자 인증 서버에서 유심 인증키 등 가입자 정보를 빼내거나 통신사 인증서를 가진 불법 초소형 기지국으로 문자·ARS 인증값을 가로챌 수 있음
+- 휴대폰 문자·본인확인에 기대는 모든 서비스가 함께 영향을 받고, 가입자 개인이 막을 방법이 없어 통신사 단위의 대응이 필요함</t>
+        </is>
+      </c>
+      <c r="G62" s="9" t="inlineStr">
+        <is>
+          <t>■ 신원 관점
+- 침해 지점: 가입자 인증 서버(HSS)의 유심 인증키·가입자 정보, 기지국 인증서, 문자·ARS 결제 인증 경로(T1557·T1111)
+- 조건: 관리망 서버 계정 비밀번호 장기 미변경, 비정상 로그인 정황 미신고, 펨토셀 인증서 유효기간을 길게 설정
+- 연계: 휴대폰 기반 2단계 인증의 SIM 교체·문자 가로채기 위험(IDT-AU-03.2)과 금전 사기(IDT-IM-01)로 이어짐
+■ 실제 사례
+- [실제 사고] SK텔레콤 유심 정보 2,696만 건 유출(2025-04): 서버 28대에서 악성코드 33종이 발견되고 유심 정보 25종 2,696만여 건이 유출, 최초 침투는 2021-08로 특정 (IDI-040)
+- [실제 사고] KT 불법 펨토셀 경유 결제 인증 탈취·무단 소액결제(2025-09): 불법 초소형 기지국으로 문자·ARS 결제 인증값을 가로채 결제 피해자 368명·2억 4,300만 원이 발생하고 정부가 펨토셀 인증서 유효기간을 1개월로 줄이도록 함 (IDI-041)</t>
+        </is>
+      </c>
       <c r="H62" s="9" t="inlineStr">
         <is>
           <t>Compromise of telecom subscriber authentication (SIM keys, rogue base stations)</t>
@@ -32517,7 +33174,7 @@
       </c>
       <c r="J62" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="K62" s="8" t="inlineStr"/>
@@ -32646,7 +33303,17 @@
 2.5.3 사용자 인증</t>
         </is>
       </c>
-      <c r="AV62" s="9" t="inlineStr"/>
+      <c r="AV62" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 가입자 인증 서버·관리망의 비정상 로그인과 대량 조회, 등록되지 않은 기지국·펨토셀 접속을 실시간 탐지(NIST SI-4)
+- 같은 기지국을 거친 결제 인증 급증처럼 지역·장비 단위의 이상 거래 분석
+■ 대응
+- 가입자 인증키를 하드웨어 보안 모듈 등으로 보호하고 침해 시 키 교체·유심 교체 절차 준비(NIST SC-12, ISMS-P 2.7.2, CCM CEK-19)
+- 기지국 인증서 수명 단축과 접속 인가 통제, 인증 신호 구간 암호화(NIST SC-8, CCM IAM-15)
+- 서비스 제공자는 문자 단독 본인확인·결제 인증을 줄이고 피싱 저항 인증을 병행(ISMS-P 2.5.3)</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="9" t="inlineStr">
@@ -32669,13 +33336,28 @@
           <t>명의 도용·합성 신원 계정 개설</t>
         </is>
       </c>
-      <c r="E63" s="9" t="inlineStr"/>
-      <c r="F63" s="26" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Account opening with stolen or synthetic identities</t>
-        </is>
-      </c>
-      <c r="G63" s="9" t="inlineStr"/>
+      <c r="E63" s="9" t="inlineStr">
+        <is>
+          <t>도용 신분증·합성 신원으로 금융 계좌·서비스 계정 부정 개설</t>
+        </is>
+      </c>
+      <c r="F63" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 훔친 신분증이나 생성형 AI로 만든 위조 신분증·합성 신원으로 비대면 계좌·서비스 계정을 개설해 대출 사기·자금 세탁에 쓸 수 있음
+- 개설 시점의 신원 확인만 통과하면 정상 고객으로 취급되고, 실제 명의자는 대출·피해가 생긴 뒤에야 알게 됨</t>
+        </is>
+      </c>
+      <c r="G63" s="9" t="inlineStr">
+        <is>
+          <t>■ 신원 관점
+- 대상: 비대면 계좌 개설·회원 가입의 신원 확인 절차, 공격자가 만든 계정(T1585·T1585.003)
+- 조건: 신분증 이미지·얼굴 대조만으로 신원 확인, 같은 신분증·기기로 여러 계정을 여는 행위 탐지 부재 — OWASP 자동화 위협 OAT-019(계정 대량 생성) 유형
+- 연계: 얼굴 인증 우회(IDT-CI-03.2)와 함께 쓰이며 금전 사기(IDT-IM-01)로 이어짐 — AI AI-01-07(딥페이크 생체인증 우회)
+■ 실제 사례
+- [실제 사고] 홍콩 딥페이크 얼굴 바꾸기로 대출·계좌 개설 사기 조직 검거(2023-08): 훔친 신분증 8장으로 은행 계좌 54개를 열고 대출 90건을 신청 (IDI-061)
+- [실제 사고] FinCEN 경보 — 딥페이크 신분증·영상으로 계좌 개설·본인확인 우회(2024-11): 생성형 AI로 만든 위조 신분증·합성 신원으로 계좌 개설 본인확인을 우회하는 의심거래 보고가 늘었다며 적신호 지표 발표 (IDI-062)</t>
+        </is>
+      </c>
       <c r="H63" s="9" t="inlineStr">
         <is>
           <t>Account opening with stolen or synthetic identities</t>
@@ -32688,7 +33370,7 @@
       </c>
       <c r="J63" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="K63" s="8" t="inlineStr"/>
@@ -32823,7 +33505,16 @@
           <t>2.5.2 사용자 식별</t>
         </is>
       </c>
-      <c r="AV63" s="9" t="inlineStr"/>
+      <c r="AV63" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 같은 신분증·얼굴·기기·연락처로 여러 계좌·계정을 여는 패턴, 개설 직후 대출 신청·고액 이체를 이상 거래로 탐지
+- 신분증 이미지 재사용·편집 흔적 점검과 공개 적신호 지표 대조
+■ 대응
+- 비대면 개설의 신원 확인을 신분증 진위·명의자 확인·기기 정보 등 여러 근거로 교차 검증(NIST IA-12, ISMS-P 2.5.2)
+- 고객별 고유 신원 관리와 외부 사용자 식별·인증 기준 적용(NIST IA-8, CCM IAM-12)</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="9" t="inlineStr">
@@ -32846,13 +33537,29 @@
           <t>eKYC·얼굴 인증 우회(딥페이크·주입 공격)</t>
         </is>
       </c>
-      <c r="E64" s="9" t="inlineStr"/>
-      <c r="F64" s="26" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Bypassing eKYC and face verification (deepfake, injection)</t>
-        </is>
-      </c>
-      <c r="G64" s="9" t="inlineStr"/>
+      <c r="E64" s="9" t="inlineStr">
+        <is>
+          <t>딥페이크 얼굴·영상으로 eKYC·생체 본인확인을 통과해 계좌 접근</t>
+        </is>
+      </c>
+      <c r="F64" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 악성 앱으로 수집한 피해자 얼굴 영상이나 AI 얼굴 바꾸기로 만든 딥페이크를 얼굴 인식·영상 본인확인에 넣어 남의 명의로 인증을 통과할 수 있음
+- 생체 정보는 비밀번호처럼 바꿀 수 없어 한 번 털리면 반복 악용되고, 카메라 입력을 바꿔치기하는 주입 공격은 화면만 봐서는 구분하기 어려움</t>
+        </is>
+      </c>
+      <c r="G64" s="9" t="inlineStr">
+        <is>
+          <t>■ 신원 관점
+- 대상: 은행·정부기관 앱의 얼굴 인식 본인확인, 비대면 영상 신원 확인(eKYC)을 노린 사칭(T1684.001)
+- 조건: 얼굴 대조만으로 고위험 거래 허용, 실제 사람인지 판별하는 생체 검사·주입 탐지 미흡, 모바일 악성 앱의 얼굴·신분증 수집
+- 연계: AI AI-01-07(딥페이크 생체인증 우회)·AI-04-04(적대적 입력 판단 회피) — 계좌 장악 뒤 금전 사기(IDT-IM-01)로 이어짐
+■ 실제 사례
+- [실제 사고] GoldPickaxe 얼굴 인식 정보 탈취 트로이목마(2024-02): 은행·정부기관 앱을 사칭한 트로이목마로 얼굴 영상·신분증을 수집하고 딥페이크로 은행의 생체 본인확인을 통과해 계좌에 접근 (IDI-060)
+- [실제 사고] 홍콩 딥페이크 얼굴 바꾸기로 대출·계좌 개설 사기 조직 검거(2023-08): 얼굴 인식 절차에서 AI 얼굴 바꾸기 프로그램으로 신분증 주인 얼굴로 바꿔 시스템을 속이고 대출 4건이 승인 (IDI-061)
+- [실제 사고] FinCEN 경보 — 딥페이크 신분증·영상으로 계좌 개설·본인확인 우회(2024-11): 딥페이크 영상으로 금융기관의 본인확인과 인증을 우회하는 의심거래 보고 증가를 경보 (IDI-062)</t>
+        </is>
+      </c>
       <c r="H64" s="9" t="inlineStr">
         <is>
           <t>Bypassing eKYC and face verification (deepfake, injection)</t>
@@ -32865,7 +33572,7 @@
       </c>
       <c r="J64" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="K64" s="8" t="inlineStr"/>
@@ -32996,7 +33703,16 @@
           <t>2.5.3 사용자 인증</t>
         </is>
       </c>
-      <c r="AV64" s="9" t="inlineStr"/>
+      <c r="AV64" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 얼굴 인증 시도의 카메라 입력 이상(가상 카메라·에뮬레이터), 같은 얼굴 데이터의 여러 계정 사용, 인증 직후 고액 이체를 탐지
+- 얼굴·신분증을 요구하는 사칭 앱 설치 정황(공식 앱 장터 밖 설치)과 연계 분석
+■ 대응
+- 실제 사람 여부를 판별하는 생체 검사와 주입 공격 탐지를 적용하고 얼굴 인증 단독으로 고위험 거래를 허용하지 않음(NIST IA-12, ISMS-P 2.5.3, CCM IAM-13)
+- 본인확인에 등록 주소·연락처로 보낸 확인 코드 등 다른 근거를 더해 교차 검증(NIST IA-12(5))</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="9" t="inlineStr">
@@ -33019,13 +33735,34 @@
           <t>계정 장악 기반 금전 사기(BEC·송금·사칭 게시)</t>
         </is>
       </c>
-      <c r="E65" s="9" t="inlineStr"/>
-      <c r="F65" s="26" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Account-takeover fraud (BEC, payment and impersonation)</t>
-        </is>
-      </c>
-      <c r="G65" s="9" t="inlineStr"/>
+      <c r="E65" s="9" t="inlineStr">
+        <is>
+          <t>장악한 메일·SNS·금융 계정으로 송금 사기·사칭 게시·부정 결제</t>
+        </is>
+      </c>
+      <c r="F65" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 장악한 업무 메일·소셜 미디어·금융·고객 계정으로 거래처 송금을 가로채거나 사칭 게시물을 올리고 결제 수단·가상자산을 빼낼 수 있음
+- 정상 계정과 정상 채널로 지시·거래가 이뤄져 피해자가 의심하기 어렵고, 송금·가상자산 이체는 되돌리기 어려워 피해가 바로 확정됨</t>
+        </is>
+      </c>
+      <c r="G65" s="9" t="inlineStr">
+        <is>
+          <t>■ 신원 관점
+- 대상: 업무 메일함(T1114.002·T1586.002), 기관·기업 공식 소셜 미디어 계정, 고객 결제·가상자산 계정과 블록체인 서명 키(T1657)
+- 앞 단계: AiTM 피싱 뒤 메일 규칙 은닉(IDT-PE-02.3), SIM 교체·2단계 인증 미적용(IDT-AU-03.2·IDT-AU-03.3), 크리덴셜 스터핑(IDT-CI-01), 딥페이크 사칭(IDT-SE-04)
+- 연계: 클라우드 CL-IM-05(금전 탈취·갈취), AI AI-01-08(AI 생성 피싱·사칭), 공급망 SCT-IM-04(암호자산 가로채기)
+■ 실제 사례
+- [실제 사고] Arup 딥페이크 화상회의 송금 사기(2024-01): CFO와 동료로 보이는 딥페이크 참석자의 지시로 직원이 15차례 총 2억 홍콩달러(약 2,500만 달러)를 송금 (IDI-013)
+- [실제 사고] AiTM 피싱으로 세션 쿠키 탈취 후 BEC(2022-07): 탈취 세션으로 메일함에 들어가 거래처 메일 스레드에 끼어들어 송금을 유도 (IDI-029)
+- [실제 사고] Coinbase 고객 데이터 유출(2025-05): 매수한 지원 인력에게서 빼낸 고객 정보로 Coinbase를 사칭한 사회공학을 벌여 고객 자산을 노림, 대응 비용 최대 4억 달러 추정 (IDI-012)
+- [실제 사고] Ronin 브리지 6억 달러대 탈취(2022-03): 탈취한 검증자 키로 약 6억 달러 상당 암호화폐를 인출 (IDI-113, ATT&amp;CK G0032)
+- [실제 사고] KT 가입자 심스와핑 의심 가상자산 탈취(2022-01): 휴대폰이 갑자기 먹통이 된 뒤 가상자산 거래소 계정에서 수천만 원에서 수억 원대 암호화폐가 탈취 (IDI-047)
+- [실제 사고] 미 SEC X 계정 장악(2024-01): 위조 신분증으로 대체 SIM을 발급받아 2단계 인증이 꺼진 계정을 장악하고 비트코인 ETF 승인 가짜 게시물로 가격을 일시 급등시킴 (IDI-058)
+- [실제 사고] KT 불법 펨토셀 경유 결제 인증 탈취·무단 소액결제(2025-09): 가로챈 문자·ARS 결제 인증값으로 무단 소액결제, 결제 피해자 368명 (IDI-041)
+- [실제 사고] Coinbase SMS 계정 복구 결함 악용(2021-10): SMS 계정 복구 절차 결함으로 인증 토큰을 받아 고객 6천여 명의 자금을 빼냄 (IDI-056)</t>
+        </is>
+      </c>
       <c r="H65" s="9" t="inlineStr">
         <is>
           <t>Account-takeover fraud (BEC, payment and impersonation)</t>
@@ -33038,7 +33775,7 @@
       </c>
       <c r="J65" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="K65" s="8" t="inlineStr">
@@ -33186,7 +33923,16 @@
           <t>2.5.3 사용자 인증</t>
         </is>
       </c>
-      <c r="AV65" s="9" t="inlineStr"/>
+      <c r="AV65" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 메일함 새 규칙·외부 전달과 거래처 계좌 변경 요청, 공식 계정의 비정상 로그인·게시를 연계 탐지(NIST SI-4)
+- 휴대폰 개통·유심 변경 직후의 금융·가상자산 계정 로그인, 인증 직후 고액 이체·출금을 이상 거래로 탐지
+■ 대응
+- 메일·공식 소셜 미디어·금융 계정에 피싱 저항 MFA를 적용하고 문자 단독 인증을 줄임(CIS 6.3, NIST IA-2(1), ISMS-P 2.5.3, CCM IAM-13)
+- 송금·계좌 변경은 사전 등록 채널로 콜백 확인하고 이중 승인, BEC·딥페이크 사칭 사례 교육(NIST AT-2(3))</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="9" t="inlineStr">
@@ -33209,13 +33955,34 @@
           <t>신원 장악 후 랜섬웨어·파괴(도메인·테넌트 전체)</t>
         </is>
       </c>
-      <c r="E66" s="9" t="inlineStr"/>
-      <c r="F66" s="26" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Ransomware and destruction after identity takeover</t>
-        </is>
-      </c>
-      <c r="G66" s="9" t="inlineStr"/>
+      <c r="E66" s="9" t="inlineStr">
+        <is>
+          <t>도메인·IdP 관리 권한 장악 뒤 전사 랜섬웨어·백업 삭제</t>
+        </is>
+      </c>
+      <c r="F66" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 헬프데스크 사칭·MFA 없는 원격 접속·디렉터리 취약점으로 도메인·IdP·클라우드 관리 권한을 얻은 뒤 전사 시스템을 암호화하고 백업·클라우드 자원을 지울 수 있음
+- 관리 권한 자체가 배포·삭제 수단이 되어 몇 시간 만에 조직 전체가 멈추고, 같은 권한으로 백업까지 지우면 복구가 크게 늦어짐</t>
+        </is>
+      </c>
+      <c r="G66" s="9" t="inlineStr">
+        <is>
+          <t>■ 신원 관점
+- 침해 지점: 도메인 관리자·그룹 정책, IdP·하이퍼바이저·클라우드 관리 계정, 백업 관리 권한(T1486·T1485·T1490)
+- 앞 단계: 헬프데스크 사칭(IDT-SE-02.1), MFA 없는 원격 접속(IDT-AU-03.3), 세션 토큰 탈취(IDT-TS-01.3), Kerberoasting(IDT-TS-02.2), 동기화 서버 장악(IDT-DI-02), 도메인 컨트롤러 취약점(IDT-DI-01.4)
+- 연계: 클라우드 CL-IM-01·CL-IM-02, OT OT-IM-02, 공급망 SCT-IM-05 — 신원 단계에서 끊으면 암호화 단계까지 가지 않음
+■ 실제 사례
+- [실제 사고] MGM Resorts 랜섬웨어(2023-09): 헬프데스크 사칭으로 Okta·Azure 관리 권한을 얻어 약 100대의 ESXi 하이퍼바이저를 암호화, 운영이 열흘가량 마비되고 약 1억 달러 영업 손실 (IDI-005, ATT&amp;CK G1015)
+- [실제 사고] Change Healthcare 랜섬웨어(2024-02): 탈취한 자격증명으로 MFA가 없던 Citrix 원격 접속 포털에 로그인하고 9일 뒤 랜섬웨어를 실행해 미국 전역의 청구·자격 확인 업무가 수주간 마비 (IDI-015, ATT&amp;CK S1068)
+- [실제 사고] Ascension 랜섬웨어(2024-05): RC4 암호화를 허용하던 Active Directory에서 Kerberoasting으로 특권 계정을 얻어 수천 대에 랜섬웨어를 배포 (IDI-021, ATT&amp;CK S1070)
+- [실제 사고] Storm-0501 하이브리드 환경 랜섬웨어(2024-09): 동기화 서버 계정 자격증명으로 MFA 없는 클라우드 관리자 계정에 들어가 클라우드 자원·백업을 지우고 랜섬웨어를 실행 (IDI-022, ATT&amp;CK G1053)
+- [실제 사고] Ryuk의 Zerologon 악용으로 5시간 만에 도메인 전체 암호화(2020-10): 도메인 컨트롤러 자격증명을 재설정해 도메인 관리자 권한을 얻고 백업·파일 서버와 단말에 랜섬웨어를 배포 (IDI-096, ATT&amp;CK S0446)
+- [실제 사고] Marks &amp; Spencer 랜섬웨어(2025-04): 협력사를 상대로 한 사칭으로 직원 비밀번호를 재설정받아 침투, 영업이익 약 3억 파운드 영향 추정 (IDI-010, ATT&amp;CK G1015)
+- [실제 사고] MERCURY·DEV-1084 하이브리드 환경 파괴 공격(2023-04): 동기화 에이전트의 특권 계정 자격증명으로 클라우드에 접근해 클라우드·온프레미스 자원을 대량 삭제 (IDI-023)
+- [실제 사고] Prestige 랜섬웨어(2022-10): 도메인 관리자 수준 권한으로 기본 그룹 정책 개체를 바꿔 랜섬웨어를 전체 도메인에 배포 (IDI-028, ATT&amp;CK G0034)</t>
+        </is>
+      </c>
       <c r="H66" s="9" t="inlineStr">
         <is>
           <t>Ransomware and destruction after identity takeover</t>
@@ -33228,7 +33995,7 @@
       </c>
       <c r="J66" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="K66" s="8" t="inlineStr"/>
@@ -33371,7 +34138,16 @@
           <t>2.5.5 특수 계정 및 권한 관리</t>
         </is>
       </c>
-      <c r="AV66" s="9" t="inlineStr"/>
+      <c r="AV66" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 도메인·IdP·클라우드 관리 권한의 새 부여·비정상 사용, 그룹 정책·하이퍼바이저 대량 작업, 백업 삭제·보존 설정 변경을 실시간 경보(NIST SI-4, CCM LOG-03)
+- 원격 접속 신규 로그인 뒤 짧은 시간 안에 이어지는 권한 상승·횡적 이동을 상관 분석
+■ 대응
+- 도메인·IdP·백업 관리 권한을 전용 관리자 계정과 피싱 저항 MFA로 분리하고 관리 계층 간 자격증명 재사용 금지(CIS 5.4·6.5, NIST AC-6(5), ISMS-P 2.5.5, CCM IAM-10)
+- 관리자 권한으로도 지울 수 없는 분리·불변 백업을 두고 복구 훈련(NIST CP-9)</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="9" t="inlineStr">
@@ -33394,13 +34170,35 @@
           <t>계정 기반 대량 데이터 탈취·갈취</t>
         </is>
       </c>
-      <c r="E67" s="9" t="inlineStr"/>
-      <c r="F67" s="26" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Mass data theft and extortion via identities</t>
-        </is>
-      </c>
-      <c r="G67" s="9" t="inlineStr"/>
+      <c r="E67" s="9" t="inlineStr">
+        <is>
+          <t>정상 계정·토큰으로 SaaS·DB를 대량 조회해 데이터 탈취·갈취</t>
+        </is>
+      </c>
+      <c r="F67" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 탈취하거나 매수·위조한 계정·토큰·서명키로 SaaS·고객 DB·코드 저장소에 정상 사용자처럼 들어가 대량의 데이터를 내려받고 공개를 빌미로 갈취할 수 있음
+- 정상 권한의 조회·내보내기라 데이터 유출 방지 통제를 통과하기 쉽고, 조회량 이상을 보지 않으면 수개월 뒤 외부 공개·통지로 알게 됨</t>
+        </is>
+      </c>
+      <c r="G67" s="9" t="inlineStr">
+        <is>
+          <t>■ 신원 관점
+- 대상: 클라우드 저장소(T1530), SaaS·협업 도구·고객 DB(T1213), 메일함(T1114.002), 데이터 일괄 내보내기·웹훅·자동화 워크플로(SAT1037·SAT1039·SAT1033)
+- 앞 단계: 인포스틸러 자격증명·MFA 미적용(IDT-CR-01.1·IDT-AU-03.3), 크리덴셜 스터핑(IDT-CI-01), 연동 토큰 탈취(IDT-NH-03.1), 인증 토큰 위조(IDT-TS-03.3), 내부자 오남용(IDT-LC-02.1)
+- 연계: 클라우드 CL-CO-01·CL-CO-04·CL-IM-05, OT OT-IM-06(운영 정보 탈취), 공급망 SCT-IM-03(소스 코드 대량 반출)
+■ 실제 사례
+- [실제 사고] Snowflake 고객 인스턴스 대량 데이터 탈취(2024-05): 인포스틸러에서 나온 고객 자격증명으로 MFA와 접속 허용 목록이 없는 인스턴스 약 165곳에 로그인해 데이터를 대량 반출·갈취 (IDI-016)
+- [실제 사고] 쿠팡 고객 계정 정보 3,367만 건 유출(2025-11): 퇴사 개발자가 토큰 서명키로 정상 로그인 없이 고객 정보를 조회해 배송지 목록 페이지가 1억 4천여 회 조회됨 (IDI-042)
+- [실제 사고] SK텔레콤 유심 정보 2,696만 건 유출(2025-04): 관리망 서버 계정 관리가 부실한 가운데 유심 정보 25종 2,696만여 건이 유출 (IDI-040)
+- [실제 사고] Salesforce 대상 음성 피싱(2025-06): 변조된 Data Loader 연결 앱으로 조직의 Salesforce 데이터를 API로 대량 조회·반출한 뒤 갈취 (IDI-036, ATT&amp;CK G1057)
+- [실제 사고] Salesloft Drift 연동 OAuth 토큰 탈취로 Salesforce 인스턴스 대량 데이터 반출(2025-08): 연동 토큰으로 여러 조직의 Salesforce 데이터를 조회·반출 (IDI-037)
+- [실제 사고] GS리테일(GS SHOP·GS25) 크리덴셜 스터핑으로 회원 166만 명 정보 노출(2025-01): 탈취한 계정의 회원정보 수정 페이지에서 이름·연락처·주소 등을 빼냄 (IDI-044)
+- [실제 사고] Co-op 회원 650만 명 정보 탈취(2025-04): 직원을 사칭해 계정 접근을 얻은 뒤 회원 650만 명 전원의 이름·주소·연락처를 탈취 (IDI-011, ATT&amp;CK G1015)
+- [실제 사고] Medibank 고객 970만 명 정보 유출(2022-10): 협력사 직원 자격증명과 MFA 없는 VPN으로 침투해 고객 약 970만 명의 정보를 탈취하고 다크웹에 공개 (IDI-018)
+- [시연] SAT1037 데이터 내보내기 서비스·SAT1039 웹훅: Google 데이터 일괄 내보내기와 Microsoft 365 웹훅으로 데이터를 빼내는 공개 시연</t>
+        </is>
+      </c>
       <c r="H67" s="9" t="inlineStr">
         <is>
           <t>Mass data theft and extortion via identities</t>
@@ -33413,7 +34211,7 @@
       </c>
       <c r="J67" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="K67" s="8" t="inlineStr">
@@ -33578,7 +34376,16 @@
           <t>2.9.5 로그 및 접속기록 점검</t>
         </is>
       </c>
-      <c r="AV67" s="9" t="inlineStr"/>
+      <c r="AV67" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 계정·토큰·연동 앱별 조회량·내보내기·API 호출 기준선을 두고 대량 조회·일괄 내보내기·새 출발지 접근을 경보(NIST SI-4·AU-6, ISMS-P 2.9.5, CCM LOG-05)
+- 데이터 플랫폼·SaaS 로그를 중앙에 모아 로그인 출발지·인증 방식(MFA 여부)과 조회 행위를 함께 분석
+■ 대응
+- 데이터 접근 권한을 역할별 최소 권한으로 줄이고 대량 조회·내보내기는 승인·속도 제한 적용(CIS 6.8, NIST AC-6, CCM IAM-05)
+- 데이터 플랫폼·SaaS에 MFA와 접속 허용 목록을 필수로 두고 고객정보 화면 마스킹·조회 기록 보존</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="9" t="inlineStr">
@@ -33601,13 +34408,29 @@
           <t>계정 접근 차단·관리자 축출과 계정 연동 파괴</t>
         </is>
       </c>
-      <c r="E68" s="9" t="inlineStr"/>
-      <c r="F68" s="26" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Account access removal and admin lockout</t>
-        </is>
-      </c>
-      <c r="G68" s="9" t="inlineStr"/>
+      <c r="E68" s="9" t="inlineStr">
+        <is>
+          <t>관리자 계정 삭제·자격증명 변경으로 대응 차단과 연동 계정 파괴</t>
+        </is>
+      </c>
+      <c r="F68" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 장악한 관리 권한으로 관리자 계정을 지우거나 비밀번호·인증 수단을 바꿔 피해 조직의 대응을 막고, 연결된 계정·기기의 데이터를 원격으로 지울 수 있음
+- 침해 대응에 필요한 관리자 접근이 먼저 사라져 복구가 늦어지고, 별도 긴급 계정이 없으면 공급업체 지원에 기대야 함</t>
+        </is>
+      </c>
+      <c r="G68" s="9" t="inlineStr">
+        <is>
+          <t>■ 신원 관점
+- 대상: IdP·클라우드 관리자 계정, 디렉터리 동기화로 연결된 클라우드 자원, 개인 클라우드 계정에 연결된 기기 원격 삭제 기능(T1531·T1485)
+- 조건: 긴급(break-glass) 계정 부재, 관리자 계정 삭제·변경 경보 부재, 다른 서비스에서 얻을 수 있는 정보로 통과되는 계정 복구 절차
+- 연계: 클라우드 CL-IM-03(계정 접근 차단), OT OT-IR-06(자격증명 변경으로 운영자 차단) — ATT&amp;CK에 LAPSUS$(G1004)의 전역 관리자 계정 삭제, Akira(G1024)의 암호화 전 관리자 계정 삭제 절차 수록
+■ 실제 사례
+- [실제 사고] LAPSUS$ 연쇄 침해(2022-03): 탈취한 계정으로 소스 코드와 데이터를 반출하고 일부 피해 조직에서는 관리자 계정을 지워 대응을 방해 (IDI-001, ATT&amp;CK G1004)
+- [실제 사고] MERCURY·DEV-1084 하이브리드 환경 파괴 공격(2023-04): 동기화 에이전트의 특권 계정 자격증명으로 클라우드에 접근해 서버 팜·가상머신·스토리지 등을 대량 삭제 (IDI-023)
+- [실제 사고] Mat Honan 계정 연쇄 탈취(2012-08): 고객지원 사회공학으로 iCloud 계정 비밀번호를 재설정받아 Gmail·Twitter 계정까지 장악하고 노트북·휴대폰·태블릿 데이터를 원격 삭제 (IDI-057)</t>
+        </is>
+      </c>
       <c r="H68" s="9" t="inlineStr">
         <is>
           <t>Account access removal and admin lockout</t>
@@ -33620,7 +34443,7 @@
       </c>
       <c r="J68" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="K68" s="8" t="inlineStr"/>
@@ -33763,7 +34586,16 @@
           <t>2.5.5 특수 계정 및 권한 관리</t>
         </is>
       </c>
-      <c r="AV68" s="9" t="inlineStr"/>
+      <c r="AV68" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 관리자 계정 삭제·비활성화, 관리자 비밀번호·인증 수단 일괄 변경, 대량 계정 삭제·원격 초기화 명령을 실시간 경보
+- 긴급 계정 사용 시 즉시 경보하고 정기 로그인 시험으로 사용 가능 여부 확인
+■ 대응
+- 일상 관리와 분리된 긴급(break-glass) 계정을 오프라인 보관 자격증명·하드웨어 키로 유지하고 특권 계정 사용을 감사(CIS 5.4, NIST AC-2(7), ISMS-P 2.5.5, CCM IAM-10)
+- 계정·설정 백업을 두고 사고 대응 절차에 관리자 접근 상실 시나리오를 포함(NIST CP-9·IR-4)</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="9" t="inlineStr">
@@ -33786,13 +34618,35 @@
           <t>공급업체·플랫폼 경유 고객 계정 연쇄 탈취</t>
         </is>
       </c>
-      <c r="E69" s="9" t="inlineStr"/>
-      <c r="F69" s="26" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Chained account compromise across vendors and customers</t>
-        </is>
-      </c>
-      <c r="G69" s="9" t="inlineStr"/>
+      <c r="E69" s="9" t="inlineStr">
+        <is>
+          <t>공급업체·플랫폼 신원 침해가 그 서비스를 쓰는 고객 계정으로 연쇄 확산</t>
+        </is>
+      </c>
+      <c r="F69" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 IdP·원격 지원·CI/CD·SaaS 연동 공급업체의 직원 계정이나 고객용 토큰·키를 장악해 그 서비스를 믿는 여러 고객 조직의 계정과 데이터로 옮겨 갈 수 있음
+- 고객은 공급업체 내부를 볼 수 없어 공지가 나와야 알게 되고, 고객마다 토큰·비밀을 교체해야 해 한 번의 침해가 수많은 조직의 대응으로 번짐</t>
+        </is>
+      </c>
+      <c r="G69" s="9" t="inlineStr">
+        <is>
+          <t>■ 신원 관점
+- 침해 지점: 공급업체 지원 시스템·고객 지원 포털, 고객 비밀을 보관하는 CI/CD·데이터 분석 SaaS, 연동 앱 토큰(T1550.001), 공급업체와의 신뢰 관계(T1199)
+- 조건: 취약한 서드파티 비인간 신원(NHI3), 공급업체 침해 공지 뒤 고객 쪽 토큰·비밀 교체 지연, 공급업체 직원 계정의 피싱 저항 MFA 부재
+- 연계: IdP 공급업체 침해(IDT-DI-03.1)·SaaS 연동 토큰 탈취(IDT-NH-03.1)의 결과 — 클라우드 CL-IA-06, AI AI-06-07(다중 에이전트 연쇄 전파), 공급망 SCT-IM-01.2·SCT-CS-03.1
+■ 실제 사례
+- [실제 사고] Okta 지원 시스템 침해(2023-10): 고객이 지원 요청에 첨부한 HAR 파일에서 세션 토큰을 추출해 BeyondTrust·Cloudflare·1Password 등 고객 134곳에 영향 (IDI-019)
+- [실제 사고] Cloudflare 내부 Atlassian 침해(2023-11): Okta 침해 때 유출되고 교체되지 않은 서비스 토큰·서비스 계정 자격증명으로 Atlassian에 접근, 탐지 하루 만에 차단 (IDI-020)
+- [실제 사고] Twilio 등 0ktapus SMS 피싱 캠페인(2022-08): 130곳 이상이 표적이 되어 자격증명 9,931건이 수집됐고 Twilio에서는 고객 209곳과 Signal 사용자 약 1,900명의 정보가 노출 (IDI-004, ATT&amp;CK G1015)
+- [실제 사고] CircleCI 고객 비밀 유출(2023-01): 엔지니어 노트북 악성코드가 SSO 세션을 훔쳐 고객 환경변수·토큰·키를 빼냈고 모든 고객에게 저장 비밀 전체 교체를 권고 (IDI-073)
+- [실제 사고] BeyondTrust 원격 지원 SaaS API 키 탈취로 미 재무부 등 고객 17곳 침해(2024-12): 공급업체 인프라 API 키로 고객 인스턴스 비밀번호를 재설정해 고객 단말에 원격 접근 (IDI-084)
+- [실제 사고] Salesloft Drift 연동 OAuth 토큰 탈취로 Salesforce 인스턴스 대량 데이터 반출(2025-08): 연동 토큰으로 여러 조직의 데이터를 반출하고 그 안에서 AWS 키·Snowflake 토큰 등 자격증명을 찾아냄 (IDI-037)
+- [실제 사고] Retool 고객 계정 27곳 장악(2023-08): 직원 계정 장악과 인증 앱 클라우드 동기화로 MFA 코드가 함께 넘어가 클라우드 고객 27곳의 계정이 장악 (IDI-072)
+- [실제 사고] npm chalk·debug 메인테이너 계정 탈취(2025-09): 가짜 2FA 재설정 메일로 유명 메인테이너 계정이 탈취되어 18개 패키지에 지갑 거래를 가로채는 코드가 실림 (IDI-077)
+- [시연] SAT1029 비밀번호 없는 로그인: Canva·Slack·Expensify에서 메일로 받은 일회용 코드 로그인으로 장악한 메일 계정에서 다른 SaaS로 옮겨 가는 공개 시연</t>
+        </is>
+      </c>
       <c r="H69" s="9" t="inlineStr">
         <is>
           <t>Chained account compromise across vendors and customers</t>
@@ -33805,7 +34659,7 @@
       </c>
       <c r="J69" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="K69" s="8" t="inlineStr">
@@ -33963,7 +34817,16 @@
           <t>2.3.3 외부자 보안 이행 관리</t>
         </is>
       </c>
-      <c r="AV69" s="9" t="inlineStr"/>
+      <c r="AV69" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 공급업체 침해 공지·보안 권고를 구독해 공지 즉시 해당 서비스 토큰·연동 키·지원 접근 이력 점검(NIST IR-4)
+- 공급업체 지원 인력·원격 지원 도구의 고객 환경 접근을 별도로 감사하고 연동 토큰의 새 출발지 사용을 경보
+■ 대응
+- 신원·원격 지원·CI/CD·연동 공급업체를 핵심 공급망으로 분류해 보안 요구 사항 계약과 정기 평가(NIST SA-9·SR-6, ISMS-P 2.3.3, CCM STA-09)
+- 공급업체에 맡긴 비밀·토큰 목록을 유지해 침해 때 전수 교체하고, 공급업체 특권 접근은 고객 승인 아래에서만 허용(CIS 6.6, CCM IAM-11)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A4:AV69"/>
@@ -37446,10 +38309,15 @@
           <t>과다 권한·권한 상승 경로 악용</t>
         </is>
       </c>
-      <c r="E41" s="9" t="inlineStr"/>
-      <c r="F41" s="26" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Excessive permissions and privilege escalation paths</t>
+      <c r="E41" s="9" t="inlineStr">
+        <is>
+          <t>과다 권한·누적 역할을 타고 탈취 계정에서 관리자 권한으로 확대</t>
+        </is>
+      </c>
+      <c r="F41" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 탈취한 계정에 필요 이상으로 붙은 역할·그룹·내부 도구 권한을 쓰거나 클라우드 역할을 직접 추가해 관리자 수준 권한까지 넓힐 수 있음
+- 수년간 누적된 권한은 실제 업무 범위와 차이가 커도 잘 보이지 않고, 지원·운영 인력 계정 하나가 수많은 고객·사용자 계정 관리로 이어짐</t>
         </is>
       </c>
       <c r="G41" s="9" t="inlineStr">
@@ -37496,7 +38364,16 @@
       <c r="P41" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="Q41" s="9" t="inlineStr"/>
+      <c r="Q41" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 관리 역할·그룹 부여, 일시 권한 상승 요청, 권한 탐색 API 대량 호출을 평소 패턴과 비교해 경보(NIST AC-2)
+- 내부 관리·지원 도구에서 한 직원이 짧은 시간에 여러 고객 계정을 조회·변경하는 패턴 점검
+■ 대응
+- 역할 기반 접근 통제로 직무별 최소 권한을 정의하고 정기 권한 검토로 누적 권한 회수(CIS 6.8, NIST AC-6·AC-6(7), ISMS-P 2.5.5·2.5.6, CCM IAM-05·IAM-08)
+- 고객 계정을 바꿀 수 있는 내부 도구는 승인된 소수에게만 열고, 일시 권한 상승은 기간 제한·승인 기록을 남김</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="9" t="inlineStr">
@@ -37519,10 +38396,15 @@
           <t>특권 접근 관리(PAM)·관리 도구 체계 침해</t>
         </is>
       </c>
-      <c r="E42" s="9" t="inlineStr"/>
-      <c r="F42" s="26" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Compromise of privileged access management and admin tooling</t>
+      <c r="E42" s="9" t="inlineStr">
+        <is>
+          <t>PAM·계정 관리 도구 장악으로 연결된 시스템 관리 권한 일괄 확보</t>
+        </is>
+      </c>
+      <c r="F42" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 특권 접근 관리(PAM) 도구의 관리자 자격증명이나 내부 계정 관리 도구를 손에 넣어 그 도구가 다루는 모든 시스템·계정의 권한을 한 번에 얻을 수 있음
+- 특권 자격증명을 한곳에 모은 도구라 장악 즉시 피해가 조직 전체로 넓어지고, 도구 관리자 계정이 스크립트·공유 폴더에 남아 있는 경우가 많음</t>
         </is>
       </c>
       <c r="G42" s="9" t="inlineStr">
@@ -37569,7 +38451,16 @@
       <c r="P42" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="Q42" s="9" t="inlineStr"/>
+      <c r="Q42" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- PAM 관리자 로그인·정책 변경·금고 대량 조회, 평소와 다른 단말·위치의 관리 도구 접근을 실시간 경보
+- 공유 폴더·스크립트 저장소의 특권 자격증명 스캔, 계정 관리 도구 감사 로그의 비업무 계정 조회 패턴 점검
+■ 대응
+- PAM·관리 도구 관리자는 전용 관리자 계정·전용 단말로 분리하고 피싱 저항 MFA 필수(CIS 5.4·6.5, NIST AC-6(5)·IA-2(1), ISMS-P 2.5.5, CCM IAM-09·IAM-10)
+- 특권 계정 사용 내역 감사와 스크립트 하드코딩 금지, 관리 도구 접근 권한 정기 검토(NIST AC-2(7))</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="9" t="inlineStr">
@@ -37592,10 +38483,15 @@
           <t>백도어 계정 생성·자격증명 추가</t>
         </is>
       </c>
-      <c r="E43" s="9" t="inlineStr"/>
-      <c r="F43" s="26" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Backdoor accounts and additional credentials</t>
+      <c r="E43" s="9" t="inlineStr">
+        <is>
+          <t>백도어 계정 생성·앱 자격증명 추가로 비밀번호 재설정 뒤에도 접근 유지</t>
+        </is>
+      </c>
+      <c r="F43" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 장악한 관리 권한으로 새 관리자 계정을 만들거나 기존 앱·서비스 주체에 자격증명·API 키를 추가해 원래 침투 경로가 막혀도 다시 들어올 수 있음
+- 사용자 비밀번호를 모두 바꿔도 새 계정·앱 자격증명은 그대로 남고, 정상 관리 작업처럼 보여 계정·자격증명 인벤토리 없이는 찾기 어려움</t>
         </is>
       </c>
       <c r="G43" s="9" t="inlineStr">
@@ -37642,7 +38538,16 @@
       <c r="P43" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="Q43" s="9" t="inlineStr"/>
+      <c r="Q43" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 새 관리자 계정 생성, 앱·서비스 주체 자격증명·API 키 추가, 업무 시간 외 계정 생성을 고위험 이벤트로 경보(NIST AU-6·AC-2(12))
+- 계정·서비스 계정 인벤토리와 실제 디렉터리·테넌트 계정을 정기 대조해 등록되지 않은 계정 식별
+■ 대응
+- 계정·서비스 계정 인벤토리를 유지하고 소유자 없는 계정 비활성화(CIS 5.1·5.5, NIST AC-2, ISMS-P 2.5.1, CCM IAM-03)
+- 앱 자격증명 추가·관리자 계정 생성 권한을 최소화하고 정기 접근 권한 검토(ISMS-P 2.5.6, CCM IAM-08)</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="9" t="inlineStr">
@@ -37665,10 +38570,15 @@
           <t>MFA 장치·인증 수단 추가 등록</t>
         </is>
       </c>
-      <c r="E44" s="9" t="inlineStr"/>
-      <c r="F44" s="26" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Registering attacker MFA devices and authentication methods</t>
+      <c r="E44" s="9" t="inlineStr">
+        <is>
+          <t>탈취 계정에 공격자 MFA 장치·인증 수단을 등록해 접근 유지</t>
+        </is>
+      </c>
+      <c r="F44" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 피싱·헬프데스크 사칭·MFA 피로로 한 번 얻은 계정에 자기 MFA 장치나 새 인증 수단, 기기를 등록해 이후에는 정상 사용자처럼 인증할 수 있음
+- 등록 뒤에는 MFA가 오히려 공격자 접근을 보증하고, 비밀번호를 바꿔도 등록된 장치·수단을 지우지 않으면 접근이 이어짐</t>
         </is>
       </c>
       <c r="G44" s="9" t="inlineStr">
@@ -37715,7 +38625,17 @@
       <c r="P44" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="Q44" s="9" t="inlineStr"/>
+      <c r="Q44" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 새 MFA 장치·인증 수단·기기 등록을 사용자 알림과 보안팀 경보로 함께 처리하고, 등록 직전의 새 위치 로그인·MFA 피로·재설정과 상관 분석(NIST AU-6)
+- 한 장치·전화번호가 여러 계정에 등록되거나 휴면 계정에 처음 MFA가 등록되는 패턴 점검
+■ 대응
+- MFA 등록·재등록에 기존 강한 인증 수단 확인이나 관리자 승인을 요구하고 등록 가능 위치·장치를 조건부로 제한(NIST IA-5, ISMS-P 2.5.3, CCM IAM-13·IAM-07)
+- 피싱 저항 MFA로 등록 이전 단계의 계정 탈취를 막고 관리자 계정은 하드웨어 키만 허용(CIS 6.3·6.5, NIST IA-2(1))
+- 침해 대응 때 비밀번호와 함께 등록된 MFA 장치·기기·세션을 전수 점검·삭제</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="9" t="inlineStr">
@@ -37738,10 +38658,15 @@
           <t>메일함 규칙·위임·전달 설정 악용</t>
         </is>
       </c>
-      <c r="E45" s="9" t="inlineStr"/>
-      <c r="F45" s="26" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Mailbox rules, delegation and forwarding abuse</t>
+      <c r="E45" s="9" t="inlineStr">
+        <is>
+          <t>메일함 규칙·자동 전달·위임 설정으로 대화 은닉과 메일 지속 수집</t>
+        </is>
+      </c>
+      <c r="F45" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 탈취한 메일함에 받은편지함 규칙·자동 전달·위임 권한을 추가해 보안 경고와 답장을 숨기고 메일을 계속 가로챌 수 있음
+- 사용자가 직접 만들 수 있는 정상 기능이라 보안 도구가 잘 보지 않고, 비밀번호를 바꿔도 규칙·전달·위임 설정은 남음</t>
         </is>
       </c>
       <c r="G45" s="9" t="inlineStr">
@@ -37788,7 +38713,16 @@
       <c r="P45" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="Q45" s="9" t="inlineStr"/>
+      <c r="Q45" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 새 받은편지함 규칙(삭제·이동·외부 전달), 외부 도메인 자동 전달, 메일함 위임·사칭 권한 추가를 실시간 경보(NIST SI-4, CCM LOG-05)
+- 송금·청구서·보안 경고 같은 키워드를 지우거나 옮기는 규칙과 같은 시점의 비정상 로그인 상관 분석(NIST AU-6, ISMS-P 2.9.5)
+■ 대응
+- 조직 외부 자동 전달을 기본 차단하고 예외는 승인제로 운영, 규칙·위임 변경 감사 로그 정기 점검(ISMS-P 2.9.5, CCM LOG-05)
+- 침해 대응 때 비밀번호 재설정과 함께 메일 규칙·전달·위임·연결 앱을 전수 점검·삭제</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="9" t="inlineStr">
@@ -37811,10 +38745,15 @@
           <t>감사 로그·조건부 액세스·MFA 정책 무력화</t>
         </is>
       </c>
-      <c r="E46" s="9" t="inlineStr"/>
-      <c r="F46" s="26" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Disabling audit logs, conditional access and MFA policies</t>
+      <c r="E46" s="9" t="inlineStr">
+        <is>
+          <t>감사 로그·조건부 액세스·MFA 정책 변경으로 신원 통제 무력화</t>
+        </is>
+      </c>
+      <c r="F46" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 관리 권한을 얻은 뒤 클라우드 감사 로그를 끄거나 조건부 액세스에 신뢰 위치를 추가하고 MFA 설정을 해제해 이후 활동이 탐지·차단되지 않게 할 수 있음
+- 직접 피해를 내지 않아 사고 경위에서 잘 드러나지 않고, 로그가 꺼진 기간의 활동은 사후 조사로도 복원하기 어려움</t>
         </is>
       </c>
       <c r="G46" s="9" t="inlineStr">
@@ -37861,7 +38800,16 @@
       <c r="P46" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="Q46" s="9" t="inlineStr"/>
+      <c r="Q46" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 감사 로그 비활성화·보존 기간 단축, 조건부 액세스 정책·신뢰 위치 변경, MFA 해제를 별도 채널로 즉시 경보(NIST SI-4·AU-12, CCM LOG-03)
+- 로그 수집이 끊긴 구간을 수집 파이프라인에서 감지하고 정책 변경 직후의 관리자 활동과 상관 분석
+■ 대응
+- 감사 로그를 관리자도 지울 수 없는 별도 저장소로 보내고 로그 설정 변경 권한 분리(NIST AU-9, ISMS-P 2.9.4)
+- 조건부 액세스·MFA 정책을 기준선으로 관리해 변경 시 이중 승인과 정기 대조(CIS 6.7, NIST CM-6, CCM IAM-13)</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="9" t="inlineStr">
@@ -37884,10 +38832,15 @@
           <t>장기 액세스 키·API 키·토큰 악용</t>
         </is>
       </c>
-      <c r="E47" s="9" t="inlineStr"/>
-      <c r="F47" s="26" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Abuse of long-lived access keys, API keys and tokens</t>
+      <c r="E47" s="9" t="inlineStr">
+        <is>
+          <t>MFA 없는 장기 액세스 키·API 키 하나로 고객 데이터·인프라 접근</t>
+        </is>
+      </c>
+      <c r="F47" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 코드·설정·연동 시스템에서 새거나 탈취한 장기 액세스 키·API 키·토큰으로 MFA 없이 클라우드·SaaS·원격 지원 인프라에 바로 접근할 수 있음
+- 키에 붙은 권한이 넓고 만료가 없어 한 번 새면 오래 쓰이며, 사람 로그인이 아니라 이상 로그인 탐지·MFA가 적용되지 않음</t>
         </is>
       </c>
       <c r="G47" s="9" t="inlineStr">
@@ -37934,7 +38887,16 @@
       <c r="P47" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="Q47" s="9" t="inlineStr"/>
+      <c r="Q47" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 키·토큰별 사용 출발지·호출 API·시간대 기준선을 두고 처음 보는 IP·국가·대량 조회를 경보, 노출이 확인되면 노출 시점 이후 사용 이력 조회
+- 저장소·이미지·공개 코드 사이트의 키 패턴 스캔, 공급업체 침해 공지 때 해당 연동 키 사용 내역 즉시 점검
+■ 대응
+- 장기 키를 단기 토큰·워크로드 신원으로 대체하고 남는 키는 권한 최소화·만료 설정·정기 교체(CIS 5.5, NIST IA-5(13)·AC-6·SC-12, ISMS-P 2.5.5·2.7.2, CCM IAM-14·IAM-05·CEK-12)
+- 서비스 간 인증에 출발지 제한·상호 인증을 더하고 비인간 신원 인벤토리로 소유자·용도 관리(NIST IA-9)</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="9" t="inlineStr">
@@ -37957,10 +38919,15 @@
           <t>비밀·자격증명 교체·폐기 실패</t>
         </is>
       </c>
-      <c r="E48" s="9" t="inlineStr"/>
-      <c r="F48" s="26" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Failure to rotate or revoke secrets and credentials</t>
+      <c r="E48" s="9" t="inlineStr">
+        <is>
+          <t>샌 비밀·퇴사자 키를 교체·폐기하지 않아 침해 뒤에도 재침투 허용</t>
+        </is>
+      </c>
+      <c r="F48" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 이미 유출됐거나 침해 대응에서 빠진 토큰·서비스 계정 비밀번호·서명 키가 계속 유효한 점을 이용해 대응이 끝난 뒤에도 다시 접근할 수 있음
+- 어떤 비밀이 어디에 쓰이는지 모르면 교체 대상을 빠뜨리기 쉽고, 퇴사자·협력사가 쓰던 키나 수년 전 유출된 비밀번호가 사고의 시작점이 됨</t>
         </is>
       </c>
       <c r="G48" s="9" t="inlineStr">
@@ -38007,7 +38974,16 @@
       <c r="P48" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="Q48" s="9" t="inlineStr"/>
+      <c r="Q48" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 침해 공지·유출 확인 이후에도 쓰이는 토큰·키를 식별하고 교체 완료 여부를 실제 사용 로그로 검증
+- 퇴사·계약 종료 인력과 연결된 키·토큰의 사용, 오랫동안 바뀌지 않은 서비스 계정 비밀번호를 정기 점검
+■ 대응
+- 비밀 인벤토리에 소유자·용도·만료일을 기록하고 정기 교체·자동 만료 적용(CIS 5.5, NIST IA-5·IA-5(13), ISMS-P 2.7.2, CCM CEK-12)
+- 침해 대응·퇴사 때 관련 비밀·서명 키를 전수 폐기·재발급하고 계정 비활성화(CIS 6.2, NIST AC-2(3), ISMS-P 2.5.1, CCM CEK-13·IAM-07)</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="9" t="inlineStr">
@@ -38030,10 +39006,15 @@
           <t>서비스 계정 악용·사람의 비인간 신원 사용</t>
         </is>
       </c>
-      <c r="E49" s="9" t="inlineStr"/>
-      <c r="F49" s="26" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Service account abuse and human use of NHIs</t>
+      <c r="E49" s="9" t="inlineStr">
+        <is>
+          <t>MFA 예외인 고권한 서비스 계정 탈취로 고객 DB·지원 시스템 장악</t>
+        </is>
+      </c>
+      <c r="F49" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 MFA가 없고 권한이 넓은 서비스 계정이나 사람이 대화형으로 쓰는 시스템 계정을 탈취해 고객 DB·지원 시스템·클라우드 관리 기능에 접근할 수 있음
+- 서비스 계정은 자동화 때문에 MFA·로그인 제한에서 빠지는 경우가 많고, 사람이 개인 브라우저에 그 자격증명을 저장하면 회사 통제 밖에서 털림</t>
         </is>
       </c>
       <c r="G49" s="9" t="inlineStr">
@@ -38080,7 +39061,16 @@
       <c r="P49" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="Q49" s="9" t="inlineStr"/>
+      <c r="Q49" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 서비스 계정의 대화형 로그인, 평소와 다른 출발지·시간대, 정해진 작업 밖의 API 호출을 경보
+- 서비스 계정 인벤토리에 없는 계정 사용, 한 서비스 계정이 여러 시스템에서 동시에 쓰이는 패턴 점검
+■ 대응
+- 서비스 계정 인벤토리로 소유자·용도·권한을 관리하고 대화형 로그인 금지·출발지 제한(CIS 5.5, NIST IA-9·AC-2, ISMS-P 2.5.1, CCM IAM-03)
+- 서비스 계정 권한을 작업 범위로 줄이고 관리자급 서비스 계정은 특권 계정으로 분리 관리(CIS 5.4, NIST AC-6, ISMS-P 2.5.5, CCM IAM-05)</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="9" t="inlineStr">
@@ -38103,10 +39093,15 @@
           <t>워크로드 ID 과다 권한·신뢰 설정 오류</t>
         </is>
       </c>
-      <c r="E50" s="9" t="inlineStr"/>
-      <c r="F50" s="26" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Overprivileged workload identities and trust misconfiguration</t>
+      <c r="E50" s="9" t="inlineStr">
+        <is>
+          <t>과다 권한 워크로드 역할·느슨한 신뢰 설정으로 클라우드 데이터 대량 접근</t>
+        </is>
+      </c>
+      <c r="F50" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 웹 서비스·CI 작업 같은 워크로드에서 메타데이터 서비스나 OIDC 신뢰로 역할 자격증명을 얻어, 그 역할에 붙은 넓은 권한으로 저장소·데이터에 접근할 수 있음
+- 워크로드 역할은 사람이 보지 않는 곳에서 자동으로 발급되고, 권한이 과다하면 애플리케이션 결함 하나가 대량 유출로 직결됨</t>
         </is>
       </c>
       <c r="G50" s="9" t="inlineStr">
@@ -38153,7 +39148,16 @@
       <c r="P50" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="Q50" s="9" t="inlineStr"/>
+      <c r="Q50" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 워크로드 역할 자격증명이 해당 인스턴스·작업 밖에서 쓰이는 경우, 평소와 다른 저장소 나열·대량 조회를 경보
+- OIDC 신뢰 정책의 조건(저장소·브랜치·환경) 누락과 와일드카드를 정기 점검
+■ 대응
+- 워크로드 역할을 작업별 최소 권한으로 나누고 데이터 접근은 별도 역할로 분리(CIS 6.8, NIST AC-6, ISMS-P 2.5.5, CCM IAM-05·IAM-15)
+- 메타데이터 서비스 보호 기능 적용과 신뢰 정책 기준선 관리(NIST CM-6·IA-9)</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="9" t="inlineStr">
@@ -38176,10 +39180,15 @@
           <t>SaaS 연동 앱 토큰 탈취와 연쇄 접근</t>
         </is>
       </c>
-      <c r="E51" s="9" t="inlineStr"/>
-      <c r="F51" s="26" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Theft of SaaS integration tokens and chained access</t>
+      <c r="E51" s="9" t="inlineStr">
+        <is>
+          <t>SaaS 연동 공급자의 OAuth 토큰 탈취로 여러 고객 조직 데이터 연쇄 접근</t>
+        </is>
+      </c>
+      <c r="F51" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 SaaS 연동 앱 공급자가 보관한 OAuth·리프레시 토큰을 탈취해 그 앱을 연결한 여러 조직의 SaaS·코드 저장소에 사용자 로그인 없이 접근할 수 있음
+- 토큰은 피해 조직의 MFA·로그인 정책을 거치지 않고, 연동 앱의 정상 API 호출처럼 보여 공급자 공지 전까지 알기 어려움</t>
         </is>
       </c>
       <c r="G51" s="9" t="inlineStr">
@@ -38226,7 +39235,16 @@
       <c r="P51" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="Q51" s="9" t="inlineStr"/>
+      <c r="Q51" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 연동 앱 토큰의 평소와 다른 출발지 IP·대량 조회·내보내기 API 호출을 경보, 연동 공급자 침해 공지 즉시 해당 앱 토큰 사용 이력 점검
+- 승인된 연동 앱 목록과 실제 토큰 발급 현황을 정기 대조
+■ 대응
+- 연동 앱 승인은 관리자 검토로 제한하고 권한 범위·토큰 수명 최소화, 미사용 연동 정기 정리(CIS 6.6, NIST AC-6, ISMS-P 2.5.5, CCM IAM-14)
+- 연동 공급자를 공급망으로 관리해 보안 요구 사항·침해 통지 의무를 계약에 넣고, 침해 시 토큰 전수 폐기 절차 준비(NIST SA-9·IA-9, ISMS-P 2.3.3, CCM STA-09)</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="9" t="inlineStr">
@@ -38249,10 +39267,15 @@
           <t>악성·과다 권한 OAuth 앱 등록·권한 부여</t>
         </is>
       </c>
-      <c r="E52" s="9" t="inlineStr"/>
-      <c r="F52" s="26" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Malicious or overprivileged OAuth app registration and grants</t>
+      <c r="E52" s="9" t="inlineStr">
+        <is>
+          <t>악성·과다 권한 OAuth 앱으로 사용자 MFA와 무관한 조직 데이터 지속 접근</t>
+        </is>
+      </c>
+      <c r="F52" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 탈취한 계정·관리 권한으로 OAuth 앱을 새로 만들거나 기존 앱에 높은 권한과 자격증명을 붙여 조직 전체 메일함·SaaS 데이터에 앱 명의로 접근할 수 있음
+- 앱 권한은 사용자 비밀번호·MFA 변경과 무관하게 유지되고, 정상 연동 앱처럼 보여 승인된 앱 목록을 따로 검토하지 않으면 드러나지 않음</t>
         </is>
       </c>
       <c r="G52" s="9" t="inlineStr">
@@ -38299,7 +39322,16 @@
       <c r="P52" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="Q52" s="9" t="inlineStr"/>
+      <c r="Q52" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 새 OAuth 앱 등록·고위험 권한 승인, 앱·서비스 주체에 역할·자격증명 추가를 실시간 경보(NIST AU-6)
+- 전체 메일함 접근 같은 테넌트 단위 권한을 가진 앱 목록을 정기 추출해 게시자·소유자 확인
+■ 대응
+- 앱 등록·동의를 관리자 승인으로 제한하고 검증된 게시자 앱만 허용(CIS 6.7, CCM IAM-15)
+- 앱 권한을 최소화하고 레거시·테스트 앱까지 포함해 정기 권한 검토·미사용 앱 삭제(CIS 6.8, NIST AC-6·AC-2, ISMS-P 2.5.5·2.5.6, CCM IAM-08)</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="9" t="inlineStr">
@@ -38322,10 +39354,15 @@
           <t>AI 에이전트 신원·위임 권한 악용</t>
         </is>
       </c>
-      <c r="E53" s="9" t="inlineStr"/>
-      <c r="F53" s="26" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Abuse of AI agent identity and delegated authority</t>
+      <c r="E53" s="9" t="inlineStr">
+        <is>
+          <t>AI 에이전트가 위임받은 사용자 토큰·연동 권한으로 데이터 노출</t>
+        </is>
+      </c>
+      <c r="F53" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 AI 에이전트가 사용자에게서 위임받은 토큰·연동 권한을 프롬프트 인젝션으로 조종하거나 연동 서버의 권한 격리 결함을 이용해 다른 저장소·조직의 데이터를 가져갈 수 있음
+- 에이전트는 사용자 권한 전체를 위임받는 경우가 많아 피해 범위가 그 권한에 좌우되고, 정상 도구 호출처럼 보여 기존 로그로 구분하기 어려움</t>
         </is>
       </c>
       <c r="G53" s="9" t="inlineStr">
@@ -38372,7 +39409,16 @@
       <c r="P53" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="Q53" s="9" t="inlineStr"/>
+      <c r="Q53" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 에이전트용 토큰·연동 계정의 호출 범위·대상 저장소·조직을 기준선과 비교해 평소와 다른 접근 경보
+- 에이전트 도구 호출 기록을 사용자 세션 로그와 구분해 남기고, 외부 콘텐츠 처리 직후의 쓰기·공개 작업 점검
+■ 대응
+- 에이전트 전용 신원을 두고 작업별 최소 범위·짧은 수명의 토큰만 위임(CIS 6.8, NIST AC-6·IA-9, ISMS-P 2.5.5, CCM IAM-05)
+- 연동 서버의 조직·테넌트 간 접근 통제를 검증하고 고위험 작업은 사람 승인 뒤 실행(NIST AC-3, CCM IAM-15)</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="9" t="inlineStr">
@@ -38395,10 +39441,15 @@
           <t>퇴사자·휴면·미사용 계정과 권한 미회수</t>
         </is>
       </c>
-      <c r="E54" s="9" t="inlineStr"/>
-      <c r="F54" s="26" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Orphaned, dormant and unrevoked accounts</t>
+      <c r="E54" s="9" t="inlineStr">
+        <is>
+          <t>퇴사자·휴면·미사용 계정과 회수되지 않은 권한으로 침투·무단 조회</t>
+        </is>
+      </c>
+      <c r="F54" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자나 퇴사자는 쓰지 않지만 활성 상태로 남은 VPN·메인테이너·클라우드 계정이나 퇴사 뒤에도 회수되지 않은 권한·키로 정상 사용자처럼 들어올 수 있음
+- 주인이 없는 계정은 이상 행위를 알아챌 사람이 없어 탐지가 늦고, MFA 없이 남은 오래된 비밀번호는 유출 비밀번호 하나로 열림</t>
         </is>
       </c>
       <c r="G54" s="9" t="inlineStr">
@@ -38445,7 +39496,16 @@
       <c r="P54" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="Q54" s="9" t="inlineStr"/>
+      <c r="Q54" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 오랫동안 로그인이 없던 계정의 갑작스러운 로그인, 퇴사·전보 처리된 사용자 명의 접근, 퇴사자와 연결된 키·토큰 사용을 경보
+- 인사 시스템의 재직 현황과 계정·권한 목록을 정기 대조해 회수 누락 식별
+■ 대응
+- 인사 변동과 연동한 계정·권한 자동 회수, 퇴사 당일 비활성화와 관련 키·토큰 폐기(CIS 6.2, NIST AC-2(3)·PS-4·PS-5, ISMS-P 2.2.5, CCM IAM-07·HRS-06)
+- 휴면 계정 자동 비활성화와 계정 관리 중앙화, 정기 접근 권한 검토(CIS 5.3·5.6, NIST AC-2, ISMS-P 2.5.1·2.5.6, CCM IAM-08)</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="9" t="inlineStr">
@@ -38468,10 +39528,15 @@
           <t>협력사·외주·게스트 계정 악용</t>
         </is>
       </c>
-      <c r="E55" s="9" t="inlineStr"/>
-      <c r="F55" s="26" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Abuse of vendor, contractor and guest accounts</t>
+      <c r="E55" s="9" t="inlineStr">
+        <is>
+          <t>협력사·외주 인력 계정과 외주 지원 창구를 거쳐 원청 시스템 침투</t>
+        </is>
+      </c>
+      <c r="F55" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 원청 시스템에 접근하는 협력사·외주 인력의 계정을 탈취하거나 외주 헬프데스크·IT 지원업체를 속여 원청 내부로 들어올 수 있음
+- 협력사 단말·절차는 원청이 직접 통제하지 못하고, 외부 인력 계정은 권한·만료 관리가 느슨해 대량 유출의 입구가 됨</t>
         </is>
       </c>
       <c r="G55" s="9" t="inlineStr">
@@ -38518,7 +39583,16 @@
       <c r="P55" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="Q55" s="9" t="inlineStr"/>
+      <c r="Q55" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 협력사·외주 계정의 접속 시간·출발지·접근 시스템을 계약 범위와 비교해 이상 접근 경보, 외주 헬프데스크의 재설정 이력 감사
+- 계약 만료·인력 교체 뒤에도 쓰이는 외부 인력 계정과 게스트 사용자 권한 정기 점검
+■ 대응
+- 외부 인력 계정은 승인 절차로 발급하고 접근 범위·기간을 계약에 맞춰 제한, 만료 시 즉시 회수(CIS 6.1·6.2, NIST PS-7·AC-2, ISMS-P 2.3.3·2.3.4, CCM IAM-06·IAM-08)
+- 협력사·외주 업체에 MFA·관리 단말 사용과 신원 확인 절차 준수를 계약으로 요구하고 이행 점검(NIST SA-9·AC-20, CCM STA-09)</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="9" t="inlineStr">
@@ -38541,10 +39615,15 @@
           <t>내부자의 정상 권한 오남용·반출</t>
         </is>
       </c>
-      <c r="E56" s="9" t="inlineStr"/>
-      <c r="F56" s="26" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Insider misuse of legitimate access</t>
+      <c r="E56" s="9" t="inlineStr">
+        <is>
+          <t>내부자가 정상 권한으로 고객·내부 데이터를 대량 조회·반출</t>
+        </is>
+      </c>
+      <c r="F56" s="9" t="inlineStr">
+        <is>
+          <t>- 내부자는 업무상 가진 DB·클라우드·보고서 접근 권한이나 재직 중 확보한 키로 고객·임직원 정보를 대량으로 내려받아 팔거나 공개·갈취에 쓸 수 있음
+- 정상 권한 안의 행위라 접근 통제가 막지 못하고, 조회량·시간대 이상을 따로 분석하지 않으면 수개월 동안 드러나지 않음</t>
         </is>
       </c>
       <c r="G56" s="9" t="inlineStr">
@@ -38591,7 +39670,16 @@
       <c r="P56" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="Q56" s="9" t="inlineStr"/>
+      <c r="Q56" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 개인별 조회·내려받기 양과 시간대 기준선을 두고 대량 조회·내보내기·외부 저장 장치 사용을 경보(NIST AU-6, ISMS-P 2.9.5, CCM LOG-05)
+- 퇴사 예정·징계 대상자처럼 위험 신호가 있는 사용자의 접근을 내부자 위협 프로그램에서 집중 점검(NIST PM-12)
+■ 대응
+- 직무 기반 최소 권한과 직무 분리, 고객정보 대량 조회는 승인·사유 기록 뒤 허용(CIS 6.8, NIST AC-6, ISMS-P 2.5.6, CCM IAM-04·IAM-05)
+- 퇴사 때 접근 권한·키를 즉시 회수하고 정기 접근 권한 검토(NIST PS-4, ISMS-P 2.2.5)</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="9" t="inlineStr">
@@ -38614,10 +39702,15 @@
           <t>외부의 내부자 매수·포섭</t>
         </is>
       </c>
-      <c r="E57" s="9" t="inlineStr"/>
-      <c r="F57" s="26" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Bribed or recruited insiders</t>
+      <c r="E57" s="9" t="inlineStr">
+        <is>
+          <t>고객지원·협력사 인력 매수로 정상 조회 권한을 통한 고객 정보 유출</t>
+        </is>
+      </c>
+      <c r="F57" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 고객 데이터 조회 권한을 가진 고객지원·협력사 인력을 돈으로 매수하거나 내부자로 모집해 정상 업무 화면으로 고객 정보를 빼내거나 사내 접근을 얻을 수 있음
+- 정상 계정의 정상 업무 조회라 기술 통제를 우회하고, 빼낸 정보는 회사를 사칭한 2차 사기로 이어져 고객 피해가 커짐</t>
         </is>
       </c>
       <c r="G57" s="9" t="inlineStr">
@@ -38664,7 +39757,16 @@
       <c r="P57" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="Q57" s="9" t="inlineStr"/>
+      <c r="Q57" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 고객지원 인력의 조회 건수·대상·시간대 기준선을 두고 담당 티켓과 무관한 고객 조회, 신분증 이미지 대량 열람을 경보(NIST AU-6, ISMS-P 2.9.5, CCM LOG-05)
+- 내부자 모집 게시물·매수 제안 신고 창구를 운영하고 신고된 인력의 접근 이력 점검(NIST PM-12)
+■ 대응
+- 고객정보 조회는 티켓·사유와 묶어 필요한 항목만 보이게 하고 민감 정보는 마스킹(CIS 6.8, ISMS-P 2.5.6, CCM IAM-04)
+- 외주·해외 지원 인력 채용 검증과 역할·책임 명시, 매수 제안 신고 의무 교육(NIST PS-3, CCM HRS-09)</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="9" t="inlineStr">
@@ -38687,10 +39789,15 @@
           <t>위장 취업(도용·위조 신원으로 정규 계정 획득)</t>
         </is>
       </c>
-      <c r="E58" s="9" t="inlineStr"/>
-      <c r="F58" s="26" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Fraudulent hiring with stolen or fake identities</t>
+      <c r="E58" s="9" t="inlineStr">
+        <is>
+          <t>도용·위조 신원으로 원격 IT 인력 위장 취업해 정규 계정 획득</t>
+        </is>
+      </c>
+      <c r="F58" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 도용·위조 신원과 AI로 보정한 사진으로 화상 면접·신원 조회를 통과해 원격 IT 인력으로 채용되고 회사가 지급한 노트북과 정규 계정을 받을 수 있음
+- 채용 절차로 정상 발급된 계정이라 접근 통제가 막지 않고, 대리 접속용 노트북 농장으로 근무 위치를 속여 데이터 탈취·갈취로 이어지기도 함</t>
         </is>
       </c>
       <c r="G58" s="9" t="inlineStr">
@@ -38737,7 +39844,17 @@
       <c r="P58" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="Q58" s="9" t="inlineStr"/>
+      <c r="Q58" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 지급 노트북의 원격 접속 도구 설치·해외 IP 접속·배송지와 다른 접속 위치, 입사 직후 대량 접근을 경보
+- 면접자와 근무자의 동일인 여부 재확인, 같은 연락처·계좌·주소를 쓰는 지원자 점검
+■ 대응
+- 원격 채용에 대면 또는 강한 신원 확인 절차를 두고 신분증·주소 진위를 검증(NIST IA-12·PS-3, CCM HRS-09)
+- 입사 초기 권한은 최소로 시작해 단계적으로 부여하고 접근 권한 부여 절차 준수(CIS 6.1, ISMS-P 2.5.1, CCM IAM-06)
+- 위장 취업 정황을 내부자 위협 프로그램 점검 대상에 포함(NIST PM-12)</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="9" t="inlineStr">
@@ -38760,10 +39877,15 @@
           <t>고객 계정 대량 크리덴셜 스터핑</t>
         </is>
       </c>
-      <c r="E59" s="9" t="inlineStr"/>
-      <c r="F59" s="26" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Large-scale credential stuffing against customer accounts</t>
+      <c r="E59" s="9" t="inlineStr">
+        <is>
+          <t>유출 아이디·비밀번호 자동 대입으로 고객 계정 대량 탈취</t>
+        </is>
+      </c>
+      <c r="F59" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 다른 곳에서 유출된 아이디·비밀번호 목록을 여러 IP로 나눠 고객 로그인에 자동 대입해 비밀번호를 재사용한 수만~수십만 계정에 한꺼번에 로그인할 수 있음
+- 서비스 자체가 뚫리지 않아도 개인정보 노출·부정 결제가 생기고, 정상 로그인과 섞여 단시간 대량 시도를 따로 탐지하지 않으면 수개월간 이어짐</t>
         </is>
       </c>
       <c r="G59" s="9" t="inlineStr">
@@ -38810,7 +39932,16 @@
       <c r="P59" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="Q59" s="9" t="inlineStr"/>
+      <c r="Q59" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 같은 IP·ASN·기기 지문의 단시간 대량 로그인, 로그인 성공률 급변, 처음 보는 기기의 개인정보 조회·배송지 변경을 실시간 탐지(NIST SI-4·AC-7)
+- 유출 자격증명 목록과 고객 계정 대조, 자동화 도구 지문으로 봇 트래픽 식별
+■ 대응
+- 고객 계정에 MFA·패스키를 제공하고 위험 기반 추가 인증 적용, 결제·개인정보 변경은 재인증(CIS 6.3, NIST IA-2(2), ISMS-P 2.5.3, CCM IAM-13)
+- 로그인 시도 제한·봇 차단과 유출 비밀번호 사용 금지, 로그인 뒤 개인정보 화면 마스킹(NIST AC-7·IA-5(1), ISMS-P 2.5.4)</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="9" t="inlineStr">
@@ -38833,10 +39964,15 @@
           <t>통신 가입자 인증 체계 침해(유심 인증키·불법 기지국)</t>
         </is>
       </c>
-      <c r="E60" s="9" t="inlineStr"/>
-      <c r="F60" s="26" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Compromise of telecom subscriber authentication (SIM keys, rogue base stations)</t>
+      <c r="E60" s="9" t="inlineStr">
+        <is>
+          <t>유심 인증키 유출·불법 기지국으로 휴대폰 기반 인증 체계 무력화</t>
+        </is>
+      </c>
+      <c r="F60" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 통신사 가입자 인증 서버에서 유심 인증키 등 가입자 정보를 빼내거나 통신사 인증서를 가진 불법 초소형 기지국으로 문자·ARS 인증값을 가로챌 수 있음
+- 휴대폰 문자·본인확인에 기대는 모든 서비스가 함께 영향을 받고, 가입자 개인이 막을 방법이 없어 통신사 단위의 대응이 필요함</t>
         </is>
       </c>
       <c r="G60" s="9" t="inlineStr">
@@ -38883,7 +40019,17 @@
       <c r="P60" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="Q60" s="9" t="inlineStr"/>
+      <c r="Q60" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 가입자 인증 서버·관리망의 비정상 로그인과 대량 조회, 등록되지 않은 기지국·펨토셀 접속을 실시간 탐지(NIST SI-4)
+- 같은 기지국을 거친 결제 인증 급증처럼 지역·장비 단위의 이상 거래 분석
+■ 대응
+- 가입자 인증키를 하드웨어 보안 모듈 등으로 보호하고 침해 시 키 교체·유심 교체 절차 준비(NIST SC-12, ISMS-P 2.7.2, CCM CEK-19)
+- 기지국 인증서 수명 단축과 접속 인가 통제, 인증 신호 구간 암호화(NIST SC-8, CCM IAM-15)
+- 서비스 제공자는 문자 단독 본인확인·결제 인증을 줄이고 피싱 저항 인증을 병행(ISMS-P 2.5.3)</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="9" t="inlineStr">
@@ -38906,10 +40052,15 @@
           <t>명의 도용·합성 신원 계정 개설</t>
         </is>
       </c>
-      <c r="E61" s="9" t="inlineStr"/>
-      <c r="F61" s="26" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Account opening with stolen or synthetic identities</t>
+      <c r="E61" s="9" t="inlineStr">
+        <is>
+          <t>도용 신분증·합성 신원으로 금융 계좌·서비스 계정 부정 개설</t>
+        </is>
+      </c>
+      <c r="F61" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 훔친 신분증이나 생성형 AI로 만든 위조 신분증·합성 신원으로 비대면 계좌·서비스 계정을 개설해 대출 사기·자금 세탁에 쓸 수 있음
+- 개설 시점의 신원 확인만 통과하면 정상 고객으로 취급되고, 실제 명의자는 대출·피해가 생긴 뒤에야 알게 됨</t>
         </is>
       </c>
       <c r="G61" s="9" t="inlineStr">
@@ -38956,7 +40107,16 @@
       <c r="P61" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="Q61" s="9" t="inlineStr"/>
+      <c r="Q61" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 같은 신분증·얼굴·기기·연락처로 여러 계좌·계정을 여는 패턴, 개설 직후 대출 신청·고액 이체를 이상 거래로 탐지
+- 신분증 이미지 재사용·편집 흔적 점검과 공개 적신호 지표 대조
+■ 대응
+- 비대면 개설의 신원 확인을 신분증 진위·명의자 확인·기기 정보 등 여러 근거로 교차 검증(NIST IA-12, ISMS-P 2.5.2)
+- 고객별 고유 신원 관리와 외부 사용자 식별·인증 기준 적용(NIST IA-8, CCM IAM-12)</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="9" t="inlineStr">
@@ -38979,10 +40139,15 @@
           <t>eKYC·얼굴 인증 우회(딥페이크·주입 공격)</t>
         </is>
       </c>
-      <c r="E62" s="9" t="inlineStr"/>
-      <c r="F62" s="26" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Bypassing eKYC and face verification (deepfake, injection)</t>
+      <c r="E62" s="9" t="inlineStr">
+        <is>
+          <t>딥페이크 얼굴·영상으로 eKYC·생체 본인확인을 통과해 계좌 접근</t>
+        </is>
+      </c>
+      <c r="F62" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 악성 앱으로 수집한 피해자 얼굴 영상이나 AI 얼굴 바꾸기로 만든 딥페이크를 얼굴 인식·영상 본인확인에 넣어 남의 명의로 인증을 통과할 수 있음
+- 생체 정보는 비밀번호처럼 바꿀 수 없어 한 번 털리면 반복 악용되고, 카메라 입력을 바꿔치기하는 주입 공격은 화면만 봐서는 구분하기 어려움</t>
         </is>
       </c>
       <c r="G62" s="9" t="inlineStr">
@@ -39029,7 +40194,16 @@
       <c r="P62" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="Q62" s="9" t="inlineStr"/>
+      <c r="Q62" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 얼굴 인증 시도의 카메라 입력 이상(가상 카메라·에뮬레이터), 같은 얼굴 데이터의 여러 계정 사용, 인증 직후 고액 이체를 탐지
+- 얼굴·신분증을 요구하는 사칭 앱 설치 정황(공식 앱 장터 밖 설치)과 연계 분석
+■ 대응
+- 실제 사람 여부를 판별하는 생체 검사와 주입 공격 탐지를 적용하고 얼굴 인증 단독으로 고위험 거래를 허용하지 않음(NIST IA-12, ISMS-P 2.5.3, CCM IAM-13)
+- 본인확인에 등록 주소·연락처로 보낸 확인 코드 등 다른 근거를 더해 교차 검증(NIST IA-12(5))</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="9" t="inlineStr">
@@ -39052,10 +40226,15 @@
           <t>계정 장악 기반 금전 사기(BEC·송금·사칭 게시)</t>
         </is>
       </c>
-      <c r="E63" s="9" t="inlineStr"/>
-      <c r="F63" s="26" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Account-takeover fraud (BEC, payment and impersonation)</t>
+      <c r="E63" s="9" t="inlineStr">
+        <is>
+          <t>장악한 메일·SNS·금융 계정으로 송금 사기·사칭 게시·부정 결제</t>
+        </is>
+      </c>
+      <c r="F63" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 장악한 업무 메일·소셜 미디어·금융·고객 계정으로 거래처 송금을 가로채거나 사칭 게시물을 올리고 결제 수단·가상자산을 빼낼 수 있음
+- 정상 계정과 정상 채널로 지시·거래가 이뤄져 피해자가 의심하기 어렵고, 송금·가상자산 이체는 되돌리기 어려워 피해가 바로 확정됨</t>
         </is>
       </c>
       <c r="G63" s="9" t="inlineStr">
@@ -39102,7 +40281,16 @@
       <c r="P63" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="Q63" s="9" t="inlineStr"/>
+      <c r="Q63" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 메일함 새 규칙·외부 전달과 거래처 계좌 변경 요청, 공식 계정의 비정상 로그인·게시를 연계 탐지(NIST SI-4)
+- 휴대폰 개통·유심 변경 직후의 금융·가상자산 계정 로그인, 인증 직후 고액 이체·출금을 이상 거래로 탐지
+■ 대응
+- 메일·공식 소셜 미디어·금융 계정에 피싱 저항 MFA를 적용하고 문자 단독 인증을 줄임(CIS 6.3, NIST IA-2(1), ISMS-P 2.5.3, CCM IAM-13)
+- 송금·계좌 변경은 사전 등록 채널로 콜백 확인하고 이중 승인, BEC·딥페이크 사칭 사례 교육(NIST AT-2(3))</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="9" t="inlineStr">
@@ -39125,10 +40313,15 @@
           <t>신원 장악 후 랜섬웨어·파괴(도메인·테넌트 전체)</t>
         </is>
       </c>
-      <c r="E64" s="9" t="inlineStr"/>
-      <c r="F64" s="26" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Ransomware and destruction after identity takeover</t>
+      <c r="E64" s="9" t="inlineStr">
+        <is>
+          <t>도메인·IdP 관리 권한 장악 뒤 전사 랜섬웨어·백업 삭제</t>
+        </is>
+      </c>
+      <c r="F64" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 헬프데스크 사칭·MFA 없는 원격 접속·디렉터리 취약점으로 도메인·IdP·클라우드 관리 권한을 얻은 뒤 전사 시스템을 암호화하고 백업·클라우드 자원을 지울 수 있음
+- 관리 권한 자체가 배포·삭제 수단이 되어 몇 시간 만에 조직 전체가 멈추고, 같은 권한으로 백업까지 지우면 복구가 크게 늦어짐</t>
         </is>
       </c>
       <c r="G64" s="9" t="inlineStr">
@@ -39175,7 +40368,16 @@
       <c r="P64" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="Q64" s="9" t="inlineStr"/>
+      <c r="Q64" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 도메인·IdP·클라우드 관리 권한의 새 부여·비정상 사용, 그룹 정책·하이퍼바이저 대량 작업, 백업 삭제·보존 설정 변경을 실시간 경보(NIST SI-4, CCM LOG-03)
+- 원격 접속 신규 로그인 뒤 짧은 시간 안에 이어지는 권한 상승·횡적 이동을 상관 분석
+■ 대응
+- 도메인·IdP·백업 관리 권한을 전용 관리자 계정과 피싱 저항 MFA로 분리하고 관리 계층 간 자격증명 재사용 금지(CIS 5.4·6.5, NIST AC-6(5), ISMS-P 2.5.5, CCM IAM-10)
+- 관리자 권한으로도 지울 수 없는 분리·불변 백업을 두고 복구 훈련(NIST CP-9)</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="9" t="inlineStr">
@@ -39198,10 +40400,15 @@
           <t>계정 기반 대량 데이터 탈취·갈취</t>
         </is>
       </c>
-      <c r="E65" s="9" t="inlineStr"/>
-      <c r="F65" s="26" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Mass data theft and extortion via identities</t>
+      <c r="E65" s="9" t="inlineStr">
+        <is>
+          <t>정상 계정·토큰으로 SaaS·DB를 대량 조회해 데이터 탈취·갈취</t>
+        </is>
+      </c>
+      <c r="F65" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 탈취하거나 매수·위조한 계정·토큰·서명키로 SaaS·고객 DB·코드 저장소에 정상 사용자처럼 들어가 대량의 데이터를 내려받고 공개를 빌미로 갈취할 수 있음
+- 정상 권한의 조회·내보내기라 데이터 유출 방지 통제를 통과하기 쉽고, 조회량 이상을 보지 않으면 수개월 뒤 외부 공개·통지로 알게 됨</t>
         </is>
       </c>
       <c r="G65" s="9" t="inlineStr">
@@ -39248,7 +40455,16 @@
       <c r="P65" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="Q65" s="9" t="inlineStr"/>
+      <c r="Q65" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 계정·토큰·연동 앱별 조회량·내보내기·API 호출 기준선을 두고 대량 조회·일괄 내보내기·새 출발지 접근을 경보(NIST SI-4·AU-6, ISMS-P 2.9.5, CCM LOG-05)
+- 데이터 플랫폼·SaaS 로그를 중앙에 모아 로그인 출발지·인증 방식(MFA 여부)과 조회 행위를 함께 분석
+■ 대응
+- 데이터 접근 권한을 역할별 최소 권한으로 줄이고 대량 조회·내보내기는 승인·속도 제한 적용(CIS 6.8, NIST AC-6, CCM IAM-05)
+- 데이터 플랫폼·SaaS에 MFA와 접속 허용 목록을 필수로 두고 고객정보 화면 마스킹·조회 기록 보존</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="9" t="inlineStr">
@@ -39271,10 +40487,15 @@
           <t>계정 접근 차단·관리자 축출과 계정 연동 파괴</t>
         </is>
       </c>
-      <c r="E66" s="9" t="inlineStr"/>
-      <c r="F66" s="26" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Account access removal and admin lockout</t>
+      <c r="E66" s="9" t="inlineStr">
+        <is>
+          <t>관리자 계정 삭제·자격증명 변경으로 대응 차단과 연동 계정 파괴</t>
+        </is>
+      </c>
+      <c r="F66" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 장악한 관리 권한으로 관리자 계정을 지우거나 비밀번호·인증 수단을 바꿔 피해 조직의 대응을 막고, 연결된 계정·기기의 데이터를 원격으로 지울 수 있음
+- 침해 대응에 필요한 관리자 접근이 먼저 사라져 복구가 늦어지고, 별도 긴급 계정이 없으면 공급업체 지원에 기대야 함</t>
         </is>
       </c>
       <c r="G66" s="9" t="inlineStr">
@@ -39321,7 +40542,16 @@
       <c r="P66" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="Q66" s="9" t="inlineStr"/>
+      <c r="Q66" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 관리자 계정 삭제·비활성화, 관리자 비밀번호·인증 수단 일괄 변경, 대량 계정 삭제·원격 초기화 명령을 실시간 경보
+- 긴급 계정 사용 시 즉시 경보하고 정기 로그인 시험으로 사용 가능 여부 확인
+■ 대응
+- 일상 관리와 분리된 긴급(break-glass) 계정을 오프라인 보관 자격증명·하드웨어 키로 유지하고 특권 계정 사용을 감사(CIS 5.4, NIST AC-2(7), ISMS-P 2.5.5, CCM IAM-10)
+- 계정·설정 백업을 두고 사고 대응 절차에 관리자 접근 상실 시나리오를 포함(NIST CP-9·IR-4)</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="9" t="inlineStr">
@@ -39344,10 +40574,15 @@
           <t>공급업체·플랫폼 경유 고객 계정 연쇄 탈취</t>
         </is>
       </c>
-      <c r="E67" s="9" t="inlineStr"/>
-      <c r="F67" s="26" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Chained account compromise across vendors and customers</t>
+      <c r="E67" s="9" t="inlineStr">
+        <is>
+          <t>공급업체·플랫폼 신원 침해가 그 서비스를 쓰는 고객 계정으로 연쇄 확산</t>
+        </is>
+      </c>
+      <c r="F67" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 IdP·원격 지원·CI/CD·SaaS 연동 공급업체의 직원 계정이나 고객용 토큰·키를 장악해 그 서비스를 믿는 여러 고객 조직의 계정과 데이터로 옮겨 갈 수 있음
+- 고객은 공급업체 내부를 볼 수 없어 공지가 나와야 알게 되고, 고객마다 토큰·비밀을 교체해야 해 한 번의 침해가 수많은 조직의 대응으로 번짐</t>
         </is>
       </c>
       <c r="G67" s="9" t="inlineStr">
@@ -39394,7 +40629,16 @@
       <c r="P67" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="Q67" s="9" t="inlineStr"/>
+      <c r="Q67" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 공급업체 침해 공지·보안 권고를 구독해 공지 즉시 해당 서비스 토큰·연동 키·지원 접근 이력 점검(NIST IR-4)
+- 공급업체 지원 인력·원격 지원 도구의 고객 환경 접근을 별도로 감사하고 연동 토큰의 새 출발지 사용을 경보
+■ 대응
+- 신원·원격 지원·CI/CD·연동 공급업체를 핵심 공급망으로 분류해 보안 요구 사항 계약과 정기 평가(NIST SA-9·SR-6, ISMS-P 2.3.3, CCM STA-09)
+- 공급업체에 맡긴 비밀·토큰 목록을 유지해 침해 때 전수 교체하고, 공급업체 특권 접근은 고객 승인 아래에서만 허용(CIS 6.6, CCM IAM-11)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A2:Q67"/>
@@ -40084,7 +41328,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="27" t="inlineStr">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>신원 유형·ID 환경별 요약 — 실제 사고 기준(한 사고가 여러 유형·환경에 걸치면 각각 집계)</t>
         </is>
@@ -40765,7 +42009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:F96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -40791,13 +42035,1985 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="28" t="inlineStr">
-        <is>
-          <t>작성 예정 — data/scenarios.yaml이 아직 없음</t>
+      <c r="A4" s="27" t="inlineStr">
+        <is>
+          <t>SCN-01. 헬프데스크 사칭 — 전화 한 통에서 IdP 관리 권한·하이퍼바이저 암호화까지</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="28" t="inlineStr">
+        <is>
+          <t>개요</t>
+        </is>
+      </c>
+      <c r="B5" s="29" t="inlineStr">
+        <is>
+          <t>기술 통제를 뚫지 않고 헬프데스크 절차로 비밀번호·MFA를 넘겨받아 IdP 관리 권한과 하이퍼바이저 암호화까지 간 흐름. 2023~2025년 대형 사고(MGM·Clorox·M&amp;S)에서 반복된 시작점이며, 재설정 전 신원 확인 절차가 가장 싼 차단 지점이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="28" t="inlineStr">
+        <is>
+          <t>근거 사고</t>
+        </is>
+      </c>
+      <c r="B6" s="29" t="inlineStr">
+        <is>
+          <t>IDI-005 MGM Resorts 랜섬웨어(헬프데스크 사칭으로 관리자 계정 확보)(2023-09) · IDI-009 Clorox 침해(외주 헬프데스크가 확인 없이 비밀번호·MFA 재설정)(2023-08) · IDI-010 Marks &amp; Spencer 랜섬웨어(협력사 대상 직원 사칭으로 비밀번호 재설정)(2025-04) · IDI-008 Scattered Spider 합동 권고(헬프데스크 사칭·SIM 스와핑·MFA 장치 등록)(2023-11) · IDI-007 Okta 고객 대상 헬프데스크 사칭·교차 테넌트 사칭(인바운드 페더레이션 악용)(2023-08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="28" t="inlineStr">
+        <is>
+          <t>참조</t>
+        </is>
+      </c>
+      <c r="B7" s="29" t="inlineStr">
+        <is>
+          <t>ATT&amp;CK G1015 · S1068</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>공격 단계</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>IDT-ID</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>세부위협</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>행위</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>탐지 포인트</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>초기 침투</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>IDT-SE-02.1</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>헬프데스크 사칭으로 비밀번호·MFA 재설정</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>LinkedIn에서 찾은 직원을 사칭해 IT 헬프데스크에 전화로 계정 접근을 요청(MGM), 협력사를 상대로 한 사칭으로 직원 비밀번호를 재설정받음(M&amp;S)</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>헬프데스크 티켓의 신원 확인 기록과 IdP 비밀번호·MFA 재설정 이벤트 대조</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>초기 침투</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>IDT-LC-01.2</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>협력사·외주·게스트 계정 악용</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>외주 헬프데스크가 여러 차례 걸려 온 전화에 신원 확인 없이 Okta 비밀번호와 Microsoft MFA를 재설정(Clorox 소송 주장)</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>외주 헬프데스크의 특권·다수 계정 재설정 이력 감사, 재설정 직후 새 위치 로그인 경보</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>지속성</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>IDT-PE-02.2</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>MFA 장치·인증 수단 추가 등록</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>MFA를 공격자 장치로 옮기게 하거나 계정을 얻은 뒤 자체 MFA 장치를 등록해 접근 유지(Scattered Spider 합동 권고)</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>새 MFA 장치 등록을 사용자·보안팀에 동시 알림, 재설정 직후 등록 여부 상관 분석</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>권한 상승</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>IDT-DI-03.2</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>IdP 관리 권한 장악·테넌트 설정 변조(외부 IdP·페더레이션 추가)</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>Okta·Azure 관리 권한 확보(MGM), 다른 사례에서는 최고 관리자 MFA를 모두 초기화하게 한 뒤 두 번째 IdP를 사칭 앱으로 구성해 다른 사용자 명의로 앱에 접근(Okta 고객)</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>외부 IdP·인바운드 페더레이션 추가와 최고 관리자 MFA 초기화를 실시간 고위험 경보</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>영향</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>IDT-IM-02</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>신원 장악 후 랜섬웨어·파괴(도메인·테넌트 전체)</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>ALPHV 랜섬웨어로 약 100대의 ESXi 하이퍼바이저를 암호화, 운영이 열흘가량 마비되고 약 1억 달러 영업 손실(MGM)</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>IdP 관리자 활동과 하이퍼바이저 관리 계정의 대량 작업을 상관 분석</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="49" customHeight="1">
+      <c r="A14" s="30" t="inlineStr">
+        <is>
+          <t>초크</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>· IDT-SE-02.1 — 특권 계정은 헬프데스크 재설정 대상에서 빼고, 일반 재설정도 영상 대면·관리자 승인 등 강한 신원 확인 뒤에만 허용(외주 계약에 절차 명시)
+· IDT-PE-02.2 — MFA 재등록에 기존 강한 인증 수단 확인을 요구하고 새 장치 등록을 즉시 알림
+· IDT-DI-03.2 — 외부 IdP·페더레이션 추가와 최고 관리자 MFA 초기화에 다중 승인</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="27" t="inlineStr">
+        <is>
+          <t>SCN-02. 토큰 서명 키 탈취·위조 — 비밀번호·MFA 없이 임의 사용자로 클라우드 메일 접근</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="28" t="inlineStr">
+        <is>
+          <t>개요</t>
+        </is>
+      </c>
+      <c r="B17" s="29" t="inlineStr">
+        <is>
+          <t>신원 체계의 열쇠인 토큰 서명 키·인증서를 손에 넣으면 비밀번호·MFA와 무관하게 임의 사용자로 인증된다. 온프레미스 페더레이션 서버(NOBELIUM의 FoggyWeb·Golden SAML·MagicWeb)와 IdP 공급업체 서명 키(Storm-0558) 두 경로가 모두 실제로 쓰였다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="28" t="inlineStr">
+        <is>
+          <t>근거 사고</t>
+        </is>
+      </c>
+      <c r="B18" s="29" t="inlineStr">
+        <is>
+          <t>IDI-025 FoggyWeb — AD FS 토큰 서명 인증서·구성 탈취 백도어(2021-09) · IDI-027 SolarWinds 침해 이후 클라우드 장악(Golden SAML·페더레이션 신뢰·앱 자격증명 추가)(2020-12) · IDI-024 MagicWeb — AD FS 서버 인증 백도어(2022-08) · IDI-026 Storm-0558 Microsoft 계정 서명 키 탈취와 토큰 위조(정부기관 메일 열람)(2023-07)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="28" t="inlineStr">
+        <is>
+          <t>참조</t>
+        </is>
+      </c>
+      <c r="B19" s="29" t="inlineStr">
+        <is>
+          <t>ATT&amp;CK G0016 · C0024 · S0661</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>공격 단계</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>IDT-ID</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>세부위협</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>행위</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>탐지 포인트</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>지속성</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>IDT-DI-04</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>인증 모듈·페더레이션 서버 백도어(AD FS·DC 인증 패치)</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>장악한 AD FS 서버에 FoggyWeb을 상주시켜 구성 DB와 토큰 서명·복호화 인증서를 원격으로 빼냄(FoggyWeb)</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>페더레이션 서버의 비정상 모듈 로드·구성 DB 접근을 무결성 감시로 탐지</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>자격증명 접근</t>
+        </is>
+      </c>
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t>IDT-TS-03.2</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>SAML 토큰 위조(Golden SAML)</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>탈취한 AD FS 토큰 서명 인증서로 임의 사용자의 SAML 토큰을 위조(SolarWinds 이후 클라우드 장악)</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>IdP 발급 기록이 없는 SAML 토큰 로그인을 클라우드 로그와 대조</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>지속성</t>
+        </is>
+      </c>
+      <c r="C23" s="11" t="inlineStr">
+        <is>
+          <t>IDT-DI-03.2
+IDT-PE-02.1</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>IdP 관리 권한 장악·테넌트 설정 변조(외부 IdP·페더레이션 추가)
+백도어 계정 생성·자격증명 추가</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>신뢰 도메인을 추가하거나 기존 애플리케이션·서비스 주체에 자격증명을 추가해 클라우드 자원에 지속 접근(SolarWinds 이후 클라우드 장악)</t>
+        </is>
+      </c>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>페더레이션 도메인 추가·서비스 주체 자격증명 추가를 실시간 고위험 경보</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>지속성</t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>IDT-DI-04</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>인증 모듈·페더레이션 서버 백도어(AD FS·DC 인증 패치)</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>AD FS 서버의 정상 DLL을 MagicWeb으로 바꿔 특수한 인증서가 든 토큰을 내면 어떤 사용자로든 인증되게 함(MagicWeb)</t>
+        </is>
+      </c>
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>인증 서버 DLL의 해시·서명 무결성 점검</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>자격증명 접근</t>
+        </is>
+      </c>
+      <c r="C25" s="11" t="inlineStr">
+        <is>
+          <t>IDT-TS-03.3
+IDT-DI-03.1</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>IdP·서비스 서명 키 탈취와 토큰·쿠키 위조
+IdP·인증 서비스 공급업체 침해</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>공급업체 경로로는 Microsoft 소비자 계정 서명 키로 인증 토큰을 위조했고 토큰 검증 결함으로 기업용 토큰 검증에도 통과(Storm-0558)</t>
+        </is>
+      </c>
+      <c r="F25" s="9" t="inlineStr">
+        <is>
+          <t>토큰의 서명 키·발급자 불일치 로그인 탐지, 공급업체 침해 공지 즉시 테넌트 감사 로그 점검</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>수집</t>
+        </is>
+      </c>
+      <c r="C26" s="11" t="inlineStr">
+        <is>
+          <t>IDT-IM-03</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>계정 기반 대량 데이터 탈취·갈취</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>Microsoft 365 메일 등 클라우드 자원에 지속 접근(SolarWinds 이후 클라우드 장악), 미 국무부 등 약 25개 조직의 Exchange Online·Outlook.com 메일에 접근(Storm-0558)</t>
+        </is>
+      </c>
+      <c r="F26" s="9" t="inlineStr">
+        <is>
+          <t>메일함 접근 감사 로그에서 평소와 다른 앱·토큰 기반 접근 주체 점검</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="64" customHeight="1">
+      <c r="A27" s="30" t="inlineStr">
+        <is>
+          <t>초크</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>· IDT-DI-04 — 페더레이션·인증 서버를 도메인 컨트롤러와 같은 최상위 계층으로 관리하고 관리 접근 분리, 파일·모듈 무결성 감시
+· IDT-TS-03.2 — 토큰 서명 키를 하드웨어 보안 모듈에 보관하고 IdP 발급 기록과 클라우드 로그인을 대조
+· IDT-DI-03.1 — IdP 공급업체를 핵심 공급망으로 관리하고 메일 접근 감사 로그를 확보해 공급업체 키가 털려도 이상 접근을 찾게 함
+· IDT-DI-03.2 — 페더레이션 도메인 추가·서비스 주체 자격증명 추가에 이중 승인과 실시간 경보</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="27" t="inlineStr">
+        <is>
+          <t>SCN-03. 인포스틸러 — 회사 밖 단말에서 털린 자격증명이 MFA 없는 SaaS·VPN 대량 반출로</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="28" t="inlineStr">
+        <is>
+          <t>개요</t>
+        </is>
+      </c>
+      <c r="B30" s="29" t="inlineStr">
+        <is>
+          <t>협력사·개인 PC에서 인포스틸러로 털린 자격증명이 수년 뒤 MFA 없는 SaaS·VPN 로그인으로 이어져 대량 반출·갈취가 된 흐름. Snowflake 플랫폼 자체 침해 증거는 없었고, MFA·접속 허용 목록·자격증명 교체 중 하나만 있었어도 끊길 수 있었다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="28" t="inlineStr">
+        <is>
+          <t>근거 사고</t>
+        </is>
+      </c>
+      <c r="B31" s="29" t="inlineStr">
+        <is>
+          <t>IDI-016 Snowflake 고객 인스턴스 대량 데이터 탈취(인포스틸러 자격증명·MFA 미적용)(2024-05) · IDI-069 HELLCAT 인포스틸러 유출 Jira 자격증명으로 연쇄 침해(Telefónica·Schneider·JLR 등)(2025-03) · IDI-018 Medibank 고객 970만 명 정보 유출(협력사 직원 브라우저 동기화 자격증명·MFA 없는 VPN)(2022-10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>공격 단계</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>IDT-ID</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>세부위협</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>행위</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>탐지 포인트</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>자격증명 접근</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>IDT-CR-01.1
+IDT-LC-01.2</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>인포스틸러로 브라우저 저장 비밀번호·세션 쿠키 탈취
+협력사·외주·게스트 계정 악용</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t>협력사 직원이 업무 브라우저 프로필에 저장한 자격증명이 개인 컴퓨터로 동기화된 뒤 악성코드로 탈취(Medibank), 인포스틸러 감염 단말에서 고객 자격증명이 유출되고 일부는 협력사 단말에서 유출(Snowflake)</t>
+        </is>
+      </c>
+      <c r="F33" s="9" t="inlineStr">
+        <is>
+          <t>인포스틸러 로그·다크웹 유출 모니터링 결과를 사내·고객 계정과 대조</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>지속성</t>
+        </is>
+      </c>
+      <c r="C34" s="12" t="inlineStr">
+        <is>
+          <t>IDT-NH-01.2</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>비밀·자격증명 교체·폐기 실패</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="inlineStr">
+        <is>
+          <t>쓰인 자격증명 일부는 2020년 유출 이후 교체되지 않음(Snowflake), 협력사 직원 단말에서 2021년에 유출된 Jira 자격증명이 여전히 유효(HELLCAT의 JLR 침해)</t>
+        </is>
+      </c>
+      <c r="F34" s="9" t="inlineStr">
+        <is>
+          <t>유출이 확인된 계정과 장기 미변경 자격증명의 로그인 경보</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>초기 침투</t>
+        </is>
+      </c>
+      <c r="C35" s="11" t="inlineStr">
+        <is>
+          <t>IDT-AU-03.3
+IDT-AU-01.2</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>MFA 미적용·레거시 인증 경로 악용
+유출·탈취 자격증명 재사용(유효 계정 악용)</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="inlineStr">
+        <is>
+          <t>MFA와 접속 허용 목록이 없는 Snowflake 고객 인스턴스 약 165곳에 로그인(Snowflake), MFA 없이 사용자 이름·비밀번호만으로 접속되던 VPN으로 침투(Medibank)</t>
+        </is>
+      </c>
+      <c r="F35" s="9" t="inlineStr">
+        <is>
+          <t>처음 보는 출발지·클라이언트 도구의 데이터 플랫폼·VPN 로그인 경보</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>반출</t>
+        </is>
+      </c>
+      <c r="C36" s="11" t="inlineStr">
+        <is>
+          <t>IDT-IM-03</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>계정 기반 대량 데이터 탈취·갈취</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="inlineStr">
+        <is>
+          <t>고객 인스턴스 데이터를 대량 반출하고 갈취(Snowflake), Telefónica·Schneider Electric·Orange·JLR 등의 Jira에서 데이터를 빼내 갈취(HELLCAT), 고객 약 970만 명 정보 탈취·다크웹 공개(Medibank)</t>
+        </is>
+      </c>
+      <c r="F36" s="9" t="inlineStr">
+        <is>
+          <t>대량 조회·내보내기 쿼리와 새 출발지 접근을 상관 분석</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="49" customHeight="1">
+      <c r="A37" s="30" t="inlineStr">
+        <is>
+          <t>초크</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>· IDT-AU-03.3 — 데이터 플랫폼·VPN·SaaS 로그인에 MFA와 접속 허용 목록을 필수로 적용(Snowflake·Medibank 모두 MFA 없는 로그인 경로)
+· IDT-NH-01.2 — 유출 모니터링으로 확인된 자격증명과 장기 미변경 비밀번호를 일괄 교체
+· IDT-CR-01.1 — 업무 자격증명의 브라우저 저장·개인 계정 동기화를 막고 협력사 단말에도 같은 요구 적용</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="27" t="inlineStr">
+        <is>
+          <t>SCN-04. SaaS 연동 토큰·연결 앱 — 연동 하나로 여러 조직 데이터와 다음 자격증명까지</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="28" t="inlineStr">
+        <is>
+          <t>개요</t>
+        </is>
+      </c>
+      <c r="B40" s="29" t="inlineStr">
+        <is>
+          <t>사용자 로그인 없이 연동 앱 토큰이나 직원이 승인한 연결 앱만으로 여러 조직의 SaaS 데이터를 대량 반출하고, 그 데이터 속 자격증명이 다음 침해의 재료가 되는 흐름. 피해 조직의 MFA·로그인 정책을 거치지 않는다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="28" t="inlineStr">
+        <is>
+          <t>근거 사고</t>
+        </is>
+      </c>
+      <c r="B41" s="29" t="inlineStr">
+        <is>
+          <t>IDI-037 Salesloft Drift 연동 OAuth 토큰 탈취로 Salesforce 인스턴스 대량 데이터 반출(2025-08) · IDI-106 Heroku·Travis CI 발급 GitHub OAuth 토큰 탈취로 비공개 저장소 반출(2022-04) · IDI-036 Salesforce 대상 음성 피싱(악성 Data Loader 연결 앱 승인 유도)(2025-06)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="28" t="inlineStr">
+        <is>
+          <t>참조</t>
+        </is>
+      </c>
+      <c r="B42" s="29" t="inlineStr">
+        <is>
+          <t>ATT&amp;CK G1057 · C0059</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>공격 단계</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>IDT-ID</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>세부위협</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>행위</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>탐지 포인트</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>자격증명 접근</t>
+        </is>
+      </c>
+      <c r="C44" s="11" t="inlineStr">
+        <is>
+          <t>IDT-NH-03.1</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="inlineStr">
+        <is>
+          <t>SaaS 연동 앱 토큰 탈취와 연쇄 접근</t>
+        </is>
+      </c>
+      <c r="E44" s="9" t="inlineStr">
+        <is>
+          <t>Salesloft Drift 앱과 Salesforce 연동에 쓰이는 OAuth·리프레시 토큰을 탈취(Drift), Heroku·Travis CI에 발급된 GitHub OAuth 사용자 토큰을 탈취(Heroku·Travis CI)</t>
+        </is>
+      </c>
+      <c r="F44" s="9" t="inlineStr">
+        <is>
+          <t>연동 공급자 침해 공지 구독, 연동 토큰의 새 출발지 사용 경보</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t>초기 침투</t>
+        </is>
+      </c>
+      <c r="C45" s="11" t="inlineStr">
+        <is>
+          <t>IDT-SE-02.2
+IDT-NH-03.2</t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="inlineStr">
+        <is>
+          <t>IT 지원 사칭으로 원격 지원 허용·연결 앱 승인 유도
+악성·과다 권한 OAuth 앱 등록·권한 부여</t>
+        </is>
+      </c>
+      <c r="E45" s="9" t="inlineStr">
+        <is>
+          <t>연결 앱 경로로는 IT 지원 인력을 사칭한 전화로 직원이 공격자가 변조한 Data Loader 연결 앱을 승인(Salesforce 음성 피싱)</t>
+        </is>
+      </c>
+      <c r="F45" s="9" t="inlineStr">
+        <is>
+          <t>신규 연결 앱 승인과 직후 API 대량 조회를 연계 탐지</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B46" s="9" t="inlineStr">
+        <is>
+          <t>횡적 이동</t>
+        </is>
+      </c>
+      <c r="C46" s="11" t="inlineStr">
+        <is>
+          <t>IDT-IM-05</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="inlineStr">
+        <is>
+          <t>공급업체·플랫폼 경유 고객 계정 연쇄 탈취</t>
+        </is>
+      </c>
+      <c r="E46" s="9" t="inlineStr">
+        <is>
+          <t>탈취한 토큰으로 여러 조직의 Salesforce 인스턴스(Drift)와 npm 등 수십 개 조직의 비공개 저장소(Heroku·Travis CI)에 접근</t>
+        </is>
+      </c>
+      <c r="F46" s="9" t="inlineStr">
+        <is>
+          <t>연동 앱별 접근 대상·조회량 기준선 위반 경보</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B47" s="9" t="inlineStr">
+        <is>
+          <t>반출</t>
+        </is>
+      </c>
+      <c r="C47" s="11" t="inlineStr">
+        <is>
+          <t>IDT-IM-03</t>
+        </is>
+      </c>
+      <c r="D47" s="9" t="inlineStr">
+        <is>
+          <t>계정 기반 대량 데이터 탈취·갈취</t>
+        </is>
+      </c>
+      <c r="E47" s="9" t="inlineStr">
+        <is>
+          <t>Salesforce 데이터를 API로 대량 조회·반출한 뒤 갈취에 쓰고(Salesforce 음성 피싱), 비공개 저장소를 복제(Heroku·Travis CI)</t>
+        </is>
+      </c>
+      <c r="F47" s="9" t="inlineStr">
+        <is>
+          <t>대량 API 조회·내보내기·저장소 복제 탐지</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B48" s="9" t="inlineStr">
+        <is>
+          <t>자격증명 접근</t>
+        </is>
+      </c>
+      <c r="C48" s="12" t="inlineStr">
+        <is>
+          <t>IDT-CR-02.1</t>
+        </is>
+      </c>
+      <c r="D48" s="9" t="inlineStr">
+        <is>
+          <t>코드·설정·문서에 노출된 자격증명</t>
+        </is>
+      </c>
+      <c r="E48" s="9" t="inlineStr">
+        <is>
+          <t>반출한 Salesforce 데이터 안에서 AWS 키·Snowflake 토큰·비밀번호 같은 자격증명을 찾아냄(Drift)</t>
+        </is>
+      </c>
+      <c r="F48" s="9" t="inlineStr">
+        <is>
+          <t>SaaS 레코드·첨부의 비밀 스캔, 노출 자격증명의 사용 이력 점검</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B49" s="9" t="inlineStr">
+        <is>
+          <t>횡적 이동</t>
+        </is>
+      </c>
+      <c r="C49" s="12" t="inlineStr">
+        <is>
+          <t>IDT-AU-01.2</t>
+        </is>
+      </c>
+      <c r="D49" s="9" t="inlineStr">
+        <is>
+          <t>유출·탈취 자격증명 재사용(유효 계정 악용)</t>
+        </is>
+      </c>
+      <c r="E49" s="9" t="inlineStr">
+        <is>
+          <t>일부 사례에서는 탈취 자격증명으로 Okta·Microsoft 365 등 다른 클라우드로 이동(Salesforce 음성 피싱)</t>
+        </is>
+      </c>
+      <c r="F49" s="9" t="inlineStr">
+        <is>
+          <t>같은 출발지가 여러 SaaS에 연달아 로그인하는 패턴 상관 분석</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="49" customHeight="1">
+      <c r="A50" s="30" t="inlineStr">
+        <is>
+          <t>초크</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>· IDT-NH-03.1 — 연동 앱 권한 범위·토큰 수명을 최소화하고 연동 공급자 침해 공지 즉시 토큰 전수 폐기
+· IDT-NH-03.2 — 연결 앱 설치·승인을 관리자 승인으로 제한하고 API 사용자 권한 최소화
+· IDT-CR-02.1 — SaaS 레코드·첨부에 자격증명을 남기지 않게 하고 비밀 스캔으로 노출 즉시 교체</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="27" t="inlineStr">
+        <is>
+          <t>SCN-05. AD 장악 — 티켓·디렉터리 취약점에서 도메인 전체 랜섬웨어와 클라우드 파괴까지</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="28" t="inlineStr">
+        <is>
+          <t>개요</t>
+        </is>
+      </c>
+      <c r="B53" s="29" t="inlineStr">
+        <is>
+          <t>공개 경위가 드문 디렉터리 내부 공격을 여러 사고로 이어 붙인 흐름. 특권 계정 하나를 얻는 단계(Kerberoasting·도메인 컨트롤러 취약점)부터 그룹 정책 배포와 하이브리드 동기화 계정을 거친 클라우드 파괴까지, 도메인 관리 권한이 곧 전사 피해 수단이 된다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="28" t="inlineStr">
+        <is>
+          <t>근거 사고</t>
+        </is>
+      </c>
+      <c r="B54" s="29" t="inlineStr">
+        <is>
+          <t>IDI-021 Ascension 랜섬웨어(Kerberoasting으로 AD 특권 계정 확보)(2024-05) · IDI-096 Ryuk의 Zerologon 악용으로 5시간 만에 도메인 전체 암호화(2020-10) · IDI-097 NotPetya의 자격증명 탈취·재사용 확산(2017-06) · IDI-028 Prestige 랜섬웨어(도메인 기본 그룹 정책으로 배포)(2022-10) · IDI-022 Storm-0501 하이브리드 환경 랜섬웨어(Entra Connect 동기화 계정 장악)(2024-09) · IDI-023 MERCURY·DEV-1084 하이브리드 환경 파괴 공격(Azure AD Connect 악용)(2023-04)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="28" t="inlineStr">
+        <is>
+          <t>참조</t>
+        </is>
+      </c>
+      <c r="B55" s="29" t="inlineStr">
+        <is>
+          <t>ATT&amp;CK S1070 · S0446 · S0368 · G0034 · G1053 · KEV CVE-2020-1472</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>공격 단계</t>
+        </is>
+      </c>
+      <c r="C56" s="7" t="inlineStr">
+        <is>
+          <t>IDT-ID</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>세부위협</t>
+        </is>
+      </c>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>행위</t>
+        </is>
+      </c>
+      <c r="F56" s="7" t="inlineStr">
+        <is>
+          <t>탐지 포인트</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B57" s="9" t="inlineStr">
+        <is>
+          <t>자격증명 접근</t>
+        </is>
+      </c>
+      <c r="C57" s="13" t="inlineStr">
+        <is>
+          <t>IDT-TS-02.2</t>
+        </is>
+      </c>
+      <c r="D57" s="9" t="inlineStr">
+        <is>
+          <t>Kerberoasting·AS-REP Roasting</t>
+        </is>
+      </c>
+      <c r="E57" s="9" t="inlineStr">
+        <is>
+          <t>협력사 직원 단말이 검색 결과의 악성 링크로 감염된 뒤 RC4 암호화를 허용하던 Active Directory에서 Kerberoasting으로 특권 계정을 얻음(Ascension)</t>
+        </is>
+      </c>
+      <c r="F57" s="9" t="inlineStr">
+        <is>
+          <t>RC4 서비스 티켓 요청 급증, 한 계정의 다수 서비스 티켓 요청 경보</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B58" s="9" t="inlineStr">
+        <is>
+          <t>권한 상승</t>
+        </is>
+      </c>
+      <c r="C58" s="12" t="inlineStr">
+        <is>
+          <t>IDT-DI-01.4</t>
+        </is>
+      </c>
+      <c r="D58" s="9" t="inlineStr">
+        <is>
+          <t>디렉터리 서비스 취약점 악용(Zerologon·noPac 등)</t>
+        </is>
+      </c>
+      <c r="E58" s="9" t="inlineStr">
+        <is>
+          <t>피싱 메일로 침투한 지 2시간도 안 돼 Netlogon 취약점(Zerologon)으로 도메인 컨트롤러 자격증명을 재설정해 도메인 관리자 권한을 얻음(Ryuk)</t>
+        </is>
+      </c>
+      <c r="F58" s="9" t="inlineStr">
+        <is>
+          <t>도메인 컨트롤러 계정 비밀번호 재설정 이벤트 경보, KEV 등재 즉시 패치 여부 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B59" s="9" t="inlineStr">
+        <is>
+          <t>횡적 이동</t>
+        </is>
+      </c>
+      <c r="C59" s="13" t="inlineStr">
+        <is>
+          <t>IDT-CR-01.2
+IDT-TS-02.1</t>
+        </is>
+      </c>
+      <c r="D59" s="9" t="inlineStr">
+        <is>
+          <t>OS 자격증명 덤프(LSASS·SAM·캐시)
+해시 전달(Pass-the-Hash)·티켓 전달(Pass-the-Ticket)</t>
+        </is>
+      </c>
+      <c r="E59" s="9" t="inlineStr">
+        <is>
+          <t>감염 단말 메모리에서 Windows 자격증명을 빼내 PsExec·WMIC 같은 정상 관리 도구로 다른 시스템에 퍼짐(NotPetya)</t>
+        </is>
+      </c>
+      <c r="F59" s="9" t="inlineStr">
+        <is>
+          <t>LSASS 접근과 원격 관리 도구 연쇄 실행을 상관 분석</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B60" s="9" t="inlineStr">
+        <is>
+          <t>실행</t>
+        </is>
+      </c>
+      <c r="C60" s="13" t="inlineStr">
+        <is>
+          <t>IDT-DI-01.2</t>
+        </is>
+      </c>
+      <c r="D60" s="9" t="inlineStr">
+        <is>
+          <t>AD 권한 구성 결함 악용(ACL·그룹 정책·위임)</t>
+        </is>
+      </c>
+      <c r="E60" s="9" t="inlineStr">
+        <is>
+          <t>도메인 관리자 수준 권한으로 Default Domain 그룹 정책 개체를 바꿔 랜섬웨어 실행 작업을 전체 도메인에 배포(Prestige)</t>
+        </is>
+      </c>
+      <c r="F60" s="9" t="inlineStr">
+        <is>
+          <t>그룹 정책 개체 생성·수정 실시간 경보</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B61" s="9" t="inlineStr">
+        <is>
+          <t>권한 상승</t>
+        </is>
+      </c>
+      <c r="C61" s="11" t="inlineStr">
+        <is>
+          <t>IDT-DI-02</t>
+        </is>
+      </c>
+      <c r="D61" s="9" t="inlineStr">
+        <is>
+          <t>하이브리드 ID·동기화 인프라 침해(Entra Connect·AD FS·PTA)</t>
+        </is>
+      </c>
+      <c r="E61" s="9" t="inlineStr">
+        <is>
+          <t>온프레미스를 장악한 뒤 Entra Connect 동기화 서버 계정 자격증명을 탈취해 MFA 없는 클라우드 관리자 계정으로 클라우드에 들어감(Storm-0501), Azure AD Connect 에이전트의 특권 계정 자격증명으로 클라우드에 접근(MERCURY)</t>
+        </is>
+      </c>
+      <c r="F61" s="9" t="inlineStr">
+        <is>
+          <t>동기화 서비스 계정의 대화형 로그인, 클라우드 관리자 비밀번호 변경 경보</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B62" s="9" t="inlineStr">
+        <is>
+          <t>영향</t>
+        </is>
+      </c>
+      <c r="C62" s="11" t="inlineStr">
+        <is>
+          <t>IDT-IM-02</t>
+        </is>
+      </c>
+      <c r="D62" s="9" t="inlineStr">
+        <is>
+          <t>신원 장악 후 랜섬웨어·파괴(도메인·테넌트 전체)</t>
+        </is>
+      </c>
+      <c r="E62" s="9" t="inlineStr">
+        <is>
+          <t>수천 대에 랜섬웨어 배포·환자 560만 명 데이터 반출(Ascension), 5시간 만에 도메인 전체 암호화(Ryuk), 클라우드 자원·백업 삭제와 랜섬웨어 실행(Storm-0501), 클라우드·온프레미스 자원 대량 삭제(MERCURY)</t>
+        </is>
+      </c>
+      <c r="F62" s="9" t="inlineStr">
+        <is>
+          <t>백업 삭제·대량 암호화·대량 자원 삭제 행위 탐지</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="64" customHeight="1">
+      <c r="A63" s="30" t="inlineStr">
+        <is>
+          <t>초크</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>· IDT-TS-02.2 — RC4 등 약한 Kerberos 암호화를 끄고 서비스 계정은 긴 무작위 비밀번호·관리형 서비스 계정 사용
+· IDT-DI-01.4 — 도메인 컨트롤러 보안 패치를 최우선 일정으로 적용하고 도메인 컨트롤러 접근을 관리 계층으로 제한
+· IDT-DI-02 — 동기화 서버를 도메인 컨트롤러와 같은 최상위 계층으로 보호하고 클라우드 관리자는 클라우드 전용 계정·MFA 필수
+· IDT-IM-02 — 도메인·클라우드 관리 권한으로도 지울 수 없는 분리·불변 백업</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="27" t="inlineStr">
+        <is>
+          <t>SCN-06. IdP 공급업체 침해 — 지원 시스템 세션 토큰에서 고객사 내부 재침투까지</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="28" t="inlineStr">
+        <is>
+          <t>개요</t>
+        </is>
+      </c>
+      <c r="B66" s="29" t="inlineStr">
+        <is>
+          <t>IdP 공급업체 직원의 개인 브라우저에 저장된 서비스 계정 하나가 고객 134곳의 세션 토큰 노출로 번지고, 고객사가 교체에서 빠뜨린 토큰이 이후 재침투 경로가 된 흐름. 공급업체 침해 뒤 고객 쪽 비밀 전수 교체가 마지막 차단 지점이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="28" t="inlineStr">
+        <is>
+          <t>근거 사고</t>
+        </is>
+      </c>
+      <c r="B67" s="29" t="inlineStr">
+        <is>
+          <t>IDI-019 Okta 지원 시스템 침해(서비스 계정 자격증명 개인 Google 프로필 저장·HAR 세션 토큰)(2023-10) · IDI-020 Cloudflare 내부 Atlassian 침해(Okta 침해 때 유출된 토큰 미교체)(2023-11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>공격 단계</t>
+        </is>
+      </c>
+      <c r="C68" s="7" t="inlineStr">
+        <is>
+          <t>IDT-ID</t>
+        </is>
+      </c>
+      <c r="D68" s="7" t="inlineStr">
+        <is>
+          <t>세부위협</t>
+        </is>
+      </c>
+      <c r="E68" s="7" t="inlineStr">
+        <is>
+          <t>행위</t>
+        </is>
+      </c>
+      <c r="F68" s="7" t="inlineStr">
+        <is>
+          <t>탐지 포인트</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B69" s="9" t="inlineStr">
+        <is>
+          <t>자격증명 접근</t>
+        </is>
+      </c>
+      <c r="C69" s="11" t="inlineStr">
+        <is>
+          <t>IDT-NH-02.1</t>
+        </is>
+      </c>
+      <c r="D69" s="9" t="inlineStr">
+        <is>
+          <t>서비스 계정 악용·사람의 비인간 신원 사용</t>
+        </is>
+      </c>
+      <c r="E69" s="9" t="inlineStr">
+        <is>
+          <t>직원이 업무용 노트북 Chrome에서 개인 Google 계정에 로그인해 지원 시스템 서비스 계정 자격증명을 저장했고, 개인 계정이나 기기가 침해되며 서비스 계정이 탈취(Okta)</t>
+        </is>
+      </c>
+      <c r="F69" s="9" t="inlineStr">
+        <is>
+          <t>서비스 계정의 대화형 로그인·새 출발지 접근 경보</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B70" s="9" t="inlineStr">
+        <is>
+          <t>자격증명 접근</t>
+        </is>
+      </c>
+      <c r="C70" s="11" t="inlineStr">
+        <is>
+          <t>IDT-DI-03.1
+IDT-TS-01.1</t>
+        </is>
+      </c>
+      <c r="D70" s="9" t="inlineStr">
+        <is>
+          <t>IdP·인증 서비스 공급업체 침해
+세션 쿠키 탈취·재사용</t>
+        </is>
+      </c>
+      <c r="E70" s="9" t="inlineStr">
+        <is>
+          <t>고객이 지원 요청에 첨부한 HAR 파일에서 세션 토큰을 추출(Okta)</t>
+        </is>
+      </c>
+      <c r="F70" s="9" t="inlineStr">
+        <is>
+          <t>지원 시스템의 고객 첨부 파일 대량 열람 감사, 고객 쪽 세션 재사용(다른 IP·ASN의 같은 세션) 탐지</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B71" s="9" t="inlineStr">
+        <is>
+          <t>횡적 이동</t>
+        </is>
+      </c>
+      <c r="C71" s="11" t="inlineStr">
+        <is>
+          <t>IDT-IM-05</t>
+        </is>
+      </c>
+      <c r="D71" s="9" t="inlineStr">
+        <is>
+          <t>공급업체·플랫폼 경유 고객 계정 연쇄 탈취</t>
+        </is>
+      </c>
+      <c r="E71" s="9" t="inlineStr">
+        <is>
+          <t>BeyondTrust·Cloudflare·1Password 등 고객 134곳에 영향(Okta)</t>
+        </is>
+      </c>
+      <c r="F71" s="9" t="inlineStr">
+        <is>
+          <t>공급업체 침해 공지 즉시 자사 테넌트 감사 로그 점검</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B72" s="9" t="inlineStr">
+        <is>
+          <t>지속성</t>
+        </is>
+      </c>
+      <c r="C72" s="12" t="inlineStr">
+        <is>
+          <t>IDT-NH-01.2</t>
+        </is>
+      </c>
+      <c r="D72" s="9" t="inlineStr">
+        <is>
+          <t>비밀·자격증명 교체·폐기 실패</t>
+        </is>
+      </c>
+      <c r="E72" s="9" t="inlineStr">
+        <is>
+          <t>Okta 침해로 유출된 것 가운데 쓰지 않는다고 잘못 판단해 교체하지 않은 서비스 토큰 1개와 서비스 계정 자격증명 3개가 남음(Cloudflare)</t>
+        </is>
+      </c>
+      <c r="F72" s="9" t="inlineStr">
+        <is>
+          <t>교체 대상 목록 기준 완료 확인, 폐기 예정 토큰의 사용 경보</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B73" s="9" t="inlineStr">
+        <is>
+          <t>초기 침투</t>
+        </is>
+      </c>
+      <c r="C73" s="11" t="inlineStr">
+        <is>
+          <t>IDT-NH-01.1</t>
+        </is>
+      </c>
+      <c r="D73" s="9" t="inlineStr">
+        <is>
+          <t>장기 액세스 키·API 키·토큰 악용</t>
+        </is>
+      </c>
+      <c r="E73" s="9" t="inlineStr">
+        <is>
+          <t>남은 토큰·자격증명으로 Cloudflare의 Atlassian(Confluence·Jira·Bitbucket)에 접근했고 탐지 하루 만에 차단(Cloudflare)</t>
+        </is>
+      </c>
+      <c r="F73" s="9" t="inlineStr">
+        <is>
+          <t>서비스 토큰의 평소와 다른 출발지·대상 접근 경보</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="49" customHeight="1">
+      <c r="A74" s="30" t="inlineStr">
+        <is>
+          <t>초크</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>· IDT-NH-02.1 — 서비스 계정의 대화형 로그인과 개인 브라우저 저장을 막고 출발지를 제한
+· IDT-TS-01.1 — 지원 자료(HAR)는 세션 정보를 지운 뒤 올리게 하고, 세션을 장치에 묶어 재사용을 차단
+· IDT-NH-01.2 — 공급업체 침해 공지 뒤 연동 토큰·서비스 계정 자격증명을 사용 여부와 무관하게 전수 교체</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="27" t="inlineStr">
+        <is>
+          <t>SCN-07. 국내 고객 계정 크리덴셜 스터핑 — 유출 목록 대입에서 개인정보 노출·과징금까지</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="28" t="inlineStr">
+        <is>
+          <t>개요</t>
+        </is>
+      </c>
+      <c r="B77" s="29" t="inlineStr">
+        <is>
+          <t>서비스 자체가 뚫리지 않아도 다른 곳에서 유출된 아이디·비밀번호를 대량 대입해 회원 계정에 로그인하고 개인정보 화면에서 정보를 빼낸 국내 사고들. 처분에서는 반복·대량 로그인 탐지·차단 소홀이 지적됐고, 로그인 뒤 개인정보 마스킹이 피해 규모를 갈랐다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="28" t="inlineStr">
+        <is>
+          <t>근거 사고</t>
+        </is>
+      </c>
+      <c r="B78" s="29" t="inlineStr">
+        <is>
+          <t>IDI-044 GS리테일(GS SHOP·GS25) 크리덴셜 스터핑으로 회원 166만 명 정보 노출(2025-01) · IDI-045 SK스토아 크리덴셜 스터핑으로 회원 12만 5천여 명 정보 유출(2023-11) · IDI-046 케이티알파 기프티쇼 크리덴셜 스터핑(9만 8천여 계정 로그인)(2023-01)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B79" s="7" t="inlineStr">
+        <is>
+          <t>공격 단계</t>
+        </is>
+      </c>
+      <c r="C79" s="7" t="inlineStr">
+        <is>
+          <t>IDT-ID</t>
+        </is>
+      </c>
+      <c r="D79" s="7" t="inlineStr">
+        <is>
+          <t>세부위협</t>
+        </is>
+      </c>
+      <c r="E79" s="7" t="inlineStr">
+        <is>
+          <t>행위</t>
+        </is>
+      </c>
+      <c r="F79" s="7" t="inlineStr">
+        <is>
+          <t>탐지 포인트</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B80" s="9" t="inlineStr">
+        <is>
+          <t>자격증명 접근</t>
+        </is>
+      </c>
+      <c r="C80" s="11" t="inlineStr">
+        <is>
+          <t>IDT-CI-01</t>
+        </is>
+      </c>
+      <c r="D80" s="9" t="inlineStr">
+        <is>
+          <t>고객 계정 대량 크리덴셜 스터핑</t>
+        </is>
+      </c>
+      <c r="E80" s="9" t="inlineStr">
+        <is>
+          <t>다른 곳에서 유출된 아이디·비밀번호를 대입 — 국내외 14개 IP로 초당 최대 372회, 총 4,400만 회 이상(SK스토아), 열흘간 4,305개 IP로 540만 회 이상(기프티쇼)</t>
+        </is>
+      </c>
+      <c r="F80" s="9" t="inlineStr">
+        <is>
+          <t>같은 IP·기기 지문의 단시간 대량 로그인, 로그인 성공률 급변을 실시간 탐지</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B81" s="9" t="inlineStr">
+        <is>
+          <t>초기 침투</t>
+        </is>
+      </c>
+      <c r="C81" s="11" t="inlineStr">
+        <is>
+          <t>IDT-CI-01</t>
+        </is>
+      </c>
+      <c r="D81" s="9" t="inlineStr">
+        <is>
+          <t>고객 계정 대량 크리덴셜 스터핑</t>
+        </is>
+      </c>
+      <c r="E81" s="9" t="inlineStr">
+        <is>
+          <t>12만 5천여 계정(SK스토아)·약 9만 8천 개 계정(기프티쇼)에 로그인, GS SHOP(2024-06~2025-02)과 GS25(2024-12~2025-01)에 로그인(GS리테일)</t>
+        </is>
+      </c>
+      <c r="F81" s="9" t="inlineStr">
+        <is>
+          <t>처음 보는 기기의 로그인 직후 개인정보 조회·변경 경보</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B82" s="9" t="inlineStr">
+        <is>
+          <t>수집</t>
+        </is>
+      </c>
+      <c r="C82" s="11" t="inlineStr">
+        <is>
+          <t>IDT-IM-03</t>
+        </is>
+      </c>
+      <c r="D82" s="9" t="inlineStr">
+        <is>
+          <t>계정 기반 대량 데이터 탈취·갈취</t>
+        </is>
+      </c>
+      <c r="E82" s="9" t="inlineStr">
+        <is>
+          <t>회원정보 수정 페이지에서 이름·연락처·주소 등을 빼냄(GS리테일), 개인정보가 담긴 페이지에 접근했고 일부 페이지는 비밀번호를 평문으로 송수신(SK스토아)</t>
+        </is>
+      </c>
+      <c r="F82" s="9" t="inlineStr">
+        <is>
+          <t>개인정보 페이지 대량 조회·자동화 도구 접근 탐지</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B83" s="9" t="inlineStr">
+        <is>
+          <t>영향</t>
+        </is>
+      </c>
+      <c r="C83" s="11" t="inlineStr">
+        <is>
+          <t>IDT-IM-03</t>
+        </is>
+      </c>
+      <c r="D83" s="9" t="inlineStr">
+        <is>
+          <t>계정 기반 대량 데이터 탈취·갈취</t>
+        </is>
+      </c>
+      <c r="E83" s="9" t="inlineStr">
+        <is>
+          <t>GS SHOP 158만여 명·GS25 7만 9천여 명 정보 노출로 과징금 128억 원(GS리테일), 과징금 14억 3,200만 원(SK스토아), 마스킹 덕분에 실제 유출은 51명에 그침(기프티쇼)</t>
+        </is>
+      </c>
+      <c r="F83" s="9" t="inlineStr">
+        <is>
+          <t>처분 사례의 지적 사항(대량 로그인 탐지·차단, 평문 전송)을 자사 탐지 규칙·점검 항목과 대조</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="34" customHeight="1">
+      <c r="A84" s="30" t="inlineStr">
+        <is>
+          <t>초크</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>· IDT-CI-01 — 같은 IP·기기의 단시간 대량 로그인 탐지·차단과 봇 차단, 고객 계정 MFA·패스키 제공
+· IDT-IM-03 — 로그인 뒤 개인정보 화면 마스킹과 개인정보 변경 재인증(기프티쇼는 마스킹으로 실제 유출이 51명에 그침)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="27" t="inlineStr">
+        <is>
+          <t>SCN-08. 국내 통신 가입자 인증 체계 — 관리망 계정·불법 기지국에서 유심 정보 유출·무단 결제까지</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="28" t="inlineStr">
+        <is>
+          <t>개요</t>
+        </is>
+      </c>
+      <c r="B87" s="29" t="inlineStr">
+        <is>
+          <t>휴대폰 문자·유심을 신원 확인 수단으로 쓰는 구조에서 통신사 인증 체계가 뚫리면 가입자 개인이 막을 수 없는 피해가 된다. 관리망 서버 계정 관리 부실(SK텔레콤), 불법 초소형 기지국(KT), 심스와핑 의심 사례(KT 가입자)가 서로 다른 경로로 이를 보여 줬다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="28" t="inlineStr">
+        <is>
+          <t>근거 사고</t>
+        </is>
+      </c>
+      <c r="B88" s="29" t="inlineStr">
+        <is>
+          <t>IDI-040 SK텔레콤 유심 정보 2,696만 건 유출(HSS 가입자 인증키 등)(2025-04) · IDI-041 KT 불법 펨토셀 경유 결제 인증 탈취·무단 소액결제(2025-09) · IDI-047 KT 가입자 심스와핑 의심 가상자산 탈취(2022-01)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B89" s="7" t="inlineStr">
+        <is>
+          <t>공격 단계</t>
+        </is>
+      </c>
+      <c r="C89" s="7" t="inlineStr">
+        <is>
+          <t>IDT-ID</t>
+        </is>
+      </c>
+      <c r="D89" s="7" t="inlineStr">
+        <is>
+          <t>세부위협</t>
+        </is>
+      </c>
+      <c r="E89" s="7" t="inlineStr">
+        <is>
+          <t>행위</t>
+        </is>
+      </c>
+      <c r="F89" s="7" t="inlineStr">
+        <is>
+          <t>탐지 포인트</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B90" s="9" t="inlineStr">
+        <is>
+          <t>초기 침투</t>
+        </is>
+      </c>
+      <c r="C90" s="11" t="inlineStr">
+        <is>
+          <t>IDT-CI-02</t>
+        </is>
+      </c>
+      <c r="D90" s="9" t="inlineStr">
+        <is>
+          <t>통신 가입자 인증 체계 침해(유심 인증키·불법 기지국)</t>
+        </is>
+      </c>
+      <c r="E90" s="9" t="inlineStr">
+        <is>
+          <t>최초 침투는 2021-08로 특정되고 서버 28대에서 악성코드 33종이 발견(SK텔레콤)</t>
+        </is>
+      </c>
+      <c r="F90" s="9" t="inlineStr">
+        <is>
+          <t>가입자 인증 서버·관리망 서버의 악성코드·비인가 접속 점검</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B91" s="9" t="inlineStr">
+        <is>
+          <t>지속성</t>
+        </is>
+      </c>
+      <c r="C91" s="12" t="inlineStr">
+        <is>
+          <t>IDT-NH-01.2</t>
+        </is>
+      </c>
+      <c r="D91" s="9" t="inlineStr">
+        <is>
+          <t>비밀·자격증명 교체·폐기 실패</t>
+        </is>
+      </c>
+      <c r="E91" s="9" t="inlineStr">
+        <is>
+          <t>시스템 관리망 서버 계정 비밀번호를 바꾸지 않고 만료일도 두지 않았으며, 2022년 HSS 관리서버의 비정상 로그인 정황을 발견하고도 신고하지 않음(SK텔레콤)</t>
+        </is>
+      </c>
+      <c r="F91" s="9" t="inlineStr">
+        <is>
+          <t>관리망 계정의 장기 미변경 비밀번호·비정상 로그인 점검과 즉시 보고 체계</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B92" s="9" t="inlineStr">
+        <is>
+          <t>수집</t>
+        </is>
+      </c>
+      <c r="C92" s="11" t="inlineStr">
+        <is>
+          <t>IDT-CI-02
+IDT-IM-03</t>
+        </is>
+      </c>
+      <c r="D92" s="9" t="inlineStr">
+        <is>
+          <t>통신 가입자 인증 체계 침해(유심 인증키·불법 기지국)
+계정 기반 대량 데이터 탈취·갈취</t>
+        </is>
+      </c>
+      <c r="E92" s="9" t="inlineStr">
+        <is>
+          <t>유심 정보 25종 2,696만여 건 유출(SK텔레콤)</t>
+        </is>
+      </c>
+      <c r="F92" s="9" t="inlineStr">
+        <is>
+          <t>가입자 인증 서버의 대량 조회·외부 전송 탐지</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B93" s="9" t="inlineStr">
+        <is>
+          <t>자격증명 접근</t>
+        </is>
+      </c>
+      <c r="C93" s="11" t="inlineStr">
+        <is>
+          <t>IDT-CI-02</t>
+        </is>
+      </c>
+      <c r="D93" s="9" t="inlineStr">
+        <is>
+          <t>통신 가입자 인증 체계 침해(유심 인증키·불법 기지국)</t>
+        </is>
+      </c>
+      <c r="E93" s="9" t="inlineStr">
+        <is>
+          <t>통신사 인증서를 가진 불법 초소형 기지국(펨토셀)으로 가입자 단말 정보를 얻고 문자·ARS 결제 인증값을 가로챔(KT)</t>
+        </is>
+      </c>
+      <c r="F93" s="9" t="inlineStr">
+        <is>
+          <t>등록되지 않은 기지국·펨토셀 접속, 같은 기지국을 거친 결제 인증 급증 탐지</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B94" s="9" t="inlineStr">
+        <is>
+          <t>자격증명 접근</t>
+        </is>
+      </c>
+      <c r="C94" s="12" t="inlineStr">
+        <is>
+          <t>IDT-AU-03.2</t>
+        </is>
+      </c>
+      <c r="D94" s="9" t="inlineStr">
+        <is>
+          <t>SMS·음성 OTP 가로채기와 SIM 스와핑</t>
+        </is>
+      </c>
+      <c r="E94" s="9" t="inlineStr">
+        <is>
+          <t>가입자 휴대폰이 갑자기 먹통이 된 뒤 피해가 신고되어 국내 첫 심스와핑 의심 사례로 수사(KT 가입자)</t>
+        </is>
+      </c>
+      <c r="F94" s="9" t="inlineStr">
+        <is>
+          <t>유심 변경·기기변경 직후의 금융·가상자산 계정 로그인 경보</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B95" s="9" t="inlineStr">
+        <is>
+          <t>영향</t>
+        </is>
+      </c>
+      <c r="C95" s="11" t="inlineStr">
+        <is>
+          <t>IDT-IM-01</t>
+        </is>
+      </c>
+      <c r="D95" s="9" t="inlineStr">
+        <is>
+          <t>계정 장악 기반 금전 사기(BEC·송금·사칭 게시)</t>
+        </is>
+      </c>
+      <c r="E95" s="9" t="inlineStr">
+        <is>
+          <t>무단 소액결제로 결제 피해자 368명·2억 4,300만 원, 개인정보 유출 2만 2,227명(KT), 가상자산 거래소 계정에서 수천만~수억 원대 암호화폐 탈취 신고(KT 가입자)</t>
+        </is>
+      </c>
+      <c r="F95" s="9" t="inlineStr">
+        <is>
+          <t>인증 직후 고액 결제·출금 이상 거래 탐지</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="49" customHeight="1">
+      <c r="A96" s="30" t="inlineStr">
+        <is>
+          <t>초크</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>· IDT-NH-01.2 — 통신 관리망 서버 계정 비밀번호 정기 교체·만료 설정과 비정상 로그인 정황의 즉시 신고·조사
+· IDT-CI-02 — 가입자 인증키를 하드웨어 보안 모듈로 보호하고 기지국·펨토셀 인증서 수명 단축(KT 사고 뒤 10년에서 1개월로)·접속 인가 통제
+· IDT-AU-03.2 — 유심 기기변경·재발급에 강한 본인확인(KT는 한동안 매장 방문으로만 처리)을 요구하고, 서비스 제공자는 문자 단독 인증을 줄임</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="36">
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="B54:F54"/>
+    <mergeCell ref="B66:F66"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="A86:F86"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B27:F27"/>
+    <mergeCell ref="B96:F96"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="A76:F76"/>
+    <mergeCell ref="B42:F42"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="B88:F88"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="A52:F52"/>
+    <mergeCell ref="B87:F87"/>
+    <mergeCell ref="B78:F78"/>
+    <mergeCell ref="B19:F19"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B84:F84"/>
+    <mergeCell ref="A39:F39"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B74:F74"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B55:F55"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B50:F50"/>
+    <mergeCell ref="B41:F41"/>
+    <mergeCell ref="A65:F65"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
